--- a/research/traditional_assets/database/data/jamaica/jamaica_household_products.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_household_products.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="jmse_bpow" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.126</v>
+        <v>-0.0389</v>
       </c>
       <c r="E2">
-        <v>-0.328</v>
+        <v>0.00378</v>
       </c>
       <c r="G2">
-        <v>-0.01919191919191919</v>
+        <v>0.09962686567164179</v>
       </c>
       <c r="H2">
-        <v>-0.01919191919191919</v>
+        <v>0.09962686567164179</v>
       </c>
       <c r="I2">
-        <v>-0.05252525252525252</v>
+        <v>0.130410447761194</v>
       </c>
       <c r="J2">
-        <v>-0.02681552365762892</v>
+        <v>0.1149671052631579</v>
       </c>
       <c r="K2">
-        <v>0.098</v>
+        <v>0.871</v>
       </c>
       <c r="L2">
-        <v>0.0197979797979798</v>
+        <v>0.1625</v>
       </c>
       <c r="M2">
-        <v>0.07000000000000001</v>
+        <v>0.149</v>
       </c>
       <c r="N2">
-        <v>0.006140350877192982</v>
+        <v>0.01542443064182195</v>
       </c>
       <c r="O2">
-        <v>0.7142857142857143</v>
+        <v>0.1710677382319173</v>
       </c>
       <c r="P2">
-        <v>0.07000000000000001</v>
+        <v>0.149</v>
       </c>
       <c r="Q2">
-        <v>0.006140350877192982</v>
+        <v>0.01542443064182195</v>
       </c>
       <c r="R2">
-        <v>0.7142857142857143</v>
+        <v>0.1710677382319173</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.121</v>
+        <v>1.23</v>
       </c>
       <c r="V2">
-        <v>0.0106140350877193</v>
+        <v>0.1273291925465838</v>
       </c>
       <c r="W2">
-        <v>0.01048128342245989</v>
+        <v>0.09275825346112886</v>
       </c>
       <c r="X2">
-        <v>0.1901168051904193</v>
+        <v>0.1154210242824232</v>
       </c>
       <c r="Y2">
-        <v>-0.1796355217679594</v>
+        <v>-0.02266277082129438</v>
       </c>
       <c r="Z2">
-        <v>0.5551194347874847</v>
+        <v>0.5581589086743727</v>
       </c>
       <c r="AA2">
-        <v>-0.01488581833635339</v>
+        <v>0.06416991400713591</v>
       </c>
       <c r="AB2">
-        <v>0.1873973145392712</v>
+        <v>0.1147860675431895</v>
       </c>
       <c r="AC2">
-        <v>-0.2022831328756245</v>
+        <v>-0.05061615353605363</v>
       </c>
       <c r="AD2">
-        <v>0.334</v>
+        <v>0.162</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.334</v>
+        <v>0.162</v>
       </c>
       <c r="AG2">
-        <v>0.213</v>
+        <v>-1.068</v>
       </c>
       <c r="AH2">
-        <v>0.02846429180160218</v>
+        <v>0.01649358582773366</v>
       </c>
       <c r="AI2">
-        <v>0.03434800493624023</v>
+        <v>0.01603642843001386</v>
       </c>
       <c r="AJ2">
-        <v>0.01834151382071816</v>
+        <v>-0.1243016759776536</v>
       </c>
       <c r="AK2">
-        <v>0.02218056857232115</v>
+        <v>-0.1203787195671776</v>
       </c>
       <c r="AL2">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="AM2">
-        <v>-0.08099999999999999</v>
+        <v>-0.194</v>
       </c>
       <c r="AN2">
-        <v>-4.771428571428571</v>
+        <v>0.1760869565217391</v>
       </c>
       <c r="AO2">
-        <v>-11.81818181818182</v>
+        <v>29.125</v>
       </c>
       <c r="AP2">
-        <v>-3.042857142857143</v>
+        <v>-1.160869565217391</v>
       </c>
       <c r="AQ2">
-        <v>3.209876543209877</v>
+        <v>-3.603092783505154</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.126</v>
+        <v>-0.0389</v>
       </c>
       <c r="E3">
-        <v>-0.328</v>
+        <v>0.00378</v>
       </c>
       <c r="G3">
-        <v>-0.01919191919191919</v>
+        <v>0.09962686567164179</v>
       </c>
       <c r="H3">
-        <v>-0.01919191919191919</v>
+        <v>0.09962686567164179</v>
       </c>
       <c r="I3">
-        <v>-0.05252525252525252</v>
+        <v>0.130410447761194</v>
       </c>
       <c r="J3">
-        <v>-0.02681552365762892</v>
+        <v>0.1149671052631579</v>
       </c>
       <c r="K3">
-        <v>0.098</v>
+        <v>0.871</v>
       </c>
       <c r="L3">
-        <v>0.0197979797979798</v>
+        <v>0.1625</v>
       </c>
       <c r="M3">
+        <v>0.149</v>
+      </c>
+      <c r="N3">
+        <v>0.01542443064182195</v>
+      </c>
+      <c r="O3">
+        <v>0.1710677382319173</v>
+      </c>
+      <c r="P3">
+        <v>0.149</v>
+      </c>
+      <c r="Q3">
+        <v>0.01542443064182195</v>
+      </c>
+      <c r="R3">
+        <v>0.1710677382319173</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>1.23</v>
+      </c>
+      <c r="V3">
+        <v>0.1273291925465838</v>
+      </c>
+      <c r="W3">
+        <v>0.09275825346112886</v>
+      </c>
+      <c r="X3">
+        <v>0.1154210242824232</v>
+      </c>
+      <c r="Y3">
+        <v>-0.02266277082129438</v>
+      </c>
+      <c r="Z3">
+        <v>0.5581589086743727</v>
+      </c>
+      <c r="AA3">
+        <v>0.06416991400713591</v>
+      </c>
+      <c r="AB3">
+        <v>0.1147860675431895</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05061615353605363</v>
+      </c>
+      <c r="AD3">
+        <v>0.162</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.162</v>
+      </c>
+      <c r="AG3">
+        <v>-1.068</v>
+      </c>
+      <c r="AH3">
+        <v>0.01649358582773366</v>
+      </c>
+      <c r="AI3">
+        <v>0.01603642843001386</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.1243016759776536</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1203787195671776</v>
+      </c>
+      <c r="AL3">
+        <v>0.024</v>
+      </c>
+      <c r="AM3">
+        <v>-0.194</v>
+      </c>
+      <c r="AN3">
+        <v>0.1760869565217391</v>
+      </c>
+      <c r="AO3">
+        <v>29.125</v>
+      </c>
+      <c r="AP3">
+        <v>-1.160869565217391</v>
+      </c>
+      <c r="AQ3">
+        <v>-3.603092783505154</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Blue Power Group Limited (JMSE:BPOW)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JMSE:BPOW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Household Products</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>29.125</v>
+      </c>
+      <c r="F2">
+        <v>4.51022044989701</v>
+      </c>
+      <c r="G2">
+        <v>0.176086956521739</v>
+      </c>
+      <c r="H2">
+        <v>3.30958695652174</v>
+      </c>
+      <c r="I2">
+        <v>0.0164935858277337</v>
+      </c>
+      <c r="J2">
+        <v>0.31</v>
+      </c>
+      <c r="K2">
+        <v>9.66</v>
+      </c>
+      <c r="L2">
+        <v>7.56402466087985</v>
+      </c>
+      <c r="M2">
+        <v>8.592000000000001</v>
+      </c>
+      <c r="N2">
+        <v>9.378844660879849</v>
+      </c>
+      <c r="O2">
+        <v>0.162</v>
+      </c>
+      <c r="P2">
+        <v>3.04482</v>
+      </c>
+      <c r="Q2">
+        <v>0.11478606754319</v>
+      </c>
+      <c r="R2">
+        <v>0.108411163841351</v>
+      </c>
+      <c r="S2">
+        <v>0.0769238323518473</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.115421024282423</v>
+      </c>
+      <c r="X2">
+        <v>0.139966541799059</v>
+      </c>
+      <c r="Y2">
+        <v>0.685127296426148</v>
+      </c>
+      <c r="Z2">
+        <v>0.9046075789340799</v>
+      </c>
+      <c r="AA2">
+        <v>0.162</v>
+      </c>
+      <c r="AB2">
+        <v>0.102565109802463</v>
+      </c>
+      <c r="AC2">
+        <v>29.125</v>
+      </c>
+      <c r="AD2">
+        <v>0.162</v>
+      </c>
+      <c r="AE2">
+        <v>0.024</v>
+      </c>
+      <c r="AF2">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>0.92</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>9.66</v>
+      </c>
+      <c r="AK2">
+        <v>0.1118347271844283</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>0.024</v>
+      </c>
+      <c r="AS2">
+        <v>0.162</v>
+      </c>
+      <c r="AT2">
+        <v>1.23</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1144692832968572</v>
+      </c>
+      <c r="C2">
+        <v>9.857969816627046</v>
+      </c>
+      <c r="D2">
+        <v>8.627969816627045</v>
+      </c>
+      <c r="E2">
+        <v>-0.162</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.23</v>
+      </c>
+      <c r="H2">
+        <v>9.66</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.92</v>
+      </c>
+      <c r="K2">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L2">
+        <v>0.699</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.699</v>
+      </c>
+      <c r="O2">
+        <v>0.17475</v>
+      </c>
+      <c r="P2">
+        <v>0.52425</v>
+      </c>
+      <c r="Q2">
+        <v>0.7452500000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1144692832968572</v>
+      </c>
+      <c r="T2">
+        <v>0.6766170509100436</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.114227360088615</v>
+      </c>
+      <c r="C3">
+        <v>9.787422880303179</v>
+      </c>
+      <c r="D3">
+        <v>8.655642880303178</v>
+      </c>
+      <c r="E3">
+        <v>-0.06377999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.09822000000000002</v>
+      </c>
+      <c r="G3">
+        <v>1.23</v>
+      </c>
+      <c r="H3">
+        <v>9.66</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.92</v>
+      </c>
+      <c r="K3">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.699</v>
+      </c>
+      <c r="M3">
+        <v>0.004390434000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.6946095659999999</v>
+      </c>
+      <c r="O3">
+        <v>0.1736523915</v>
+      </c>
+      <c r="P3">
+        <v>0.5209571744999999</v>
+      </c>
+      <c r="Q3">
+        <v>0.7419571745</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1150425354430455</v>
+      </c>
+      <c r="T3">
+        <v>0.6817429376593621</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>159.2097728835007</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1139854368803729</v>
+      </c>
+      <c r="C4">
+        <v>9.717054030497767</v>
+      </c>
+      <c r="D4">
+        <v>8.683494030497767</v>
+      </c>
+      <c r="E4">
+        <v>0.03444000000000003</v>
+      </c>
+      <c r="F4">
+        <v>0.19644</v>
+      </c>
+      <c r="G4">
+        <v>1.23</v>
+      </c>
+      <c r="H4">
+        <v>9.66</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.92</v>
+      </c>
+      <c r="K4">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.699</v>
+      </c>
+      <c r="M4">
+        <v>0.008780868000000002</v>
+      </c>
+      <c r="N4">
+        <v>0.690219132</v>
+      </c>
+      <c r="O4">
+        <v>0.172554783</v>
+      </c>
+      <c r="P4">
+        <v>0.5176643489999999</v>
+      </c>
+      <c r="Q4">
+        <v>0.738664349</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1156274866126254</v>
+      </c>
+      <c r="T4">
+        <v>0.6869734343423403</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>79.60488644175038</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1137435136721307</v>
+      </c>
+      <c r="C5">
+        <v>9.646864991840202</v>
+      </c>
+      <c r="D5">
+        <v>8.711524991840202</v>
+      </c>
+      <c r="E5">
+        <v>0.13266</v>
+      </c>
+      <c r="F5">
+        <v>0.29466</v>
+      </c>
+      <c r="G5">
+        <v>1.23</v>
+      </c>
+      <c r="H5">
+        <v>9.66</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.92</v>
+      </c>
+      <c r="K5">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L5">
+        <v>0.699</v>
+      </c>
+      <c r="M5">
+        <v>0.013171302</v>
+      </c>
+      <c r="N5">
+        <v>0.6858286979999999</v>
+      </c>
+      <c r="O5">
+        <v>0.1714571745</v>
+      </c>
+      <c r="P5">
+        <v>0.5143715234999999</v>
+      </c>
+      <c r="Q5">
+        <v>0.7353715235</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1162244986310626</v>
+      </c>
+      <c r="T5">
+        <v>0.6923117763177508</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>53.06992429450025</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1135015904638886</v>
+      </c>
+      <c r="C6">
+        <v>9.576857511300901</v>
+      </c>
+      <c r="D6">
+        <v>8.7397375113009</v>
+      </c>
+      <c r="E6">
+        <v>0.2308800000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.3928800000000001</v>
+      </c>
+      <c r="G6">
+        <v>1.23</v>
+      </c>
+      <c r="H6">
+        <v>9.66</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.92</v>
+      </c>
+      <c r="K6">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L6">
+        <v>0.699</v>
+      </c>
+      <c r="M6">
+        <v>0.017561736</v>
+      </c>
+      <c r="N6">
+        <v>0.681438264</v>
+      </c>
+      <c r="O6">
+        <v>0.170359566</v>
+      </c>
+      <c r="P6">
+        <v>0.5110786979999999</v>
+      </c>
+      <c r="Q6">
+        <v>0.732078698</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1168339483998839</v>
+      </c>
+      <c r="T6">
+        <v>0.6977613337509825</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>39.80244322087519</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1132596672556464</v>
+      </c>
+      <c r="C7">
+        <v>9.507033358554271</v>
+      </c>
+      <c r="D7">
+        <v>8.76813335855427</v>
+      </c>
+      <c r="E7">
+        <v>0.3291000000000001</v>
+      </c>
+      <c r="F7">
+        <v>0.4911000000000001</v>
+      </c>
+      <c r="G7">
+        <v>1.23</v>
+      </c>
+      <c r="H7">
+        <v>9.66</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.92</v>
+      </c>
+      <c r="K7">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L7">
+        <v>0.699</v>
+      </c>
+      <c r="M7">
+        <v>0.02195217000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.6770478299999999</v>
+      </c>
+      <c r="O7">
+        <v>0.1692619575</v>
+      </c>
+      <c r="P7">
+        <v>0.5077858725</v>
+      </c>
+      <c r="Q7">
+        <v>0.7287858725</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1174562286901542</v>
+      </c>
+      <c r="T7">
+        <v>0.7033256187091244</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>31.84195457670015</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1130177440474043</v>
+      </c>
+      <c r="C8">
+        <v>9.437394326348729</v>
+      </c>
+      <c r="D8">
+        <v>8.796714326348729</v>
+      </c>
+      <c r="E8">
+        <v>0.42732</v>
+      </c>
+      <c r="F8">
+        <v>0.5893200000000001</v>
+      </c>
+      <c r="G8">
+        <v>1.23</v>
+      </c>
+      <c r="H8">
+        <v>9.66</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.92</v>
+      </c>
+      <c r="K8">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L8">
+        <v>0.699</v>
+      </c>
+      <c r="M8">
+        <v>0.02634260400000001</v>
+      </c>
+      <c r="N8">
+        <v>0.672657396</v>
+      </c>
+      <c r="O8">
+        <v>0.168164349</v>
+      </c>
+      <c r="P8">
+        <v>0.504493047</v>
+      </c>
+      <c r="Q8">
+        <v>0.7254930470000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1180917489866003</v>
+      </c>
+      <c r="T8">
+        <v>0.7090082927089287</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>26.53496214725013</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
         <v>0.07000000000000001</v>
       </c>
-      <c r="N3">
-        <v>0.006140350877192982</v>
-      </c>
-      <c r="O3">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q3">
-        <v>0.006140350877192982</v>
-      </c>
-      <c r="R3">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.121</v>
-      </c>
-      <c r="V3">
-        <v>0.0106140350877193</v>
-      </c>
-      <c r="W3">
-        <v>0.01048128342245989</v>
-      </c>
-      <c r="X3">
-        <v>0.1901168051904193</v>
-      </c>
-      <c r="Y3">
-        <v>-0.1796355217679594</v>
-      </c>
-      <c r="Z3">
-        <v>0.5551194347874847</v>
-      </c>
-      <c r="AA3">
-        <v>-0.01488581833635339</v>
-      </c>
-      <c r="AB3">
-        <v>0.1873973145392712</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2022831328756245</v>
-      </c>
-      <c r="AD3">
-        <v>0.334</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.334</v>
-      </c>
-      <c r="AG3">
-        <v>0.213</v>
-      </c>
-      <c r="AH3">
-        <v>0.02846429180160218</v>
-      </c>
-      <c r="AI3">
-        <v>0.03434800493624023</v>
-      </c>
-      <c r="AJ3">
-        <v>0.01834151382071816</v>
-      </c>
-      <c r="AK3">
-        <v>0.02218056857232115</v>
-      </c>
-      <c r="AL3">
-        <v>0.022</v>
-      </c>
-      <c r="AM3">
-        <v>-0.08099999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>-4.771428571428571</v>
-      </c>
-      <c r="AO3">
-        <v>-11.81818181818182</v>
-      </c>
-      <c r="AP3">
-        <v>-3.042857142857143</v>
-      </c>
-      <c r="AQ3">
-        <v>3.209876543209877</v>
+      <c r="B9">
+        <v>0.1127758208391622</v>
+      </c>
+      <c r="C9">
+        <v>9.36794223088401</v>
+      </c>
+      <c r="D9">
+        <v>8.82548223088401</v>
+      </c>
+      <c r="E9">
+        <v>0.5255400000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.6875400000000002</v>
+      </c>
+      <c r="G9">
+        <v>1.23</v>
+      </c>
+      <c r="H9">
+        <v>9.66</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.92</v>
+      </c>
+      <c r="K9">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L9">
+        <v>0.699</v>
+      </c>
+      <c r="M9">
+        <v>0.03073303800000001</v>
+      </c>
+      <c r="N9">
+        <v>0.6682669619999999</v>
+      </c>
+      <c r="O9">
+        <v>0.1670667405</v>
+      </c>
+      <c r="P9">
+        <v>0.5012002215</v>
+      </c>
+      <c r="Q9">
+        <v>0.7222002215000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1187409363861959</v>
+      </c>
+      <c r="T9">
+        <v>0.7148131747517397</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>22.74425326907154</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.11253389763092</v>
+      </c>
+      <c r="C10">
+        <v>9.298678912195863</v>
+      </c>
+      <c r="D10">
+        <v>8.854438912195862</v>
+      </c>
+      <c r="E10">
+        <v>0.6237600000000001</v>
+      </c>
+      <c r="F10">
+        <v>0.7857600000000001</v>
+      </c>
+      <c r="G10">
+        <v>1.23</v>
+      </c>
+      <c r="H10">
+        <v>9.66</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.92</v>
+      </c>
+      <c r="K10">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L10">
+        <v>0.699</v>
+      </c>
+      <c r="M10">
+        <v>0.03512347200000001</v>
+      </c>
+      <c r="N10">
+        <v>0.663876528</v>
+      </c>
+      <c r="O10">
+        <v>0.165969132</v>
+      </c>
+      <c r="P10">
+        <v>0.497907396</v>
+      </c>
+      <c r="Q10">
+        <v>0.7189073960000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1194042365553478</v>
+      </c>
+      <c r="T10">
+        <v>0.7207442498824378</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>19.9012216104376</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1122919744226779</v>
+      </c>
+      <c r="C11">
+        <v>9.229606234548406</v>
+      </c>
+      <c r="D11">
+        <v>8.883586234548405</v>
+      </c>
+      <c r="E11">
+        <v>0.7219800000000001</v>
+      </c>
+      <c r="F11">
+        <v>0.8839800000000001</v>
+      </c>
+      <c r="G11">
+        <v>1.23</v>
+      </c>
+      <c r="H11">
+        <v>9.66</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.92</v>
+      </c>
+      <c r="K11">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L11">
+        <v>0.699</v>
+      </c>
+      <c r="M11">
+        <v>0.03951390600000001</v>
+      </c>
+      <c r="N11">
+        <v>0.6594860939999999</v>
+      </c>
+      <c r="O11">
+        <v>0.1648715235</v>
+      </c>
+      <c r="P11">
+        <v>0.4946145704999999</v>
+      </c>
+      <c r="Q11">
+        <v>0.7156145705</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1200821147501955</v>
+      </c>
+      <c r="T11">
+        <v>0.7268056783127117</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>17.68997476483342</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1120500512144357</v>
+      </c>
+      <c r="C12">
+        <v>9.16072608683419</v>
+      </c>
+      <c r="D12">
+        <v>8.91292608683419</v>
+      </c>
+      <c r="E12">
+        <v>0.8202000000000002</v>
+      </c>
+      <c r="F12">
+        <v>0.9822000000000002</v>
+      </c>
+      <c r="G12">
+        <v>1.23</v>
+      </c>
+      <c r="H12">
+        <v>9.66</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.92</v>
+      </c>
+      <c r="K12">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0.699</v>
+      </c>
+      <c r="M12">
+        <v>0.04390434000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.65509566</v>
+      </c>
+      <c r="O12">
+        <v>0.163773915</v>
+      </c>
+      <c r="P12">
+        <v>0.491321745</v>
+      </c>
+      <c r="Q12">
+        <v>0.7123217450000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1207750569049286</v>
+      </c>
+      <c r="T12">
+        <v>0.7330018051525472</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>15.92097728835008</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1118081280061936</v>
+      </c>
+      <c r="C13">
+        <v>9.092040382982269</v>
+      </c>
+      <c r="D13">
+        <v>8.942460382982269</v>
+      </c>
+      <c r="E13">
+        <v>0.9184200000000001</v>
+      </c>
+      <c r="F13">
+        <v>1.08042</v>
+      </c>
+      <c r="G13">
+        <v>1.23</v>
+      </c>
+      <c r="H13">
+        <v>9.66</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.92</v>
+      </c>
+      <c r="K13">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.699</v>
+      </c>
+      <c r="M13">
+        <v>0.04829477400000001</v>
+      </c>
+      <c r="N13">
+        <v>0.6507052259999999</v>
+      </c>
+      <c r="O13">
+        <v>0.1626763065</v>
+      </c>
+      <c r="P13">
+        <v>0.4880289194999999</v>
+      </c>
+      <c r="Q13">
+        <v>0.7090289195</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.121483570793476</v>
+      </c>
+      <c r="T13">
+        <v>0.7393371707977725</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.47361571668189</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1115662047979514</v>
+      </c>
+      <c r="C14">
+        <v>9.023551062374393</v>
+      </c>
+      <c r="D14">
+        <v>8.972191062374392</v>
+      </c>
+      <c r="E14">
+        <v>1.01664</v>
+      </c>
+      <c r="F14">
+        <v>1.17864</v>
+      </c>
+      <c r="G14">
+        <v>1.23</v>
+      </c>
+      <c r="H14">
+        <v>9.66</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.92</v>
+      </c>
+      <c r="K14">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L14">
+        <v>0.699</v>
+      </c>
+      <c r="M14">
+        <v>0.05268520800000001</v>
+      </c>
+      <c r="N14">
+        <v>0.646314792</v>
+      </c>
+      <c r="O14">
+        <v>0.161578698</v>
+      </c>
+      <c r="P14">
+        <v>0.484736094</v>
+      </c>
+      <c r="Q14">
+        <v>0.705736094</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1222081872703994</v>
+      </c>
+      <c r="T14">
+        <v>0.7458165220258436</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.033525</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.26748107362507</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1114315315897093</v>
+      </c>
+      <c r="C15">
+        <v>8.941967277099387</v>
+      </c>
+      <c r="D15">
+        <v>8.988827277099386</v>
+      </c>
+      <c r="E15">
+        <v>1.11486</v>
+      </c>
+      <c r="F15">
+        <v>1.27686</v>
+      </c>
+      <c r="G15">
+        <v>1.23</v>
+      </c>
+      <c r="H15">
+        <v>9.66</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.92</v>
+      </c>
+      <c r="K15">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L15">
+        <v>0.699</v>
+      </c>
+      <c r="M15">
+        <v>0.058480188</v>
+      </c>
+      <c r="N15">
+        <v>0.640519812</v>
+      </c>
+      <c r="O15">
+        <v>0.160129953</v>
+      </c>
+      <c r="P15">
+        <v>0.480389859</v>
+      </c>
+      <c r="Q15">
+        <v>0.7013898590000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.122949461597367</v>
+      </c>
+      <c r="T15">
+        <v>0.7524448238568588</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.03435</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>11.9527659521204</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1111978583814671</v>
+      </c>
+      <c r="C16">
+        <v>8.872759849503213</v>
+      </c>
+      <c r="D16">
+        <v>9.017839849503213</v>
+      </c>
+      <c r="E16">
+        <v>1.21308</v>
+      </c>
+      <c r="F16">
+        <v>1.37508</v>
+      </c>
+      <c r="G16">
+        <v>1.23</v>
+      </c>
+      <c r="H16">
+        <v>9.66</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.92</v>
+      </c>
+      <c r="K16">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L16">
+        <v>0.699</v>
+      </c>
+      <c r="M16">
+        <v>0.06297866400000002</v>
+      </c>
+      <c r="N16">
+        <v>0.636021336</v>
+      </c>
+      <c r="O16">
+        <v>0.159005334</v>
+      </c>
+      <c r="P16">
+        <v>0.477016002</v>
+      </c>
+      <c r="Q16">
+        <v>0.6980160020000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1237079748621711</v>
+      </c>
+      <c r="T16">
+        <v>0.7592272722420839</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.03435</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.09899695554037</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.110964185173225</v>
+      </c>
+      <c r="C17">
+        <v>8.80374031180995</v>
+      </c>
+      <c r="D17">
+        <v>9.047040311809949</v>
+      </c>
+      <c r="E17">
+        <v>1.3113</v>
+      </c>
+      <c r="F17">
+        <v>1.4733</v>
+      </c>
+      <c r="G17">
+        <v>1.23</v>
+      </c>
+      <c r="H17">
+        <v>9.66</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.92</v>
+      </c>
+      <c r="K17">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L17">
+        <v>0.699</v>
+      </c>
+      <c r="M17">
+        <v>0.06747714</v>
+      </c>
+      <c r="N17">
+        <v>0.6315228599999999</v>
+      </c>
+      <c r="O17">
+        <v>0.157880715</v>
+      </c>
+      <c r="P17">
+        <v>0.4736421449999999</v>
+      </c>
+      <c r="Q17">
+        <v>0.694642145</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1244843354979118</v>
+      </c>
+      <c r="T17">
+        <v>0.7661693076481376</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.03435</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.35906382517101</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1109945119649829</v>
+      </c>
+      <c r="C18">
+        <v>8.701719916183004</v>
+      </c>
+      <c r="D18">
+        <v>9.043239916183003</v>
+      </c>
+      <c r="E18">
+        <v>1.40952</v>
+      </c>
+      <c r="F18">
+        <v>1.57152</v>
+      </c>
+      <c r="G18">
+        <v>1.23</v>
+      </c>
+      <c r="H18">
+        <v>9.66</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.92</v>
+      </c>
+      <c r="K18">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L18">
+        <v>0.699</v>
+      </c>
+      <c r="M18">
+        <v>0.07543296000000001</v>
+      </c>
+      <c r="N18">
+        <v>0.62356704</v>
+      </c>
+      <c r="O18">
+        <v>0.15589176</v>
+      </c>
+      <c r="P18">
+        <v>0.46767528</v>
+      </c>
+      <c r="Q18">
+        <v>0.68867528</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1252791809106939</v>
+      </c>
+      <c r="T18">
+        <v>0.7732766296114784</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.036</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>9.266506312360006</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1107773387567408</v>
+      </c>
+      <c r="C19">
+        <v>8.630785579412899</v>
+      </c>
+      <c r="D19">
+        <v>9.0705255794129</v>
+      </c>
+      <c r="E19">
+        <v>1.50774</v>
+      </c>
+      <c r="F19">
+        <v>1.66974</v>
+      </c>
+      <c r="G19">
+        <v>1.23</v>
+      </c>
+      <c r="H19">
+        <v>9.66</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.92</v>
+      </c>
+      <c r="K19">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L19">
+        <v>0.699</v>
+      </c>
+      <c r="M19">
+        <v>0.08014752000000001</v>
+      </c>
+      <c r="N19">
+        <v>0.6188524799999999</v>
+      </c>
+      <c r="O19">
+        <v>0.15471312</v>
+      </c>
+      <c r="P19">
+        <v>0.4641393599999999</v>
+      </c>
+      <c r="Q19">
+        <v>0.68513936</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1260931792249889</v>
+      </c>
+      <c r="T19">
+        <v>0.7805552123450203</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.036</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.721417705750593</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1105601655484986</v>
+      </c>
+      <c r="C20">
+        <v>8.560016395969232</v>
+      </c>
+      <c r="D20">
+        <v>9.097976395969232</v>
+      </c>
+      <c r="E20">
+        <v>1.60596</v>
+      </c>
+      <c r="F20">
+        <v>1.76796</v>
+      </c>
+      <c r="G20">
+        <v>1.23</v>
+      </c>
+      <c r="H20">
+        <v>9.66</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.92</v>
+      </c>
+      <c r="K20">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L20">
+        <v>0.699</v>
+      </c>
+      <c r="M20">
+        <v>0.08486208000000001</v>
+      </c>
+      <c r="N20">
+        <v>0.6141379199999999</v>
+      </c>
+      <c r="O20">
+        <v>0.15353448</v>
+      </c>
+      <c r="P20">
+        <v>0.4606034399999999</v>
+      </c>
+      <c r="Q20">
+        <v>0.6816034399999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1269270311567056</v>
+      </c>
+      <c r="T20">
+        <v>0.7880113214866972</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.036</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.236894499875561</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1103429923402565</v>
+      </c>
+      <c r="C21">
+        <v>8.489413869851603</v>
+      </c>
+      <c r="D21">
+        <v>9.125593869851603</v>
+      </c>
+      <c r="E21">
+        <v>1.70418</v>
+      </c>
+      <c r="F21">
+        <v>1.86618</v>
+      </c>
+      <c r="G21">
+        <v>1.23</v>
+      </c>
+      <c r="H21">
+        <v>9.66</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.92</v>
+      </c>
+      <c r="K21">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L21">
+        <v>0.699</v>
+      </c>
+      <c r="M21">
+        <v>0.08957664000000001</v>
+      </c>
+      <c r="N21">
+        <v>0.60942336</v>
+      </c>
+      <c r="O21">
+        <v>0.15235584</v>
+      </c>
+      <c r="P21">
+        <v>0.4570675199999999</v>
+      </c>
+      <c r="Q21">
+        <v>0.67806752</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.127781472025008</v>
+      </c>
+      <c r="T21">
+        <v>0.7956515320886626</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.036</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.803373736724216</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1103508191320143</v>
+      </c>
+      <c r="C22">
+        <v>8.390195640568521</v>
+      </c>
+      <c r="D22">
+        <v>9.12459564056852</v>
+      </c>
+      <c r="E22">
+        <v>1.8024</v>
+      </c>
+      <c r="F22">
+        <v>1.9644</v>
+      </c>
+      <c r="G22">
+        <v>1.23</v>
+      </c>
+      <c r="H22">
+        <v>9.66</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.92</v>
+      </c>
+      <c r="K22">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L22">
+        <v>0.699</v>
+      </c>
+      <c r="M22">
+        <v>0.09723780000000003</v>
+      </c>
+      <c r="N22">
+        <v>0.6017621999999999</v>
+      </c>
+      <c r="O22">
+        <v>0.15044055</v>
+      </c>
+      <c r="P22">
+        <v>0.4513216499999999</v>
+      </c>
+      <c r="Q22">
+        <v>0.67232165</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1286572739150179</v>
+      </c>
+      <c r="T22">
+        <v>0.8034827479556769</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.188562472618671</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1101448959237721</v>
+      </c>
+      <c r="C23">
+        <v>8.318312016617424</v>
+      </c>
+      <c r="D23">
+        <v>9.150932016617425</v>
+      </c>
+      <c r="E23">
+        <v>1.90062</v>
+      </c>
+      <c r="F23">
+        <v>2.06262</v>
+      </c>
+      <c r="G23">
+        <v>1.23</v>
+      </c>
+      <c r="H23">
+        <v>9.66</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.92</v>
+      </c>
+      <c r="K23">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L23">
+        <v>0.699</v>
+      </c>
+      <c r="M23">
+        <v>0.10209969</v>
+      </c>
+      <c r="N23">
+        <v>0.5969003099999999</v>
+      </c>
+      <c r="O23">
+        <v>0.1492250775</v>
+      </c>
+      <c r="P23">
+        <v>0.4476752324999999</v>
+      </c>
+      <c r="Q23">
+        <v>0.6686752325</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1295552480047749</v>
+      </c>
+      <c r="T23">
+        <v>0.8115122224522359</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.846249973922544</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.10993897271553</v>
+      </c>
+      <c r="C24">
+        <v>8.246580862426356</v>
+      </c>
+      <c r="D24">
+        <v>9.177420862426356</v>
+      </c>
+      <c r="E24">
+        <v>1.99884</v>
+      </c>
+      <c r="F24">
+        <v>2.16084</v>
+      </c>
+      <c r="G24">
+        <v>1.23</v>
+      </c>
+      <c r="H24">
+        <v>9.66</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.92</v>
+      </c>
+      <c r="K24">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.699</v>
+      </c>
+      <c r="M24">
+        <v>0.10696158</v>
+      </c>
+      <c r="N24">
+        <v>0.59203842</v>
+      </c>
+      <c r="O24">
+        <v>0.148009605</v>
+      </c>
+      <c r="P24">
+        <v>0.444028815</v>
+      </c>
+      <c r="Q24">
+        <v>0.6650288150000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1304762470711923</v>
+      </c>
+      <c r="T24">
+        <v>0.8197475809102451</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.535056793289701</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1097330495072879</v>
+      </c>
+      <c r="C25">
+        <v>8.175003505883904</v>
+      </c>
+      <c r="D25">
+        <v>9.204063505883903</v>
+      </c>
+      <c r="E25">
+        <v>2.09706</v>
+      </c>
+      <c r="F25">
+        <v>2.25906</v>
+      </c>
+      <c r="G25">
+        <v>1.23</v>
+      </c>
+      <c r="H25">
+        <v>9.66</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.92</v>
+      </c>
+      <c r="K25">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L25">
+        <v>0.699</v>
+      </c>
+      <c r="M25">
+        <v>0.11182347</v>
+      </c>
+      <c r="N25">
+        <v>0.5871765299999999</v>
+      </c>
+      <c r="O25">
+        <v>0.1467941325</v>
+      </c>
+      <c r="P25">
+        <v>0.4403823975</v>
+      </c>
+      <c r="Q25">
+        <v>0.6613823975000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.131421168191283</v>
+      </c>
+      <c r="T25">
+        <v>0.8281968447827482</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.250923889233627</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1097791262990457</v>
+      </c>
+      <c r="C26">
+        <v>8.070808598335734</v>
+      </c>
+      <c r="D26">
+        <v>9.198088598335735</v>
+      </c>
+      <c r="E26">
+        <v>2.19528</v>
+      </c>
+      <c r="F26">
+        <v>2.35728</v>
+      </c>
+      <c r="G26">
+        <v>1.23</v>
+      </c>
+      <c r="H26">
+        <v>9.66</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.92</v>
+      </c>
+      <c r="K26">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L26">
+        <v>0.699</v>
+      </c>
+      <c r="M26">
+        <v>0.119985552</v>
+      </c>
+      <c r="N26">
+        <v>0.5790144479999999</v>
+      </c>
+      <c r="O26">
+        <v>0.144753612</v>
+      </c>
+      <c r="P26">
+        <v>0.4342608359999999</v>
+      </c>
+      <c r="Q26">
+        <v>0.6552608360000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1323909556566391</v>
+      </c>
+      <c r="T26">
+        <v>0.8368684577045277</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.038175</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.825701414450299</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1095837030908036</v>
+      </c>
+      <c r="C27">
+        <v>7.9979831440446</v>
+      </c>
+      <c r="D27">
+        <v>9.2234831440446</v>
+      </c>
+      <c r="E27">
+        <v>2.2935</v>
+      </c>
+      <c r="F27">
+        <v>2.4555</v>
+      </c>
+      <c r="G27">
+        <v>1.23</v>
+      </c>
+      <c r="H27">
+        <v>9.66</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.92</v>
+      </c>
+      <c r="K27">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L27">
+        <v>0.699</v>
+      </c>
+      <c r="M27">
+        <v>0.12498495</v>
+      </c>
+      <c r="N27">
+        <v>0.57401505</v>
+      </c>
+      <c r="O27">
+        <v>0.1435037625</v>
+      </c>
+      <c r="P27">
+        <v>0.4305112875</v>
+      </c>
+      <c r="Q27">
+        <v>0.6515112875000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1333866041210715</v>
+      </c>
+      <c r="T27">
+        <v>0.8457713136375545</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.038175</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.592673357872287</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1093882798825615</v>
+      </c>
+      <c r="C28">
+        <v>7.92529829903315</v>
+      </c>
+      <c r="D28">
+        <v>9.24901829903315</v>
+      </c>
+      <c r="E28">
+        <v>2.39172</v>
+      </c>
+      <c r="F28">
+        <v>2.55372</v>
+      </c>
+      <c r="G28">
+        <v>1.23</v>
+      </c>
+      <c r="H28">
+        <v>9.66</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.92</v>
+      </c>
+      <c r="K28">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L28">
+        <v>0.699</v>
+      </c>
+      <c r="M28">
+        <v>0.129984348</v>
+      </c>
+      <c r="N28">
+        <v>0.5690156519999999</v>
+      </c>
+      <c r="O28">
+        <v>0.142253913</v>
+      </c>
+      <c r="P28">
+        <v>0.4267617389999999</v>
+      </c>
+      <c r="Q28">
+        <v>0.647761739</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1344091620034614</v>
+      </c>
+      <c r="T28">
+        <v>0.8549147872985011</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.038175</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.377570536415661</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1091928566743193</v>
+      </c>
+      <c r="C29">
+        <v>7.852755234371206</v>
+      </c>
+      <c r="D29">
+        <v>9.274695234371206</v>
+      </c>
+      <c r="E29">
+        <v>2.489940000000001</v>
+      </c>
+      <c r="F29">
+        <v>2.651940000000001</v>
+      </c>
+      <c r="G29">
+        <v>1.23</v>
+      </c>
+      <c r="H29">
+        <v>9.66</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.92</v>
+      </c>
+      <c r="K29">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L29">
+        <v>0.699</v>
+      </c>
+      <c r="M29">
+        <v>0.134983746</v>
+      </c>
+      <c r="N29">
+        <v>0.5640162539999999</v>
+      </c>
+      <c r="O29">
+        <v>0.1410040635</v>
+      </c>
+      <c r="P29">
+        <v>0.4230121904999999</v>
+      </c>
+      <c r="Q29">
+        <v>0.6440121905</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1354597351703004</v>
+      </c>
+      <c r="T29">
+        <v>0.8643087670871449</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.038175</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.178401257289154</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1089974334660772</v>
+      </c>
+      <c r="C30">
+        <v>7.780355134169175</v>
+      </c>
+      <c r="D30">
+        <v>9.300515134169176</v>
+      </c>
+      <c r="E30">
+        <v>2.588160000000001</v>
+      </c>
+      <c r="F30">
+        <v>2.750160000000001</v>
+      </c>
+      <c r="G30">
+        <v>1.23</v>
+      </c>
+      <c r="H30">
+        <v>9.66</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.92</v>
+      </c>
+      <c r="K30">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L30">
+        <v>0.699</v>
+      </c>
+      <c r="M30">
+        <v>0.139983144</v>
+      </c>
+      <c r="N30">
+        <v>0.559016856</v>
+      </c>
+      <c r="O30">
+        <v>0.139754214</v>
+      </c>
+      <c r="P30">
+        <v>0.419262642</v>
+      </c>
+      <c r="Q30">
+        <v>0.640262642</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1365394909251072</v>
+      </c>
+      <c r="T30">
+        <v>0.8739636907588064</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.038175</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.993458355243113</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.108802010257835</v>
+      </c>
+      <c r="C31">
+        <v>7.708099195760118</v>
+      </c>
+      <c r="D31">
+        <v>9.326479195760118</v>
+      </c>
+      <c r="E31">
+        <v>2.68638</v>
+      </c>
+      <c r="F31">
+        <v>2.84838</v>
+      </c>
+      <c r="G31">
+        <v>1.23</v>
+      </c>
+      <c r="H31">
+        <v>9.66</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.92</v>
+      </c>
+      <c r="K31">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L31">
+        <v>0.699</v>
+      </c>
+      <c r="M31">
+        <v>0.144982542</v>
+      </c>
+      <c r="N31">
+        <v>0.5540174579999999</v>
+      </c>
+      <c r="O31">
+        <v>0.1385043645</v>
+      </c>
+      <c r="P31">
+        <v>0.4155130934999999</v>
+      </c>
+      <c r="Q31">
+        <v>0.6365130935000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1376496623349789</v>
+      </c>
+      <c r="T31">
+        <v>0.8838905841113598</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.038175</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.821270136096799</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1086065870495929</v>
+      </c>
+      <c r="C32">
+        <v>7.635988629884784</v>
+      </c>
+      <c r="D32">
+        <v>9.352588629884783</v>
+      </c>
+      <c r="E32">
+        <v>2.7846</v>
+      </c>
+      <c r="F32">
+        <v>2.9466</v>
+      </c>
+      <c r="G32">
+        <v>1.23</v>
+      </c>
+      <c r="H32">
+        <v>9.66</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.92</v>
+      </c>
+      <c r="K32">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L32">
+        <v>0.699</v>
+      </c>
+      <c r="M32">
+        <v>0.14998194</v>
+      </c>
+      <c r="N32">
+        <v>0.54901806</v>
+      </c>
+      <c r="O32">
+        <v>0.137254515</v>
+      </c>
+      <c r="P32">
+        <v>0.411763545</v>
+      </c>
+      <c r="Q32">
+        <v>0.6327635450000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1387915529279898</v>
+      </c>
+      <c r="T32">
+        <v>0.8941011029882719</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.038175</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.66056113156024</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1084111638413507</v>
+      </c>
+      <c r="C33">
+        <v>7.564024660879848</v>
+      </c>
+      <c r="D33">
+        <v>9.378844660879848</v>
+      </c>
+      <c r="E33">
+        <v>2.88282</v>
+      </c>
+      <c r="F33">
+        <v>3.04482</v>
+      </c>
+      <c r="G33">
+        <v>1.23</v>
+      </c>
+      <c r="H33">
+        <v>9.66</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.92</v>
+      </c>
+      <c r="K33">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L33">
+        <v>0.699</v>
+      </c>
+      <c r="M33">
+        <v>0.154981338</v>
+      </c>
+      <c r="N33">
+        <v>0.5440186619999999</v>
+      </c>
+      <c r="O33">
+        <v>0.1360046655</v>
+      </c>
+      <c r="P33">
+        <v>0.4080139964999999</v>
+      </c>
+      <c r="Q33">
+        <v>0.6290139965</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.139966541799059</v>
+      </c>
+      <c r="T33">
+        <v>0.9046075789340801</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.038175</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.510220449897005</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1088397406331086</v>
+      </c>
+      <c r="C34">
+        <v>7.408415025812364</v>
+      </c>
+      <c r="D34">
+        <v>9.321455025812364</v>
+      </c>
+      <c r="E34">
+        <v>2.981040000000001</v>
+      </c>
+      <c r="F34">
+        <v>3.143040000000001</v>
+      </c>
+      <c r="G34">
+        <v>1.23</v>
+      </c>
+      <c r="H34">
+        <v>9.66</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.92</v>
+      </c>
+      <c r="K34">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L34">
+        <v>0.699</v>
+      </c>
+      <c r="M34">
+        <v>0.16815264</v>
+      </c>
+      <c r="N34">
+        <v>0.5308473599999999</v>
+      </c>
+      <c r="O34">
+        <v>0.13271184</v>
+      </c>
+      <c r="P34">
+        <v>0.3981355199999999</v>
+      </c>
+      <c r="Q34">
+        <v>0.6191355199999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1411760891663362</v>
+      </c>
+      <c r="T34">
+        <v>0.9154230688782944</v>
+      </c>
+      <c r="U34">
+        <v>0.0535</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.040125</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.156937411152152</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1086638174248664</v>
+      </c>
+      <c r="C35">
+        <v>7.333667265579244</v>
+      </c>
+      <c r="D35">
+        <v>9.344927265579244</v>
+      </c>
+      <c r="E35">
+        <v>3.079260000000001</v>
+      </c>
+      <c r="F35">
+        <v>3.24126</v>
+      </c>
+      <c r="G35">
+        <v>1.23</v>
+      </c>
+      <c r="H35">
+        <v>9.66</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.92</v>
+      </c>
+      <c r="K35">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L35">
+        <v>0.699</v>
+      </c>
+      <c r="M35">
+        <v>0.17340741</v>
+      </c>
+      <c r="N35">
+        <v>0.5255925899999999</v>
+      </c>
+      <c r="O35">
+        <v>0.1313981475</v>
+      </c>
+      <c r="P35">
+        <v>0.3941944424999999</v>
+      </c>
+      <c r="Q35">
+        <v>0.6151944425</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1424217424251738</v>
+      </c>
+      <c r="T35">
+        <v>0.9265614092686046</v>
+      </c>
+      <c r="U35">
+        <v>0.0535</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.040125</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.030969610814209</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1091763942166243</v>
+      </c>
+      <c r="C36">
+        <v>7.167384772603869</v>
+      </c>
+      <c r="D36">
+        <v>9.276864772603869</v>
+      </c>
+      <c r="E36">
+        <v>3.177480000000001</v>
+      </c>
+      <c r="F36">
+        <v>3.33948</v>
+      </c>
+      <c r="G36">
+        <v>1.23</v>
+      </c>
+      <c r="H36">
+        <v>9.66</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.92</v>
+      </c>
+      <c r="K36">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L36">
+        <v>0.699</v>
+      </c>
+      <c r="M36">
+        <v>0.187678776</v>
+      </c>
+      <c r="N36">
+        <v>0.5113212239999999</v>
+      </c>
+      <c r="O36">
+        <v>0.127830306</v>
+      </c>
+      <c r="P36">
+        <v>0.3834909179999999</v>
+      </c>
+      <c r="Q36">
+        <v>0.604490918</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1437051427524611</v>
+      </c>
+      <c r="T36">
+        <v>0.9380372751252879</v>
+      </c>
+      <c r="U36">
+        <v>0.0562</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.04215</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.724448842313421</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1090207210083822</v>
+      </c>
+      <c r="C37">
+        <v>7.089730771939125</v>
+      </c>
+      <c r="D37">
+        <v>9.297430771939126</v>
+      </c>
+      <c r="E37">
+        <v>3.275700000000001</v>
+      </c>
+      <c r="F37">
+        <v>3.437700000000001</v>
+      </c>
+      <c r="G37">
+        <v>1.23</v>
+      </c>
+      <c r="H37">
+        <v>9.66</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.92</v>
+      </c>
+      <c r="K37">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L37">
+        <v>0.699</v>
+      </c>
+      <c r="M37">
+        <v>0.19319874</v>
+      </c>
+      <c r="N37">
+        <v>0.5058012599999999</v>
+      </c>
+      <c r="O37">
+        <v>0.126450315</v>
+      </c>
+      <c r="P37">
+        <v>0.3793509449999999</v>
+      </c>
+      <c r="Q37">
+        <v>0.600350945</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1450280323205879</v>
+      </c>
+      <c r="T37">
+        <v>0.9498662445467921</v>
+      </c>
+      <c r="U37">
+        <v>0.0562</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.04215</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.618036018247323</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.10886504780014</v>
+      </c>
+      <c r="C38">
+        <v>7.012168159925293</v>
+      </c>
+      <c r="D38">
+        <v>9.318088159925294</v>
+      </c>
+      <c r="E38">
+        <v>3.37392</v>
+      </c>
+      <c r="F38">
+        <v>3.53592</v>
+      </c>
+      <c r="G38">
+        <v>1.23</v>
+      </c>
+      <c r="H38">
+        <v>9.66</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.92</v>
+      </c>
+      <c r="K38">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L38">
+        <v>0.699</v>
+      </c>
+      <c r="M38">
+        <v>0.198718704</v>
+      </c>
+      <c r="N38">
+        <v>0.5002812959999999</v>
+      </c>
+      <c r="O38">
+        <v>0.125070324</v>
+      </c>
+      <c r="P38">
+        <v>0.375210972</v>
+      </c>
+      <c r="Q38">
+        <v>0.5962109720000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1463922621877188</v>
+      </c>
+      <c r="T38">
+        <v>0.9620648692627183</v>
+      </c>
+      <c r="U38">
+        <v>0.0562</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.04215</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.517535017740453</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1100136245918979</v>
+      </c>
+      <c r="C39">
+        <v>6.763660348212625</v>
+      </c>
+      <c r="D39">
+        <v>9.167800348212625</v>
+      </c>
+      <c r="E39">
+        <v>3.47214</v>
+      </c>
+      <c r="F39">
+        <v>3.63414</v>
+      </c>
+      <c r="G39">
+        <v>1.23</v>
+      </c>
+      <c r="H39">
+        <v>9.66</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.92</v>
+      </c>
+      <c r="K39">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L39">
+        <v>0.699</v>
+      </c>
+      <c r="M39">
+        <v>0.221319126</v>
+      </c>
+      <c r="N39">
+        <v>0.4776808739999999</v>
+      </c>
+      <c r="O39">
+        <v>0.1194202185</v>
+      </c>
+      <c r="P39">
+        <v>0.3582606555</v>
+      </c>
+      <c r="Q39">
+        <v>0.5792606555000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1477998009395204</v>
+      </c>
+      <c r="T39">
+        <v>0.9746507519061343</v>
+      </c>
+      <c r="U39">
+        <v>0.0609</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.045675</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.158335262899962</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1098932013836557</v>
+      </c>
+      <c r="C40">
+        <v>6.680969483333403</v>
+      </c>
+      <c r="D40">
+        <v>9.183329483333402</v>
+      </c>
+      <c r="E40">
+        <v>3.57036</v>
+      </c>
+      <c r="F40">
+        <v>3.73236</v>
+      </c>
+      <c r="G40">
+        <v>1.23</v>
+      </c>
+      <c r="H40">
+        <v>9.66</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.92</v>
+      </c>
+      <c r="K40">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L40">
+        <v>0.699</v>
+      </c>
+      <c r="M40">
+        <v>0.227300724</v>
+      </c>
+      <c r="N40">
+        <v>0.4716992759999999</v>
+      </c>
+      <c r="O40">
+        <v>0.117924819</v>
+      </c>
+      <c r="P40">
+        <v>0.353774457</v>
+      </c>
+      <c r="Q40">
+        <v>0.5747744570000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1492527441671866</v>
+      </c>
+      <c r="T40">
+        <v>0.9876426307638541</v>
+      </c>
+      <c r="U40">
+        <v>0.0609</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.045675</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.075221177034174</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1124930281754136</v>
+      </c>
+      <c r="C41">
+        <v>6.258769500159421</v>
+      </c>
+      <c r="D41">
+        <v>8.859349500159421</v>
+      </c>
+      <c r="E41">
+        <v>3.66858</v>
+      </c>
+      <c r="F41">
+        <v>3.83058</v>
+      </c>
+      <c r="G41">
+        <v>1.23</v>
+      </c>
+      <c r="H41">
+        <v>9.66</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.92</v>
+      </c>
+      <c r="K41">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L41">
+        <v>0.699</v>
+      </c>
+      <c r="M41">
+        <v>0.268906716</v>
+      </c>
+      <c r="N41">
+        <v>0.430093284</v>
+      </c>
+      <c r="O41">
+        <v>0.107523321</v>
+      </c>
+      <c r="P41">
+        <v>0.322569963</v>
+      </c>
+      <c r="Q41">
+        <v>0.543569963</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1507533248777272</v>
+      </c>
+      <c r="T41">
+        <v>1.001060472862811</v>
+      </c>
+      <c r="U41">
+        <v>0.0702</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.05265</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.599414437830553</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1124423549671714</v>
+      </c>
+      <c r="C42">
+        <v>6.166645606976099</v>
+      </c>
+      <c r="D42">
+        <v>8.865445606976099</v>
+      </c>
+      <c r="E42">
+        <v>3.766800000000001</v>
+      </c>
+      <c r="F42">
+        <v>3.928800000000001</v>
+      </c>
+      <c r="G42">
+        <v>1.23</v>
+      </c>
+      <c r="H42">
+        <v>9.66</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.92</v>
+      </c>
+      <c r="K42">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L42">
+        <v>0.699</v>
+      </c>
+      <c r="M42">
+        <v>0.2758017600000001</v>
+      </c>
+      <c r="N42">
+        <v>0.4231982399999999</v>
+      </c>
+      <c r="O42">
+        <v>0.10579956</v>
+      </c>
+      <c r="P42">
+        <v>0.3173986799999999</v>
+      </c>
+      <c r="Q42">
+        <v>0.53839868</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1523039249452857</v>
+      </c>
+      <c r="T42">
+        <v>1.014925576365066</v>
+      </c>
+      <c r="U42">
+        <v>0.0702</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.05265</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.534429076884788</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1138369317589293</v>
+      </c>
+      <c r="C43">
+        <v>5.903659479120542</v>
+      </c>
+      <c r="D43">
+        <v>8.700679479120542</v>
+      </c>
+      <c r="E43">
+        <v>3.86502</v>
+      </c>
+      <c r="F43">
+        <v>4.02702</v>
+      </c>
+      <c r="G43">
+        <v>1.23</v>
+      </c>
+      <c r="H43">
+        <v>9.66</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.92</v>
+      </c>
+      <c r="K43">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L43">
+        <v>0.699</v>
+      </c>
+      <c r="M43">
+        <v>0.301623798</v>
+      </c>
+      <c r="N43">
+        <v>0.397376202</v>
+      </c>
+      <c r="O43">
+        <v>0.09934405049999999</v>
+      </c>
+      <c r="P43">
+        <v>0.2980321515</v>
+      </c>
+      <c r="Q43">
+        <v>0.5190321515</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1539070877269988</v>
+      </c>
+      <c r="T43">
+        <v>1.029260683375872</v>
+      </c>
+      <c r="U43">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.056175</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.317456396461131</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1138215085506872</v>
+      </c>
+      <c r="C44">
+        <v>5.80722819803658</v>
+      </c>
+      <c r="D44">
+        <v>8.702468198036581</v>
+      </c>
+      <c r="E44">
+        <v>3.963240000000001</v>
+      </c>
+      <c r="F44">
+        <v>4.125240000000001</v>
+      </c>
+      <c r="G44">
+        <v>1.23</v>
+      </c>
+      <c r="H44">
+        <v>9.66</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.92</v>
+      </c>
+      <c r="K44">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L44">
+        <v>0.699</v>
+      </c>
+      <c r="M44">
+        <v>0.308980476</v>
+      </c>
+      <c r="N44">
+        <v>0.390019524</v>
+      </c>
+      <c r="O44">
+        <v>0.09750488099999999</v>
+      </c>
+      <c r="P44">
+        <v>0.292514643</v>
+      </c>
+      <c r="Q44">
+        <v>0.513514643</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1555655319839434</v>
+      </c>
+      <c r="T44">
+        <v>1.044090104421533</v>
+      </c>
+      <c r="U44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.056175</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.262278863212056</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.113806085342445</v>
+      </c>
+      <c r="C45">
+        <v>5.710797652567186</v>
+      </c>
+      <c r="D45">
+        <v>8.704257652567186</v>
+      </c>
+      <c r="E45">
+        <v>4.06146</v>
+      </c>
+      <c r="F45">
+        <v>4.22346</v>
+      </c>
+      <c r="G45">
+        <v>1.23</v>
+      </c>
+      <c r="H45">
+        <v>9.66</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.92</v>
+      </c>
+      <c r="K45">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L45">
+        <v>0.699</v>
+      </c>
+      <c r="M45">
+        <v>0.316337154</v>
+      </c>
+      <c r="N45">
+        <v>0.3826628459999999</v>
+      </c>
+      <c r="O45">
+        <v>0.09566571149999999</v>
+      </c>
+      <c r="P45">
+        <v>0.2869971345</v>
+      </c>
+      <c r="Q45">
+        <v>0.5079971345000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1572821672674474</v>
+      </c>
+      <c r="T45">
+        <v>1.0594398560302</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.056175</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.209667726858287</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1137906621342029</v>
+      </c>
+      <c r="C46">
+        <v>5.614367843166233</v>
+      </c>
+      <c r="D46">
+        <v>8.706047843166234</v>
+      </c>
+      <c r="E46">
+        <v>4.159680000000001</v>
+      </c>
+      <c r="F46">
+        <v>4.321680000000001</v>
+      </c>
+      <c r="G46">
+        <v>1.23</v>
+      </c>
+      <c r="H46">
+        <v>9.66</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.92</v>
+      </c>
+      <c r="K46">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L46">
+        <v>0.699</v>
+      </c>
+      <c r="M46">
+        <v>0.323693832</v>
+      </c>
+      <c r="N46">
+        <v>0.3753061679999999</v>
+      </c>
+      <c r="O46">
+        <v>0.09382654199999999</v>
+      </c>
+      <c r="P46">
+        <v>0.281479626</v>
+      </c>
+      <c r="Q46">
+        <v>0.5024796260000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1590601109539337</v>
+      </c>
+      <c r="T46">
+        <v>1.075337813053462</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.056175</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.159448005793326</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1137752389259607</v>
+      </c>
+      <c r="C47">
+        <v>5.517938770287969</v>
+      </c>
+      <c r="D47">
+        <v>8.707838770287969</v>
+      </c>
+      <c r="E47">
+        <v>4.2579</v>
+      </c>
+      <c r="F47">
+        <v>4.4199</v>
+      </c>
+      <c r="G47">
+        <v>1.23</v>
+      </c>
+      <c r="H47">
+        <v>9.66</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.92</v>
+      </c>
+      <c r="K47">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L47">
+        <v>0.699</v>
+      </c>
+      <c r="M47">
+        <v>0.33105051</v>
+      </c>
+      <c r="N47">
+        <v>0.36794949</v>
+      </c>
+      <c r="O47">
+        <v>0.0919873725</v>
+      </c>
+      <c r="P47">
+        <v>0.2759621175</v>
+      </c>
+      <c r="Q47">
+        <v>0.4969621175000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1609027071381104</v>
+      </c>
+      <c r="T47">
+        <v>1.091813877604843</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.056175</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.111460272331253</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1137598157177186</v>
+      </c>
+      <c r="C48">
+        <v>5.421510434387023</v>
+      </c>
+      <c r="D48">
+        <v>8.709630434387023</v>
+      </c>
+      <c r="E48">
+        <v>4.356120000000001</v>
+      </c>
+      <c r="F48">
+        <v>4.518120000000001</v>
+      </c>
+      <c r="G48">
+        <v>1.23</v>
+      </c>
+      <c r="H48">
+        <v>9.66</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.92</v>
+      </c>
+      <c r="K48">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L48">
+        <v>0.699</v>
+      </c>
+      <c r="M48">
+        <v>0.338407188</v>
+      </c>
+      <c r="N48">
+        <v>0.3605928119999999</v>
+      </c>
+      <c r="O48">
+        <v>0.09014820299999998</v>
+      </c>
+      <c r="P48">
+        <v>0.2704446089999999</v>
+      </c>
+      <c r="Q48">
+        <v>0.491444609</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1628135476254048</v>
+      </c>
+      <c r="T48">
+        <v>1.108900166769238</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.056175</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.065558962063181</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1137443925094764</v>
+      </c>
+      <c r="C49">
+        <v>5.325082835918394</v>
+      </c>
+      <c r="D49">
+        <v>8.711422835918395</v>
+      </c>
+      <c r="E49">
+        <v>4.454340000000001</v>
+      </c>
+      <c r="F49">
+        <v>4.616340000000001</v>
+      </c>
+      <c r="G49">
+        <v>1.23</v>
+      </c>
+      <c r="H49">
+        <v>9.66</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.92</v>
+      </c>
+      <c r="K49">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L49">
+        <v>0.699</v>
+      </c>
+      <c r="M49">
+        <v>0.345763866</v>
+      </c>
+      <c r="N49">
+        <v>0.3532361339999999</v>
+      </c>
+      <c r="O49">
+        <v>0.08830903349999998</v>
+      </c>
+      <c r="P49">
+        <v>0.2649271005</v>
+      </c>
+      <c r="Q49">
+        <v>0.4859271005</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1647964953008989</v>
+      </c>
+      <c r="T49">
+        <v>1.126631221562478</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.056175</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.021610899040561</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1195969693012343</v>
+      </c>
+      <c r="C50">
+        <v>4.595845712954272</v>
+      </c>
+      <c r="D50">
+        <v>8.080405712954272</v>
+      </c>
+      <c r="E50">
+        <v>4.552560000000001</v>
+      </c>
+      <c r="F50">
+        <v>4.714560000000001</v>
+      </c>
+      <c r="G50">
+        <v>1.23</v>
+      </c>
+      <c r="H50">
+        <v>9.66</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.92</v>
+      </c>
+      <c r="K50">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L50">
+        <v>0.699</v>
+      </c>
+      <c r="M50">
+        <v>0.4299678720000001</v>
+      </c>
+      <c r="N50">
+        <v>0.2690321279999999</v>
+      </c>
+      <c r="O50">
+        <v>0.06725803199999997</v>
+      </c>
+      <c r="P50">
+        <v>0.2017740959999999</v>
+      </c>
+      <c r="Q50">
+        <v>0.422774096</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1668557101946813</v>
+      </c>
+      <c r="T50">
+        <v>1.145044240001612</v>
+      </c>
+      <c r="U50">
+        <v>0.0912</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.0684</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.625702861817545</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1197037960929921</v>
+      </c>
+      <c r="C51">
+        <v>4.486956203486207</v>
+      </c>
+      <c r="D51">
+        <v>8.069736203486206</v>
+      </c>
+      <c r="E51">
+        <v>4.65078</v>
+      </c>
+      <c r="F51">
+        <v>4.81278</v>
+      </c>
+      <c r="G51">
+        <v>1.23</v>
+      </c>
+      <c r="H51">
+        <v>9.66</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.92</v>
+      </c>
+      <c r="K51">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L51">
+        <v>0.699</v>
+      </c>
+      <c r="M51">
+        <v>0.438925536</v>
+      </c>
+      <c r="N51">
+        <v>0.2600744639999999</v>
+      </c>
+      <c r="O51">
+        <v>0.06501861599999999</v>
+      </c>
+      <c r="P51">
+        <v>0.195055848</v>
+      </c>
+      <c r="Q51">
+        <v>0.4160558480000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1689956786137101</v>
+      </c>
+      <c r="T51">
+        <v>1.164179337595222</v>
+      </c>
+      <c r="U51">
+        <v>0.0912</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.0684</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.592525252392697</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.11981062288475</v>
+      </c>
+      <c r="C52">
+        <v>4.378094833277545</v>
+      </c>
+      <c r="D52">
+        <v>8.059094833277545</v>
+      </c>
+      <c r="E52">
+        <v>4.749000000000001</v>
+      </c>
+      <c r="F52">
+        <v>4.911</v>
+      </c>
+      <c r="G52">
+        <v>1.23</v>
+      </c>
+      <c r="H52">
+        <v>9.66</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.92</v>
+      </c>
+      <c r="K52">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L52">
+        <v>0.699</v>
+      </c>
+      <c r="M52">
+        <v>0.4478832</v>
+      </c>
+      <c r="N52">
+        <v>0.2511167999999999</v>
+      </c>
+      <c r="O52">
+        <v>0.06277919999999998</v>
+      </c>
+      <c r="P52">
+        <v>0.1883375999999999</v>
+      </c>
+      <c r="Q52">
+        <v>0.4093376</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1712212457695</v>
+      </c>
+      <c r="T52">
+        <v>1.184079839092576</v>
+      </c>
+      <c r="U52">
+        <v>0.0912</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.0684</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.560674747344843</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1199174496765079</v>
+      </c>
+      <c r="C53">
+        <v>4.269261491155168</v>
+      </c>
+      <c r="D53">
+        <v>8.048481491155169</v>
+      </c>
+      <c r="E53">
+        <v>4.847220000000001</v>
+      </c>
+      <c r="F53">
+        <v>5.009220000000001</v>
+      </c>
+      <c r="G53">
+        <v>1.23</v>
+      </c>
+      <c r="H53">
+        <v>9.66</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.92</v>
+      </c>
+      <c r="K53">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L53">
+        <v>0.699</v>
+      </c>
+      <c r="M53">
+        <v>0.4568408640000001</v>
+      </c>
+      <c r="N53">
+        <v>0.2421591359999998</v>
+      </c>
+      <c r="O53">
+        <v>0.06053978399999996</v>
+      </c>
+      <c r="P53">
+        <v>0.1816193519999999</v>
+      </c>
+      <c r="Q53">
+        <v>0.402619352</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1735376524010365</v>
+      </c>
+      <c r="T53">
+        <v>1.20479260595717</v>
+      </c>
+      <c r="U53">
+        <v>0.0912</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.0684</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.53007328171063</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1200242764682657</v>
+      </c>
+      <c r="C54">
+        <v>4.160456066530816</v>
+      </c>
+      <c r="D54">
+        <v>8.037896066530816</v>
+      </c>
+      <c r="E54">
+        <v>4.945440000000001</v>
+      </c>
+      <c r="F54">
+        <v>5.10744</v>
+      </c>
+      <c r="G54">
+        <v>1.23</v>
+      </c>
+      <c r="H54">
+        <v>9.66</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.92</v>
+      </c>
+      <c r="K54">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L54">
+        <v>0.699</v>
+      </c>
+      <c r="M54">
+        <v>0.465798528</v>
+      </c>
+      <c r="N54">
+        <v>0.2332014719999999</v>
+      </c>
+      <c r="O54">
+        <v>0.05830036799999998</v>
+      </c>
+      <c r="P54">
+        <v>0.1749011039999999</v>
+      </c>
+      <c r="Q54">
+        <v>0.395901104</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1759505759755536</v>
+      </c>
+      <c r="T54">
+        <v>1.226368404774454</v>
+      </c>
+      <c r="U54">
+        <v>0.0912</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.0684</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.500648795523888</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1505146269923341</v>
+      </c>
+      <c r="C55">
+        <v>1.868447525650018</v>
+      </c>
+      <c r="D55">
+        <v>5.844107525650019</v>
+      </c>
+      <c r="E55">
+        <v>5.043660000000001</v>
+      </c>
+      <c r="F55">
+        <v>5.205660000000001</v>
+      </c>
+      <c r="G55">
+        <v>1.23</v>
+      </c>
+      <c r="H55">
+        <v>9.66</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.92</v>
+      </c>
+      <c r="K55">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L55">
+        <v>0.699</v>
+      </c>
+      <c r="M55">
+        <v>0.8152063560000002</v>
+      </c>
+      <c r="N55">
+        <v>-0.1162063560000003</v>
+      </c>
+      <c r="O55">
+        <v>-0.02905158900000007</v>
+      </c>
+      <c r="P55">
+        <v>-0.08715476700000022</v>
+      </c>
+      <c r="Q55">
+        <v>0.1338452329999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1815070619405645</v>
+      </c>
+      <c r="T55">
+        <v>1.276053203985773</v>
+      </c>
+      <c r="U55">
+        <v>0.1566</v>
+      </c>
+      <c r="V55">
+        <v>0.2143629017534303</v>
+      </c>
+      <c r="W55">
+        <v>0.1230307695854128</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8574516070137213</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1516926269923341</v>
+      </c>
+      <c r="C56">
+        <v>1.709246052823779</v>
+      </c>
+      <c r="D56">
+        <v>5.783126052823781</v>
+      </c>
+      <c r="E56">
+        <v>5.141880000000001</v>
+      </c>
+      <c r="F56">
+        <v>5.303880000000001</v>
+      </c>
+      <c r="G56">
+        <v>1.23</v>
+      </c>
+      <c r="H56">
+        <v>9.66</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.92</v>
+      </c>
+      <c r="K56">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L56">
+        <v>0.699</v>
+      </c>
+      <c r="M56">
+        <v>0.8305876080000003</v>
+      </c>
+      <c r="N56">
+        <v>-0.1315876080000004</v>
+      </c>
+      <c r="O56">
+        <v>-0.03289690200000009</v>
+      </c>
+      <c r="P56">
+        <v>-0.09869070600000027</v>
+      </c>
+      <c r="Q56">
+        <v>0.1223092939999998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.184609389374055</v>
+      </c>
+      <c r="T56">
+        <v>1.303793491028942</v>
+      </c>
+      <c r="U56">
+        <v>0.1566</v>
+      </c>
+      <c r="V56">
+        <v>0.210393218387626</v>
+      </c>
+      <c r="W56">
+        <v>0.1236524220004978</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8415728735505041</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1528706269923341</v>
+      </c>
+      <c r="C57">
+        <v>1.551304083462778</v>
+      </c>
+      <c r="D57">
+        <v>5.723404083462779</v>
+      </c>
+      <c r="E57">
+        <v>5.240100000000001</v>
+      </c>
+      <c r="F57">
+        <v>5.402100000000001</v>
+      </c>
+      <c r="G57">
+        <v>1.23</v>
+      </c>
+      <c r="H57">
+        <v>9.66</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.92</v>
+      </c>
+      <c r="K57">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L57">
+        <v>0.699</v>
+      </c>
+      <c r="M57">
+        <v>0.8459688600000003</v>
+      </c>
+      <c r="N57">
+        <v>-0.1469688600000003</v>
+      </c>
+      <c r="O57">
+        <v>-0.03674221500000008</v>
+      </c>
+      <c r="P57">
+        <v>-0.1102266450000002</v>
+      </c>
+      <c r="Q57">
+        <v>0.1107733549999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1878495980268118</v>
+      </c>
+      <c r="T57">
+        <v>1.332766679718474</v>
+      </c>
+      <c r="U57">
+        <v>0.1566</v>
+      </c>
+      <c r="V57">
+        <v>0.2065678871442147</v>
+      </c>
+      <c r="W57">
+        <v>0.124251468873216</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.8262715485768586</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1540486269923341</v>
+      </c>
+      <c r="C58">
+        <v>1.394582995976784</v>
+      </c>
+      <c r="D58">
+        <v>5.664902995976785</v>
+      </c>
+      <c r="E58">
+        <v>5.338320000000001</v>
+      </c>
+      <c r="F58">
+        <v>5.500320000000001</v>
+      </c>
+      <c r="G58">
+        <v>1.23</v>
+      </c>
+      <c r="H58">
+        <v>9.66</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.92</v>
+      </c>
+      <c r="K58">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L58">
+        <v>0.699</v>
+      </c>
+      <c r="M58">
+        <v>0.8613501120000003</v>
+      </c>
+      <c r="N58">
+        <v>-0.1623501120000004</v>
+      </c>
+      <c r="O58">
+        <v>-0.04058752800000009</v>
+      </c>
+      <c r="P58">
+        <v>-0.1217625840000003</v>
+      </c>
+      <c r="Q58">
+        <v>0.0992374159999998</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1912370888910575</v>
+      </c>
+      <c r="T58">
+        <v>1.363056831530257</v>
+      </c>
+      <c r="U58">
+        <v>0.1566</v>
+      </c>
+      <c r="V58">
+        <v>0.2028791748737822</v>
+      </c>
+      <c r="W58">
+        <v>0.1248291212147657</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8115166994951289</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1871298680385321</v>
+      </c>
+      <c r="C59">
+        <v>0.03294906598828806</v>
+      </c>
+      <c r="D59">
+        <v>4.401489065988288</v>
+      </c>
+      <c r="E59">
+        <v>5.436540000000001</v>
+      </c>
+      <c r="F59">
+        <v>5.598540000000001</v>
+      </c>
+      <c r="G59">
+        <v>1.23</v>
+      </c>
+      <c r="H59">
+        <v>9.66</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.92</v>
+      </c>
+      <c r="K59">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L59">
+        <v>0.699</v>
+      </c>
+      <c r="M59">
+        <v>1.168975152</v>
+      </c>
+      <c r="N59">
+        <v>-0.4699751520000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.1174937880000001</v>
+      </c>
+      <c r="P59">
+        <v>-0.3524813640000002</v>
+      </c>
+      <c r="Q59">
+        <v>-0.1314813640000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1997803724610774</v>
+      </c>
+      <c r="T59">
+        <v>1.439448877052316</v>
+      </c>
+      <c r="U59">
+        <v>0.2088</v>
+      </c>
+      <c r="V59">
+        <v>0.1494899183280501</v>
+      </c>
+      <c r="W59">
+        <v>0.1775865050531031</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5979596733122003</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1888298680385321</v>
+      </c>
+      <c r="C60">
+        <v>-0.1151445459131653</v>
+      </c>
+      <c r="D60">
+        <v>4.351615454086835</v>
+      </c>
+      <c r="E60">
+        <v>5.53476</v>
+      </c>
+      <c r="F60">
+        <v>5.69676</v>
+      </c>
+      <c r="G60">
+        <v>1.23</v>
+      </c>
+      <c r="H60">
+        <v>9.66</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.92</v>
+      </c>
+      <c r="K60">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L60">
+        <v>0.699</v>
+      </c>
+      <c r="M60">
+        <v>1.189483488</v>
+      </c>
+      <c r="N60">
+        <v>-0.4904834880000001</v>
+      </c>
+      <c r="O60">
+        <v>-0.122620872</v>
+      </c>
+      <c r="P60">
+        <v>-0.367862616</v>
+      </c>
+      <c r="Q60">
+        <v>-0.1468626159999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2036132384720554</v>
+      </c>
+      <c r="T60">
+        <v>1.473721469363085</v>
+      </c>
+      <c r="U60">
+        <v>0.2088</v>
+      </c>
+      <c r="V60">
+        <v>0.1469125059430837</v>
+      </c>
+      <c r="W60">
+        <v>0.1781246687590841</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.587650023772335</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1905298680385321</v>
+      </c>
+      <c r="C61">
+        <v>-0.2621205777187754</v>
+      </c>
+      <c r="D61">
+        <v>4.302859422281225</v>
+      </c>
+      <c r="E61">
+        <v>5.632980000000001</v>
+      </c>
+      <c r="F61">
+        <v>5.794980000000001</v>
+      </c>
+      <c r="G61">
+        <v>1.23</v>
+      </c>
+      <c r="H61">
+        <v>9.66</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.92</v>
+      </c>
+      <c r="K61">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L61">
+        <v>0.699</v>
+      </c>
+      <c r="M61">
+        <v>1.209991824</v>
+      </c>
+      <c r="N61">
+        <v>-0.5109918240000003</v>
+      </c>
+      <c r="O61">
+        <v>-0.1277479560000001</v>
+      </c>
+      <c r="P61">
+        <v>-0.3832438680000002</v>
+      </c>
+      <c r="Q61">
+        <v>-0.1622438680000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2076330735567397</v>
+      </c>
+      <c r="T61">
+        <v>1.509665895445111</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0.1444224634694721</v>
+      </c>
+      <c r="W61">
+        <v>0.1786445896275742</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5776898538778885</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1922298680385321</v>
+      </c>
+      <c r="C62">
+        <v>-0.4080161777267293</v>
+      </c>
+      <c r="D62">
+        <v>4.255183822273271</v>
+      </c>
+      <c r="E62">
+        <v>5.7312</v>
+      </c>
+      <c r="F62">
+        <v>5.8932</v>
+      </c>
+      <c r="G62">
+        <v>1.23</v>
+      </c>
+      <c r="H62">
+        <v>9.66</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.92</v>
+      </c>
+      <c r="K62">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L62">
+        <v>0.699</v>
+      </c>
+      <c r="M62">
+        <v>1.23050016</v>
+      </c>
+      <c r="N62">
+        <v>-0.5315001600000001</v>
+      </c>
+      <c r="O62">
+        <v>-0.13287504</v>
+      </c>
+      <c r="P62">
+        <v>-0.3986251200000001</v>
+      </c>
+      <c r="Q62">
+        <v>-0.17762512</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2118539003956582</v>
+      </c>
+      <c r="T62">
+        <v>1.547407542831239</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.1420154224116476</v>
+      </c>
+      <c r="W62">
+        <v>0.179147179800448</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5680616896465904</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1939298680385321</v>
+      </c>
+      <c r="C63">
+        <v>-0.552866865867764</v>
+      </c>
+      <c r="D63">
+        <v>4.208553134132237</v>
+      </c>
+      <c r="E63">
+        <v>5.829420000000001</v>
+      </c>
+      <c r="F63">
+        <v>5.991420000000001</v>
+      </c>
+      <c r="G63">
+        <v>1.23</v>
+      </c>
+      <c r="H63">
+        <v>9.66</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.92</v>
+      </c>
+      <c r="K63">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L63">
+        <v>0.699</v>
+      </c>
+      <c r="M63">
+        <v>1.251008496</v>
+      </c>
+      <c r="N63">
+        <v>-0.5520084960000003</v>
+      </c>
+      <c r="O63">
+        <v>-0.1380021240000001</v>
+      </c>
+      <c r="P63">
+        <v>-0.4140063720000002</v>
+      </c>
+      <c r="Q63">
+        <v>-0.1930063720000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2162911798929828</v>
+      </c>
+      <c r="T63">
+        <v>1.587084659314092</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.1396873007327681</v>
+      </c>
+      <c r="W63">
+        <v>0.179633291606998</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5587492029310726</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1956298680385321</v>
+      </c>
+      <c r="C64">
+        <v>-0.696706621960824</v>
+      </c>
+      <c r="D64">
+        <v>4.162933378039177</v>
+      </c>
+      <c r="E64">
+        <v>5.92764</v>
+      </c>
+      <c r="F64">
+        <v>6.08964</v>
+      </c>
+      <c r="G64">
+        <v>1.23</v>
+      </c>
+      <c r="H64">
+        <v>9.66</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.92</v>
+      </c>
+      <c r="K64">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L64">
+        <v>0.699</v>
+      </c>
+      <c r="M64">
+        <v>1.271516832</v>
+      </c>
+      <c r="N64">
+        <v>-0.5725168320000001</v>
+      </c>
+      <c r="O64">
+        <v>-0.143129208</v>
+      </c>
+      <c r="P64">
+        <v>-0.4293876240000001</v>
+      </c>
+      <c r="Q64">
+        <v>-0.208387624</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2209620004164823</v>
+      </c>
+      <c r="T64">
+        <v>1.628850045085515</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.1374342797532074</v>
+      </c>
+      <c r="W64">
+        <v>0.1801037223875303</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5497371190128295</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1973298680385321</v>
+      </c>
+      <c r="C65">
+        <v>-0.8395679682902522</v>
+      </c>
+      <c r="D65">
+        <v>4.118292031709749</v>
+      </c>
+      <c r="E65">
+        <v>6.025860000000001</v>
+      </c>
+      <c r="F65">
+        <v>6.187860000000001</v>
+      </c>
+      <c r="G65">
+        <v>1.23</v>
+      </c>
+      <c r="H65">
+        <v>9.66</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.92</v>
+      </c>
+      <c r="K65">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L65">
+        <v>0.699</v>
+      </c>
+      <c r="M65">
+        <v>1.292025168</v>
+      </c>
+      <c r="N65">
+        <v>-0.5930251680000002</v>
+      </c>
+      <c r="O65">
+        <v>-0.148256292</v>
+      </c>
+      <c r="P65">
+        <v>-0.4447688760000001</v>
+      </c>
+      <c r="Q65">
+        <v>-0.2237688760000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2258852977250359</v>
+      </c>
+      <c r="T65">
+        <v>1.672873019277016</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.1352527832491882</v>
+      </c>
+      <c r="W65">
+        <v>0.1805592188575695</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5410111329967529</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1990298680385321</v>
+      </c>
+      <c r="C66">
+        <v>-0.9814820469262218</v>
+      </c>
+      <c r="D66">
+        <v>4.07459795307378</v>
+      </c>
+      <c r="E66">
+        <v>6.124080000000001</v>
+      </c>
+      <c r="F66">
+        <v>6.286080000000001</v>
+      </c>
+      <c r="G66">
+        <v>1.23</v>
+      </c>
+      <c r="H66">
+        <v>9.66</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.92</v>
+      </c>
+      <c r="K66">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L66">
+        <v>0.699</v>
+      </c>
+      <c r="M66">
+        <v>1.312533504</v>
+      </c>
+      <c r="N66">
+        <v>-0.6135335040000004</v>
+      </c>
+      <c r="O66">
+        <v>-0.1533833760000001</v>
+      </c>
+      <c r="P66">
+        <v>-0.4601501280000003</v>
+      </c>
+      <c r="Q66">
+        <v>-0.2391501280000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2310821115507314</v>
+      </c>
+      <c r="T66">
+        <v>1.719341714256933</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1331394585109196</v>
+      </c>
+      <c r="W66">
+        <v>0.18100048106292</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5325578340436785</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2007298680385321</v>
+      </c>
+      <c r="C67">
+        <v>-1.122478692174751</v>
+      </c>
+      <c r="D67">
+        <v>4.03182130782525</v>
+      </c>
+      <c r="E67">
+        <v>6.222300000000001</v>
+      </c>
+      <c r="F67">
+        <v>6.384300000000001</v>
+      </c>
+      <c r="G67">
+        <v>1.23</v>
+      </c>
+      <c r="H67">
+        <v>9.66</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.92</v>
+      </c>
+      <c r="K67">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L67">
+        <v>0.699</v>
+      </c>
+      <c r="M67">
+        <v>1.33304184</v>
+      </c>
+      <c r="N67">
+        <v>-0.6340418400000002</v>
+      </c>
+      <c r="O67">
+        <v>-0.15851046</v>
+      </c>
+      <c r="P67">
+        <v>-0.4755313800000002</v>
+      </c>
+      <c r="Q67">
+        <v>-0.2545313800000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2365758861664665</v>
+      </c>
+      <c r="T67">
+        <v>1.768465763235703</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1310911591492132</v>
+      </c>
+      <c r="W67">
+        <v>0.1814281659696443</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5243646365968527</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2024298680385321</v>
+      </c>
+      <c r="C68">
+        <v>-1.262586498511482</v>
+      </c>
+      <c r="D68">
+        <v>3.989933501488519</v>
+      </c>
+      <c r="E68">
+        <v>6.320520000000001</v>
+      </c>
+      <c r="F68">
+        <v>6.482520000000001</v>
+      </c>
+      <c r="G68">
+        <v>1.23</v>
+      </c>
+      <c r="H68">
+        <v>9.66</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.92</v>
+      </c>
+      <c r="K68">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L68">
+        <v>0.699</v>
+      </c>
+      <c r="M68">
+        <v>1.353550176</v>
+      </c>
+      <c r="N68">
+        <v>-0.6545501760000004</v>
+      </c>
+      <c r="O68">
+        <v>-0.1636375440000001</v>
+      </c>
+      <c r="P68">
+        <v>-0.4909126320000003</v>
+      </c>
+      <c r="Q68">
+        <v>-0.2699126320000003</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.242392823994892</v>
+      </c>
+      <c r="T68">
+        <v>1.820479462154399</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1291049294651342</v>
+      </c>
+      <c r="W68">
+        <v>0.18184289072768</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5164197178605368</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2041298680385321</v>
+      </c>
+      <c r="C69">
+        <v>-1.401832884324295</v>
+      </c>
+      <c r="D69">
+        <v>3.948907115675706</v>
+      </c>
+      <c r="E69">
+        <v>6.418740000000001</v>
+      </c>
+      <c r="F69">
+        <v>6.580740000000001</v>
+      </c>
+      <c r="G69">
+        <v>1.23</v>
+      </c>
+      <c r="H69">
+        <v>9.66</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.92</v>
+      </c>
+      <c r="K69">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L69">
+        <v>0.699</v>
+      </c>
+      <c r="M69">
+        <v>1.374058512</v>
+      </c>
+      <c r="N69">
+        <v>-0.6750585120000004</v>
+      </c>
+      <c r="O69">
+        <v>-0.1687646280000001</v>
+      </c>
+      <c r="P69">
+        <v>-0.5062938840000003</v>
+      </c>
+      <c r="Q69">
+        <v>-0.2852938840000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2485623035098887</v>
+      </c>
+      <c r="T69">
+        <v>1.875645506462108</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1271779902193859</v>
+      </c>
+      <c r="W69">
+        <v>0.1822452356421922</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5087119608775437</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2058298680385321</v>
+      </c>
+      <c r="C70">
+        <v>-1.540244151763363</v>
+      </c>
+      <c r="D70">
+        <v>3.908715848236637</v>
+      </c>
+      <c r="E70">
+        <v>6.516960000000001</v>
+      </c>
+      <c r="F70">
+        <v>6.678960000000001</v>
+      </c>
+      <c r="G70">
+        <v>1.23</v>
+      </c>
+      <c r="H70">
+        <v>9.66</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.92</v>
+      </c>
+      <c r="K70">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L70">
+        <v>0.699</v>
+      </c>
+      <c r="M70">
+        <v>1.394566848</v>
+      </c>
+      <c r="N70">
+        <v>-0.6955668480000002</v>
+      </c>
+      <c r="O70">
+        <v>-0.1738917120000001</v>
+      </c>
+      <c r="P70">
+        <v>-0.5216751360000002</v>
+      </c>
+      <c r="Q70">
+        <v>-0.3006751360000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2551173754945728</v>
+      </c>
+      <c r="T70">
+        <v>1.93425942853905</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.1253077256573361</v>
+      </c>
+      <c r="W70">
+        <v>0.1826357468827483</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5012309026293444</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2290398835082046</v>
+      </c>
+      <c r="C71">
+        <v>-2.115342888393867</v>
+      </c>
+      <c r="D71">
+        <v>3.431837111606134</v>
+      </c>
+      <c r="E71">
+        <v>6.615180000000001</v>
+      </c>
+      <c r="F71">
+        <v>6.777180000000001</v>
+      </c>
+      <c r="G71">
+        <v>1.23</v>
+      </c>
+      <c r="H71">
+        <v>9.66</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.92</v>
+      </c>
+      <c r="K71">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L71">
+        <v>0.699</v>
+      </c>
+      <c r="M71">
+        <v>1.618390584</v>
+      </c>
+      <c r="N71">
+        <v>-0.9193905840000004</v>
+      </c>
+      <c r="O71">
+        <v>-0.2298476460000001</v>
+      </c>
+      <c r="P71">
+        <v>-0.6895429380000003</v>
+      </c>
+      <c r="Q71">
+        <v>-0.4685429380000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2647083084772125</v>
+      </c>
+      <c r="T71">
+        <v>2.020019310322668</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.107977642558998</v>
+      </c>
+      <c r="W71">
+        <v>0.2130149389569113</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4319105702359918</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2310398835082047</v>
+      </c>
+      <c r="C72">
+        <v>-2.249266583683089</v>
+      </c>
+      <c r="D72">
+        <v>3.396133416316913</v>
+      </c>
+      <c r="E72">
+        <v>6.713400000000002</v>
+      </c>
+      <c r="F72">
+        <v>6.875400000000002</v>
+      </c>
+      <c r="G72">
+        <v>1.23</v>
+      </c>
+      <c r="H72">
+        <v>9.66</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.92</v>
+      </c>
+      <c r="K72">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L72">
+        <v>0.699</v>
+      </c>
+      <c r="M72">
+        <v>1.64184552</v>
+      </c>
+      <c r="N72">
+        <v>-0.9428455200000004</v>
+      </c>
+      <c r="O72">
+        <v>-0.2357113800000001</v>
+      </c>
+      <c r="P72">
+        <v>-0.7071341400000003</v>
+      </c>
+      <c r="Q72">
+        <v>-0.4861341400000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.272238585426453</v>
+      </c>
+      <c r="T72">
+        <v>2.087353287333424</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.1064351048081551</v>
+      </c>
+      <c r="W72">
+        <v>0.2133832969718126</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4257404192326205</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2330398835082047</v>
+      </c>
+      <c r="C73">
+        <v>-2.382455029452089</v>
+      </c>
+      <c r="D73">
+        <v>3.361164970547911</v>
+      </c>
+      <c r="E73">
+        <v>6.81162</v>
+      </c>
+      <c r="F73">
+        <v>6.97362</v>
+      </c>
+      <c r="G73">
+        <v>1.23</v>
+      </c>
+      <c r="H73">
+        <v>9.66</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.92</v>
+      </c>
+      <c r="K73">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L73">
+        <v>0.699</v>
+      </c>
+      <c r="M73">
+        <v>1.665300456</v>
+      </c>
+      <c r="N73">
+        <v>-0.9663004560000003</v>
+      </c>
+      <c r="O73">
+        <v>-0.2415751140000001</v>
+      </c>
+      <c r="P73">
+        <v>-0.7247253420000002</v>
+      </c>
+      <c r="Q73">
+        <v>-0.5037253420000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2802881918204685</v>
+      </c>
+      <c r="T73">
+        <v>2.159330986896645</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.1049360188249417</v>
+      </c>
+      <c r="W73">
+        <v>0.2137412787046039</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4197440752997668</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2350398835082047</v>
+      </c>
+      <c r="C74">
+        <v>-2.514930705825923</v>
+      </c>
+      <c r="D74">
+        <v>3.326909294174078</v>
+      </c>
+      <c r="E74">
+        <v>6.909840000000001</v>
+      </c>
+      <c r="F74">
+        <v>7.071840000000001</v>
+      </c>
+      <c r="G74">
+        <v>1.23</v>
+      </c>
+      <c r="H74">
+        <v>9.66</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.92</v>
+      </c>
+      <c r="K74">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L74">
+        <v>0.699</v>
+      </c>
+      <c r="M74">
+        <v>1.688755392</v>
+      </c>
+      <c r="N74">
+        <v>-0.9897553920000003</v>
+      </c>
+      <c r="O74">
+        <v>-0.2474388480000001</v>
+      </c>
+      <c r="P74">
+        <v>-0.7423165440000002</v>
+      </c>
+      <c r="Q74">
+        <v>-0.5213165440000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.288912770099771</v>
+      </c>
+      <c r="T74">
+        <v>2.236449950714382</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.1034785741190397</v>
+      </c>
+      <c r="W74">
+        <v>0.2140893165003733</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4139142964761588</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2370398835082047</v>
+      </c>
+      <c r="C75">
+        <v>-2.646715185740846</v>
+      </c>
+      <c r="D75">
+        <v>3.293344814259154</v>
+      </c>
+      <c r="E75">
+        <v>7.00806</v>
+      </c>
+      <c r="F75">
+        <v>7.17006</v>
+      </c>
+      <c r="G75">
+        <v>1.23</v>
+      </c>
+      <c r="H75">
+        <v>9.66</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.92</v>
+      </c>
+      <c r="K75">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L75">
+        <v>0.699</v>
+      </c>
+      <c r="M75">
+        <v>1.712210328</v>
+      </c>
+      <c r="N75">
+        <v>-1.013210328</v>
+      </c>
+      <c r="O75">
+        <v>-0.253302582</v>
+      </c>
+      <c r="P75">
+        <v>-0.759907746</v>
+      </c>
+      <c r="Q75">
+        <v>-0.5389077459999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2981762060293922</v>
+      </c>
+      <c r="T75">
+        <v>2.31928143037047</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.1020610594050803</v>
+      </c>
+      <c r="W75">
+        <v>0.2144278190140669</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4082442376203211</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2390398835082047</v>
+      </c>
+      <c r="C76">
+        <v>-2.77782918024943</v>
+      </c>
+      <c r="D76">
+        <v>3.26045081975057</v>
+      </c>
+      <c r="E76">
+        <v>7.106280000000001</v>
+      </c>
+      <c r="F76">
+        <v>7.268280000000001</v>
+      </c>
+      <c r="G76">
+        <v>1.23</v>
+      </c>
+      <c r="H76">
+        <v>9.66</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.92</v>
+      </c>
+      <c r="K76">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L76">
+        <v>0.699</v>
+      </c>
+      <c r="M76">
+        <v>1.735665264</v>
+      </c>
+      <c r="N76">
+        <v>-1.036665264</v>
+      </c>
+      <c r="O76">
+        <v>-0.2591663160000001</v>
+      </c>
+      <c r="P76">
+        <v>-0.7774989480000002</v>
+      </c>
+      <c r="Q76">
+        <v>-0.5564989480000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3081522139535995</v>
+      </c>
+      <c r="T76">
+        <v>2.408484562307796</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.1006818558996062</v>
+      </c>
+      <c r="W76">
+        <v>0.214757172811174</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4027274235984248</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2410398835082047</v>
+      </c>
+      <c r="C77">
+        <v>-2.908292581137448</v>
+      </c>
+      <c r="D77">
+        <v>3.228207418862552</v>
+      </c>
+      <c r="E77">
+        <v>7.2045</v>
+      </c>
+      <c r="F77">
+        <v>7.3665</v>
+      </c>
+      <c r="G77">
+        <v>1.23</v>
+      </c>
+      <c r="H77">
+        <v>9.66</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.92</v>
+      </c>
+      <c r="K77">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L77">
+        <v>0.699</v>
+      </c>
+      <c r="M77">
+        <v>1.7591202</v>
+      </c>
+      <c r="N77">
+        <v>-1.0601202</v>
+      </c>
+      <c r="O77">
+        <v>-0.26503005</v>
+      </c>
+      <c r="P77">
+        <v>-0.7950901500000001</v>
+      </c>
+      <c r="Q77">
+        <v>-0.57409015</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3189263025117435</v>
+      </c>
+      <c r="T77">
+        <v>2.504823944800108</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.09933943115427812</v>
+      </c>
+      <c r="W77">
+        <v>0.2150777438403584</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3973577246171126</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2430398835082047</v>
+      </c>
+      <c r="C78">
+        <v>-3.038124501036854</v>
+      </c>
+      <c r="D78">
+        <v>3.196595498963147</v>
+      </c>
+      <c r="E78">
+        <v>7.302720000000001</v>
+      </c>
+      <c r="F78">
+        <v>7.464720000000001</v>
+      </c>
+      <c r="G78">
+        <v>1.23</v>
+      </c>
+      <c r="H78">
+        <v>9.66</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.92</v>
+      </c>
+      <c r="K78">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L78">
+        <v>0.699</v>
+      </c>
+      <c r="M78">
+        <v>1.782575136</v>
+      </c>
+      <c r="N78">
+        <v>-1.083575136</v>
+      </c>
+      <c r="O78">
+        <v>-0.2708937840000001</v>
+      </c>
+      <c r="P78">
+        <v>-0.8126813520000002</v>
+      </c>
+      <c r="Q78">
+        <v>-0.5916813520000002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3305982317830662</v>
+      </c>
+      <c r="T78">
+        <v>2.609191609166779</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.09803233337593237</v>
+      </c>
+      <c r="W78">
+        <v>0.2153898787898274</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3921293335037294</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2450398835082047</v>
+      </c>
+      <c r="C79">
+        <v>-3.167343311204782</v>
+      </c>
+      <c r="D79">
+        <v>3.16559668879522</v>
+      </c>
+      <c r="E79">
+        <v>7.400940000000001</v>
+      </c>
+      <c r="F79">
+        <v>7.562940000000001</v>
+      </c>
+      <c r="G79">
+        <v>1.23</v>
+      </c>
+      <c r="H79">
+        <v>9.66</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.92</v>
+      </c>
+      <c r="K79">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L79">
+        <v>0.699</v>
+      </c>
+      <c r="M79">
+        <v>1.806030072</v>
+      </c>
+      <c r="N79">
+        <v>-1.107030072000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.2767575180000001</v>
+      </c>
+      <c r="P79">
+        <v>-0.8302725540000004</v>
+      </c>
+      <c r="Q79">
+        <v>-0.6092725540000004</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3432851114258081</v>
+      </c>
+      <c r="T79">
+        <v>2.722634722608813</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.09675918618923193</v>
+      </c>
+      <c r="W79">
+        <v>0.2156939063380114</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3870367447569276</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2470398835082047</v>
+      </c>
+      <c r="C80">
+        <v>-3.295966677125513</v>
+      </c>
+      <c r="D80">
+        <v>3.135193322874488</v>
+      </c>
+      <c r="E80">
+        <v>7.499160000000001</v>
+      </c>
+      <c r="F80">
+        <v>7.661160000000001</v>
+      </c>
+      <c r="G80">
+        <v>1.23</v>
+      </c>
+      <c r="H80">
+        <v>9.66</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.92</v>
+      </c>
+      <c r="K80">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L80">
+        <v>0.699</v>
+      </c>
+      <c r="M80">
+        <v>1.829485008</v>
+      </c>
+      <c r="N80">
+        <v>-1.130485008</v>
+      </c>
+      <c r="O80">
+        <v>-0.2826212520000001</v>
+      </c>
+      <c r="P80">
+        <v>-0.8478637560000003</v>
+      </c>
+      <c r="Q80">
+        <v>-0.6268637560000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3571253437633449</v>
+      </c>
+      <c r="T80">
+        <v>2.846390846363759</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.0955186838021905</v>
+      </c>
+      <c r="W80">
+        <v>0.2159901383080369</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.382074735208762</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2490398835082047</v>
+      </c>
+      <c r="C81">
+        <v>-3.424011592080359</v>
+      </c>
+      <c r="D81">
+        <v>3.105368407919642</v>
+      </c>
+      <c r="E81">
+        <v>7.597380000000001</v>
+      </c>
+      <c r="F81">
+        <v>7.759380000000001</v>
+      </c>
+      <c r="G81">
+        <v>1.23</v>
+      </c>
+      <c r="H81">
+        <v>9.66</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.92</v>
+      </c>
+      <c r="K81">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L81">
+        <v>0.699</v>
+      </c>
+      <c r="M81">
+        <v>1.852939944</v>
+      </c>
+      <c r="N81">
+        <v>-1.153939944</v>
+      </c>
+      <c r="O81">
+        <v>-0.2884849860000001</v>
+      </c>
+      <c r="P81">
+        <v>-0.8654549580000002</v>
+      </c>
+      <c r="Q81">
+        <v>-0.6444549580000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3722836934663613</v>
+      </c>
+      <c r="T81">
+        <v>2.981933267619176</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.09430958653887163</v>
+      </c>
+      <c r="W81">
+        <v>0.2162788707345175</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3772383461554866</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2510398835082047</v>
+      </c>
+      <c r="C82">
+        <v>-3.551494408819512</v>
+      </c>
+      <c r="D82">
+        <v>3.07610559118049</v>
+      </c>
+      <c r="E82">
+        <v>7.695600000000002</v>
+      </c>
+      <c r="F82">
+        <v>7.857600000000001</v>
+      </c>
+      <c r="G82">
+        <v>1.23</v>
+      </c>
+      <c r="H82">
+        <v>9.66</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.92</v>
+      </c>
+      <c r="K82">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L82">
+        <v>0.699</v>
+      </c>
+      <c r="M82">
+        <v>1.876394880000001</v>
+      </c>
+      <c r="N82">
+        <v>-1.17739488</v>
+      </c>
+      <c r="O82">
+        <v>-0.2943487200000001</v>
+      </c>
+      <c r="P82">
+        <v>-0.8830461600000004</v>
+      </c>
+      <c r="Q82">
+        <v>-0.6620461600000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3889578781396795</v>
+      </c>
+      <c r="T82">
+        <v>3.131029931000135</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.09313071670713573</v>
+      </c>
+      <c r="W82">
+        <v>0.216560384850336</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.372522866828543</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2530398835082047</v>
+      </c>
+      <c r="C83">
+        <v>-3.678430869459882</v>
+      </c>
+      <c r="D83">
+        <v>3.04738913054012</v>
+      </c>
+      <c r="E83">
+        <v>7.793820000000001</v>
+      </c>
+      <c r="F83">
+        <v>7.955820000000001</v>
+      </c>
+      <c r="G83">
+        <v>1.23</v>
+      </c>
+      <c r="H83">
+        <v>9.66</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.92</v>
+      </c>
+      <c r="K83">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L83">
+        <v>0.699</v>
+      </c>
+      <c r="M83">
+        <v>1.899849816</v>
+      </c>
+      <c r="N83">
+        <v>-1.200849816</v>
+      </c>
+      <c r="O83">
+        <v>-0.3002124540000001</v>
+      </c>
+      <c r="P83">
+        <v>-0.9006373620000002</v>
+      </c>
+      <c r="Q83">
+        <v>-0.6796373620000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.407387240147031</v>
+      </c>
+      <c r="T83">
+        <v>3.295820980000143</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.09198095477247974</v>
+      </c>
+      <c r="W83">
+        <v>0.2168349480003319</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.367923819089919</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2550398835082047</v>
+      </c>
+      <c r="C84">
+        <v>-3.804836133723811</v>
+      </c>
+      <c r="D84">
+        <v>3.01920386627619</v>
+      </c>
+      <c r="E84">
+        <v>7.892040000000001</v>
+      </c>
+      <c r="F84">
+        <v>8.054040000000001</v>
+      </c>
+      <c r="G84">
+        <v>1.23</v>
+      </c>
+      <c r="H84">
+        <v>9.66</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.92</v>
+      </c>
+      <c r="K84">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L84">
+        <v>0.699</v>
+      </c>
+      <c r="M84">
+        <v>1.923304752</v>
+      </c>
+      <c r="N84">
+        <v>-1.224304752</v>
+      </c>
+      <c r="O84">
+        <v>-0.306076188</v>
+      </c>
+      <c r="P84">
+        <v>-0.9182285640000001</v>
+      </c>
+      <c r="Q84">
+        <v>-0.697228564</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4278643090440883</v>
+      </c>
+      <c r="T84">
+        <v>3.478922145555706</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.09085923581183976</v>
+      </c>
+      <c r="W84">
+        <v>0.2171028144881327</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3634369432473591</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2570398835082047</v>
+      </c>
+      <c r="C85">
+        <v>-3.930724805625047</v>
+      </c>
+      <c r="D85">
+        <v>2.991535194374954</v>
+      </c>
+      <c r="E85">
+        <v>7.990260000000002</v>
+      </c>
+      <c r="F85">
+        <v>8.152260000000002</v>
+      </c>
+      <c r="G85">
+        <v>1.23</v>
+      </c>
+      <c r="H85">
+        <v>9.66</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.92</v>
+      </c>
+      <c r="K85">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L85">
+        <v>0.699</v>
+      </c>
+      <c r="M85">
+        <v>1.946759688</v>
+      </c>
+      <c r="N85">
+        <v>-1.247759688</v>
+      </c>
+      <c r="O85">
+        <v>-0.3119399220000001</v>
+      </c>
+      <c r="P85">
+        <v>-0.9358197660000003</v>
+      </c>
+      <c r="Q85">
+        <v>-0.7148197660000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4507504448702112</v>
+      </c>
+      <c r="T85">
+        <v>3.683564624706042</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.08976454622374529</v>
+      </c>
+      <c r="W85">
+        <v>0.2173642263617696</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3590581848949812</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2590398835082047</v>
+      </c>
+      <c r="C86">
+        <v>-4.056110958700709</v>
+      </c>
+      <c r="D86">
+        <v>2.964369041299292</v>
+      </c>
+      <c r="E86">
+        <v>8.088480000000001</v>
+      </c>
+      <c r="F86">
+        <v>8.250480000000001</v>
+      </c>
+      <c r="G86">
+        <v>1.23</v>
+      </c>
+      <c r="H86">
+        <v>9.66</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.92</v>
+      </c>
+      <c r="K86">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L86">
+        <v>0.699</v>
+      </c>
+      <c r="M86">
+        <v>1.970214624</v>
+      </c>
+      <c r="N86">
+        <v>-1.271214624000001</v>
+      </c>
+      <c r="O86">
+        <v>-0.3178036560000002</v>
+      </c>
+      <c r="P86">
+        <v>-0.9534109680000005</v>
+      </c>
+      <c r="Q86">
+        <v>-0.7324109680000004</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4764973476745992</v>
+      </c>
+      <c r="T86">
+        <v>3.913787413750168</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0886959206734626</v>
+      </c>
+      <c r="W86">
+        <v>0.2176194141431771</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3547836826938503</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2610398835082047</v>
+      </c>
+      <c r="C87">
+        <v>-4.181008159880845</v>
+      </c>
+      <c r="D87">
+        <v>2.937691840119156</v>
+      </c>
+      <c r="E87">
+        <v>8.1867</v>
+      </c>
+      <c r="F87">
+        <v>8.348700000000001</v>
+      </c>
+      <c r="G87">
+        <v>1.23</v>
+      </c>
+      <c r="H87">
+        <v>9.66</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.92</v>
+      </c>
+      <c r="K87">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L87">
+        <v>0.699</v>
+      </c>
+      <c r="M87">
+        <v>1.99366956</v>
+      </c>
+      <c r="N87">
+        <v>-1.29466956</v>
+      </c>
+      <c r="O87">
+        <v>-0.3236673900000001</v>
+      </c>
+      <c r="P87">
+        <v>-0.9710021700000003</v>
+      </c>
+      <c r="Q87">
+        <v>-0.7500021700000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5056771708529058</v>
+      </c>
+      <c r="T87">
+        <v>4.174706574666846</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.08765243925377482</v>
+      </c>
+      <c r="W87">
+        <v>0.2178685975061986</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3506097570150992</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2630398835082047</v>
+      </c>
+      <c r="C88">
+        <v>-4.305429492080625</v>
+      </c>
+      <c r="D88">
+        <v>2.911490507919376</v>
+      </c>
+      <c r="E88">
+        <v>8.28492</v>
+      </c>
+      <c r="F88">
+        <v>8.44692</v>
+      </c>
+      <c r="G88">
+        <v>1.23</v>
+      </c>
+      <c r="H88">
+        <v>9.66</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.92</v>
+      </c>
+      <c r="K88">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L88">
+        <v>0.699</v>
+      </c>
+      <c r="M88">
+        <v>2.017124496</v>
+      </c>
+      <c r="N88">
+        <v>-1.318124496</v>
+      </c>
+      <c r="O88">
+        <v>-0.3295311240000001</v>
+      </c>
+      <c r="P88">
+        <v>-0.9885933720000002</v>
+      </c>
+      <c r="Q88">
+        <v>-0.7675933720000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5390255401995419</v>
+      </c>
+      <c r="T88">
+        <v>4.472899901428764</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.08663322484384721</v>
+      </c>
+      <c r="W88">
+        <v>0.2181119859072893</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3465328993753888</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2650398835082047</v>
+      </c>
+      <c r="C89">
+        <v>-4.429387575594212</v>
+      </c>
+      <c r="D89">
+        <v>2.885752424405788</v>
+      </c>
+      <c r="E89">
+        <v>8.383139999999999</v>
+      </c>
+      <c r="F89">
+        <v>8.54514</v>
+      </c>
+      <c r="G89">
+        <v>1.23</v>
+      </c>
+      <c r="H89">
+        <v>9.66</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.92</v>
+      </c>
+      <c r="K89">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L89">
+        <v>0.699</v>
+      </c>
+      <c r="M89">
+        <v>2.040579432</v>
+      </c>
+      <c r="N89">
+        <v>-1.341579432</v>
+      </c>
+      <c r="O89">
+        <v>-0.335394858</v>
+      </c>
+      <c r="P89">
+        <v>-1.006184574</v>
+      </c>
+      <c r="Q89">
+        <v>-0.7851845740000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.577504427907199</v>
+      </c>
+      <c r="T89">
+        <v>4.816969124615591</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.08563744065023977</v>
+      </c>
+      <c r="W89">
+        <v>0.2183497791727227</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.342549762600959</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2670398835082047</v>
+      </c>
+      <c r="C90">
+        <v>-4.552894588363847</v>
+      </c>
+      <c r="D90">
+        <v>2.860465411636155</v>
+      </c>
+      <c r="E90">
+        <v>8.48136</v>
+      </c>
+      <c r="F90">
+        <v>8.643360000000001</v>
+      </c>
+      <c r="G90">
+        <v>1.23</v>
+      </c>
+      <c r="H90">
+        <v>9.66</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.92</v>
+      </c>
+      <c r="K90">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L90">
+        <v>0.699</v>
+      </c>
+      <c r="M90">
+        <v>2.064034368000001</v>
+      </c>
+      <c r="N90">
+        <v>-1.365034368000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.3412585920000002</v>
+      </c>
+      <c r="P90">
+        <v>-1.023775776000001</v>
+      </c>
+      <c r="Q90">
+        <v>-0.8027757760000005</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6223964635661323</v>
+      </c>
+      <c r="T90">
+        <v>5.218383218333559</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.08466428791557794</v>
+      </c>
+      <c r="W90">
+        <v>0.21858216804576</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3386571516623117</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2690398835082047</v>
+      </c>
+      <c r="C91">
+        <v>-4.675962285192483</v>
+      </c>
+      <c r="D91">
+        <v>2.835617714807517</v>
+      </c>
+      <c r="E91">
+        <v>8.57958</v>
+      </c>
+      <c r="F91">
+        <v>8.741580000000001</v>
+      </c>
+      <c r="G91">
+        <v>1.23</v>
+      </c>
+      <c r="H91">
+        <v>9.66</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.92</v>
+      </c>
+      <c r="K91">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L91">
+        <v>0.699</v>
+      </c>
+      <c r="M91">
+        <v>2.087489304</v>
+      </c>
+      <c r="N91">
+        <v>-1.388489304000001</v>
+      </c>
+      <c r="O91">
+        <v>-0.3471223260000001</v>
+      </c>
+      <c r="P91">
+        <v>-1.041366978000001</v>
+      </c>
+      <c r="Q91">
+        <v>-0.8203669780000005</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6754506875266899</v>
+      </c>
+      <c r="T91">
+        <v>5.692781692727518</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.08371300378169504</v>
+      </c>
+      <c r="W91">
+        <v>0.2188093346969313</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3348520151267801</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2710398835082047</v>
+      </c>
+      <c r="C92">
+        <v>-4.798602015963724</v>
+      </c>
+      <c r="D92">
+        <v>2.811197984036276</v>
+      </c>
+      <c r="E92">
+        <v>8.6778</v>
+      </c>
+      <c r="F92">
+        <v>8.8398</v>
+      </c>
+      <c r="G92">
+        <v>1.23</v>
+      </c>
+      <c r="H92">
+        <v>9.66</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.92</v>
+      </c>
+      <c r="K92">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L92">
+        <v>0.699</v>
+      </c>
+      <c r="M92">
+        <v>2.11094424</v>
+      </c>
+      <c r="N92">
+        <v>-1.41194424</v>
+      </c>
+      <c r="O92">
+        <v>-0.3529860600000001</v>
+      </c>
+      <c r="P92">
+        <v>-1.05895818</v>
+      </c>
+      <c r="Q92">
+        <v>-0.8379581800000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7391157562793589</v>
+      </c>
+      <c r="T92">
+        <v>6.26205986200027</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.08278285929523177</v>
+      </c>
+      <c r="W92">
+        <v>0.2190314532002987</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3311314371809271</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2730398835082047</v>
+      </c>
+      <c r="C93">
+        <v>-4.92082474292835</v>
+      </c>
+      <c r="D93">
+        <v>2.787195257071652</v>
+      </c>
+      <c r="E93">
+        <v>8.776020000000001</v>
+      </c>
+      <c r="F93">
+        <v>8.938020000000002</v>
+      </c>
+      <c r="G93">
+        <v>1.23</v>
+      </c>
+      <c r="H93">
+        <v>9.66</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.92</v>
+      </c>
+      <c r="K93">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L93">
+        <v>0.699</v>
+      </c>
+      <c r="M93">
+        <v>2.134399176000001</v>
+      </c>
+      <c r="N93">
+        <v>-1.435399176000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.3588497940000002</v>
+      </c>
+      <c r="P93">
+        <v>-1.076549382</v>
+      </c>
+      <c r="Q93">
+        <v>-0.8555493820000004</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8169286180881767</v>
+      </c>
+      <c r="T93">
+        <v>6.957844291111413</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0818731575447347</v>
+      </c>
+      <c r="W93">
+        <v>0.2192486899783174</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3274926301789388</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2750398835082047</v>
+      </c>
+      <c r="C94">
+        <v>-5.042641057112738</v>
+      </c>
+      <c r="D94">
+        <v>2.763598942887263</v>
+      </c>
+      <c r="E94">
+        <v>8.87424</v>
+      </c>
+      <c r="F94">
+        <v>9.036240000000001</v>
+      </c>
+      <c r="G94">
+        <v>1.23</v>
+      </c>
+      <c r="H94">
+        <v>9.66</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.92</v>
+      </c>
+      <c r="K94">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L94">
+        <v>0.699</v>
+      </c>
+      <c r="M94">
+        <v>2.157854112</v>
+      </c>
+      <c r="N94">
+        <v>-1.458854112</v>
+      </c>
+      <c r="O94">
+        <v>-0.3647135280000001</v>
+      </c>
+      <c r="P94">
+        <v>-1.094140584</v>
+      </c>
+      <c r="Q94">
+        <v>-0.8731405840000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9141946953491988</v>
+      </c>
+      <c r="T94">
+        <v>7.827574827500341</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.08098323191924847</v>
+      </c>
+      <c r="W94">
+        <v>0.2194612042176835</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3239329276769938</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2770398835082047</v>
+      </c>
+      <c r="C95">
+        <v>-5.164061193900851</v>
+      </c>
+      <c r="D95">
+        <v>2.74039880609915</v>
+      </c>
+      <c r="E95">
+        <v>8.97246</v>
+      </c>
+      <c r="F95">
+        <v>9.134460000000001</v>
+      </c>
+      <c r="G95">
+        <v>1.23</v>
+      </c>
+      <c r="H95">
+        <v>9.66</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.92</v>
+      </c>
+      <c r="K95">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L95">
+        <v>0.699</v>
+      </c>
+      <c r="M95">
+        <v>2.181309048</v>
+      </c>
+      <c r="N95">
+        <v>-1.482309048</v>
+      </c>
+      <c r="O95">
+        <v>-0.3705772620000001</v>
+      </c>
+      <c r="P95">
+        <v>-1.111731786</v>
+      </c>
+      <c r="Q95">
+        <v>-0.8907317860000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.039251080399084</v>
+      </c>
+      <c r="T95">
+        <v>8.945799802857533</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.08011244447925656</v>
+      </c>
+      <c r="W95">
+        <v>0.2196691482583535</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3204497779170262</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2790398835082047</v>
+      </c>
+      <c r="C96">
+        <v>-5.285095047837853</v>
+      </c>
+      <c r="D96">
+        <v>2.717584952162149</v>
+      </c>
+      <c r="E96">
+        <v>9.070680000000001</v>
+      </c>
+      <c r="F96">
+        <v>9.232680000000002</v>
+      </c>
+      <c r="G96">
+        <v>1.23</v>
+      </c>
+      <c r="H96">
+        <v>9.66</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.92</v>
+      </c>
+      <c r="K96">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L96">
+        <v>0.699</v>
+      </c>
+      <c r="M96">
+        <v>2.204763984</v>
+      </c>
+      <c r="N96">
+        <v>-1.505763984000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.3764409960000001</v>
+      </c>
+      <c r="P96">
+        <v>-1.129322988</v>
+      </c>
+      <c r="Q96">
+        <v>-0.9083229880000003</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.205992927132266</v>
+      </c>
+      <c r="T96">
+        <v>10.43676643666712</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.07926018443160489</v>
+      </c>
+      <c r="W96">
+        <v>0.2198726679577328</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3170407377264195</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2810398835082047</v>
+      </c>
+      <c r="C97">
+        <v>-5.405752186700415</v>
+      </c>
+      <c r="D97">
+        <v>2.695147813299587</v>
+      </c>
+      <c r="E97">
+        <v>9.168900000000001</v>
+      </c>
+      <c r="F97">
+        <v>9.330900000000002</v>
+      </c>
+      <c r="G97">
+        <v>1.23</v>
+      </c>
+      <c r="H97">
+        <v>9.66</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.92</v>
+      </c>
+      <c r="K97">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L97">
+        <v>0.699</v>
+      </c>
+      <c r="M97">
+        <v>2.228218920000001</v>
+      </c>
+      <c r="N97">
+        <v>-1.529218920000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.3823047300000002</v>
+      </c>
+      <c r="P97">
+        <v>-1.146914190000001</v>
+      </c>
+      <c r="Q97">
+        <v>-0.9259141900000005</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.439431512558719</v>
+      </c>
+      <c r="T97">
+        <v>12.52411972400055</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.07842586670074587</v>
+      </c>
+      <c r="W97">
+        <v>0.2200719030318619</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3137034668029834</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2830398835082046</v>
+      </c>
+      <c r="C98">
+        <v>-5.526041864875715</v>
+      </c>
+      <c r="D98">
+        <v>2.673078135124286</v>
+      </c>
+      <c r="E98">
+        <v>9.26712</v>
+      </c>
+      <c r="F98">
+        <v>9.429120000000001</v>
+      </c>
+      <c r="G98">
+        <v>1.23</v>
+      </c>
+      <c r="H98">
+        <v>9.66</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.92</v>
+      </c>
+      <c r="K98">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L98">
+        <v>0.699</v>
+      </c>
+      <c r="M98">
+        <v>2.251673856</v>
+      </c>
+      <c r="N98">
+        <v>-1.552673856000001</v>
+      </c>
+      <c r="O98">
+        <v>-0.3881684640000002</v>
+      </c>
+      <c r="P98">
+        <v>-1.164505392000001</v>
+      </c>
+      <c r="Q98">
+        <v>-0.9435053920000005</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.789589390698395</v>
+      </c>
+      <c r="T98">
+        <v>15.65514965500066</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.07760893058927978</v>
+      </c>
+      <c r="W98">
+        <v>0.22026698737528</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.310435722357119</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2850398835082047</v>
+      </c>
+      <c r="C99">
+        <v>-5.645973036088442</v>
+      </c>
+      <c r="D99">
+        <v>2.651366963911559</v>
+      </c>
+      <c r="E99">
+        <v>9.36534</v>
+      </c>
+      <c r="F99">
+        <v>9.527340000000001</v>
+      </c>
+      <c r="G99">
+        <v>1.23</v>
+      </c>
+      <c r="H99">
+        <v>9.66</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.92</v>
+      </c>
+      <c r="K99">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L99">
+        <v>0.699</v>
+      </c>
+      <c r="M99">
+        <v>2.275128792</v>
+      </c>
+      <c r="N99">
+        <v>-1.576128792</v>
+      </c>
+      <c r="O99">
+        <v>-0.3940321980000001</v>
+      </c>
+      <c r="P99">
+        <v>-1.182096594</v>
+      </c>
+      <c r="Q99">
+        <v>-0.9610965940000002</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.373185854264528</v>
+      </c>
+      <c r="T99">
+        <v>20.87353287333422</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.07680883852134907</v>
+      </c>
+      <c r="W99">
+        <v>0.2204580493611019</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3072353540853963</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2870398835082046</v>
+      </c>
+      <c r="C100">
+        <v>-5.765554365512557</v>
+      </c>
+      <c r="D100">
+        <v>2.630005634487443</v>
+      </c>
+      <c r="E100">
+        <v>9.463559999999999</v>
+      </c>
+      <c r="F100">
+        <v>9.62556</v>
+      </c>
+      <c r="G100">
+        <v>1.23</v>
+      </c>
+      <c r="H100">
+        <v>9.66</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.92</v>
+      </c>
+      <c r="K100">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L100">
+        <v>0.699</v>
+      </c>
+      <c r="M100">
+        <v>2.298583728</v>
+      </c>
+      <c r="N100">
+        <v>-1.599583728</v>
+      </c>
+      <c r="O100">
+        <v>-0.3998959320000001</v>
+      </c>
+      <c r="P100">
+        <v>-1.199687796</v>
+      </c>
+      <c r="Q100">
+        <v>-0.978687796</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.540378781396791</v>
+      </c>
+      <c r="T100">
+        <v>31.31029931000132</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.07602507486296796</v>
+      </c>
+      <c r="W100">
+        <v>0.2206452121227233</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3041002994518718</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2890398835082047</v>
+      </c>
+      <c r="C101">
+        <v>-5.884794241302274</v>
+      </c>
+      <c r="D101">
+        <v>2.608985758697728</v>
+      </c>
+      <c r="E101">
+        <v>9.561780000000001</v>
+      </c>
+      <c r="F101">
+        <v>9.723780000000001</v>
+      </c>
+      <c r="G101">
+        <v>1.23</v>
+      </c>
+      <c r="H101">
+        <v>9.66</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.92</v>
+      </c>
+      <c r="K101">
+        <v>0.2210000000000001</v>
+      </c>
+      <c r="L101">
+        <v>0.699</v>
+      </c>
+      <c r="M101">
+        <v>2.322038664</v>
+      </c>
+      <c r="N101">
+        <v>-1.623038664000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.4057596660000001</v>
+      </c>
+      <c r="P101">
+        <v>-1.217278998</v>
+      </c>
+      <c r="Q101">
+        <v>-0.9962789980000002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.041957562793582</v>
+      </c>
+      <c r="T101">
+        <v>62.62059862000264</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.07525714481384706</v>
+      </c>
+      <c r="W101">
+        <v>0.2208285938184534</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3010285792553882</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_household_products.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1157652096930715</v>
+        <v>0.1155095466688388</v>
       </c>
       <c r="C2">
-        <v>20.57035206377255</v>
+        <v>20.43223621594927</v>
       </c>
       <c r="D2">
-        <v>18.40035206377255</v>
+        <v>18.46783621594927</v>
       </c>
       <c r="E2">
-        <v>-0.06</v>
+        <v>0.1456</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2056</v>
       </c>
       <c r="G2">
         <v>2.17</v>
@@ -1451,28 +1451,28 @@
         <v>1.07</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01034168</v>
       </c>
       <c r="N2">
-        <v>1.07</v>
+        <v>1.05965832</v>
       </c>
       <c r="O2">
-        <v>0.2675</v>
+        <v>0.26491458</v>
       </c>
       <c r="P2">
-        <v>0.8025</v>
+        <v>0.79474374</v>
       </c>
       <c r="Q2">
-        <v>1.0425</v>
+        <v>1.03474374</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1157652096930715</v>
+        <v>0.1162952491604433</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6817429376593621</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>103.4648142274756</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1155095466688388</v>
+        <v>0.1152538836446061</v>
       </c>
       <c r="C3">
-        <v>20.43223621594927</v>
+        <v>20.29461719282543</v>
       </c>
       <c r="D3">
-        <v>18.46783621594927</v>
+        <v>18.53581719282543</v>
       </c>
       <c r="E3">
-        <v>0.1456</v>
+        <v>0.3512</v>
       </c>
       <c r="F3">
-        <v>0.2056</v>
+        <v>0.4112</v>
       </c>
       <c r="G3">
         <v>2.17</v>
@@ -1533,28 +1533,28 @@
         <v>1.07</v>
       </c>
       <c r="M3">
-        <v>0.01034168</v>
+        <v>0.02068336</v>
       </c>
       <c r="N3">
-        <v>1.05965832</v>
+        <v>1.04931664</v>
       </c>
       <c r="O3">
-        <v>0.26491458</v>
+        <v>0.26232916</v>
       </c>
       <c r="P3">
-        <v>0.79474374</v>
+        <v>0.7869874800000001</v>
       </c>
       <c r="Q3">
-        <v>1.03474374</v>
+        <v>1.02698748</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1162952491604433</v>
+        <v>0.1168361057598022</v>
       </c>
       <c r="T3">
-        <v>0.6817429376593621</v>
+        <v>0.6869734343423403</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>103.4648142274756</v>
+        <v>51.73240711373781</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1152538836446061</v>
+        <v>0.1149982206203735</v>
       </c>
       <c r="C4">
-        <v>20.29461719282543</v>
+        <v>20.15750050117724</v>
       </c>
       <c r="D4">
-        <v>18.53581719282543</v>
+        <v>18.60430050117724</v>
       </c>
       <c r="E4">
-        <v>0.3512</v>
+        <v>0.5568</v>
       </c>
       <c r="F4">
-        <v>0.4112</v>
+        <v>0.6167999999999999</v>
       </c>
       <c r="G4">
         <v>2.17</v>
@@ -1615,28 +1615,28 @@
         <v>1.07</v>
       </c>
       <c r="M4">
-        <v>0.02068336</v>
+        <v>0.03102503999999999</v>
       </c>
       <c r="N4">
-        <v>1.04931664</v>
+        <v>1.03897496</v>
       </c>
       <c r="O4">
-        <v>0.26232916</v>
+        <v>0.25974374</v>
       </c>
       <c r="P4">
-        <v>0.7869874800000001</v>
+        <v>0.77923122</v>
       </c>
       <c r="Q4">
-        <v>1.02698748</v>
+        <v>1.01923122</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1168361057598022</v>
+        <v>0.1173881140416221</v>
       </c>
       <c r="T4">
-        <v>0.6869734343423403</v>
+        <v>0.6923117763177508</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.73240711373781</v>
+        <v>34.48827140915854</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1149982206203735</v>
+        <v>0.1147425575961408</v>
       </c>
       <c r="C5">
-        <v>20.15750050117724</v>
+        <v>20.02089172946511</v>
       </c>
       <c r="D5">
-        <v>18.60430050117724</v>
+        <v>18.67329172946511</v>
       </c>
       <c r="E5">
-        <v>0.5568</v>
+        <v>0.7624</v>
       </c>
       <c r="F5">
-        <v>0.6167999999999999</v>
+        <v>0.8224</v>
       </c>
       <c r="G5">
         <v>2.17</v>
@@ -1697,28 +1697,28 @@
         <v>1.07</v>
       </c>
       <c r="M5">
-        <v>0.03102503999999999</v>
+        <v>0.04136672</v>
       </c>
       <c r="N5">
-        <v>1.03897496</v>
+        <v>1.02863328</v>
       </c>
       <c r="O5">
-        <v>0.25974374</v>
+        <v>0.25715832</v>
       </c>
       <c r="P5">
-        <v>0.77923122</v>
+        <v>0.7714749599999999</v>
       </c>
       <c r="Q5">
-        <v>1.01923122</v>
+        <v>1.01147496</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1173881140416221</v>
+        <v>0.11795162249598</v>
       </c>
       <c r="T5">
-        <v>0.6923117763177508</v>
+        <v>0.6977613337509825</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.48827140915854</v>
+        <v>25.86620355686891</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1147425575961408</v>
+        <v>0.1144868945719081</v>
       </c>
       <c r="C6">
-        <v>20.02089172946511</v>
+        <v>19.88479654935379</v>
       </c>
       <c r="D6">
-        <v>18.67329172946511</v>
+        <v>18.74279654935379</v>
       </c>
       <c r="E6">
-        <v>0.7624</v>
+        <v>0.968</v>
       </c>
       <c r="F6">
-        <v>0.8224</v>
+        <v>1.028</v>
       </c>
       <c r="G6">
         <v>2.17</v>
@@ -1779,28 +1779,28 @@
         <v>1.07</v>
       </c>
       <c r="M6">
-        <v>0.04136672</v>
+        <v>0.0517084</v>
       </c>
       <c r="N6">
-        <v>1.02863328</v>
+        <v>1.0182916</v>
       </c>
       <c r="O6">
-        <v>0.25715832</v>
+        <v>0.2545729</v>
       </c>
       <c r="P6">
-        <v>0.7714749599999999</v>
+        <v>0.7637187</v>
       </c>
       <c r="Q6">
-        <v>1.01147496</v>
+        <v>1.0037187</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.11795162249598</v>
+        <v>0.1185269942862191</v>
       </c>
       <c r="T6">
-        <v>0.6977613337509825</v>
+        <v>0.7033256187091244</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.86620355686891</v>
+        <v>20.69296284549512</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1144868945719081</v>
+        <v>0.1142312315476754</v>
       </c>
       <c r="C7">
-        <v>19.88479654935379</v>
+        <v>19.74922071726677</v>
       </c>
       <c r="D7">
-        <v>18.74279654935379</v>
+        <v>18.81282071726677</v>
       </c>
       <c r="E7">
-        <v>0.968</v>
+        <v>1.1736</v>
       </c>
       <c r="F7">
-        <v>1.028</v>
+        <v>1.2336</v>
       </c>
       <c r="G7">
         <v>2.17</v>
@@ -1861,28 +1861,28 @@
         <v>1.07</v>
       </c>
       <c r="M7">
-        <v>0.0517084</v>
+        <v>0.06205008</v>
       </c>
       <c r="N7">
-        <v>1.0182916</v>
+        <v>1.00794992</v>
       </c>
       <c r="O7">
-        <v>0.2545729</v>
+        <v>0.25198748</v>
       </c>
       <c r="P7">
-        <v>0.7637187</v>
+        <v>0.7559624400000001</v>
       </c>
       <c r="Q7">
-        <v>1.0037187</v>
+        <v>0.9959624400000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1185269942862191</v>
+        <v>0.119114608029442</v>
       </c>
       <c r="T7">
-        <v>0.7033256187091244</v>
+        <v>0.7090082927089287</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.69296284549512</v>
+        <v>17.24413570457927</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1142312315476754</v>
+        <v>0.1139755685234428</v>
       </c>
       <c r="C8">
-        <v>19.74922071726677</v>
+        <v>19.61417007597537</v>
       </c>
       <c r="D8">
-        <v>18.81282071726677</v>
+        <v>18.88337007597537</v>
       </c>
       <c r="E8">
-        <v>1.1736</v>
+        <v>1.3792</v>
       </c>
       <c r="F8">
-        <v>1.2336</v>
+        <v>1.4392</v>
       </c>
       <c r="G8">
         <v>2.17</v>
@@ -1943,28 +1943,28 @@
         <v>1.07</v>
       </c>
       <c r="M8">
-        <v>0.06205007999999999</v>
+        <v>0.07239175999999999</v>
       </c>
       <c r="N8">
-        <v>1.00794992</v>
+        <v>0.99760824</v>
       </c>
       <c r="O8">
-        <v>0.25198748</v>
+        <v>0.24940206</v>
       </c>
       <c r="P8">
-        <v>0.7559624400000001</v>
+        <v>0.7482061800000001</v>
       </c>
       <c r="Q8">
-        <v>0.9959624400000001</v>
+        <v>0.98820618</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.119114608029442</v>
+        <v>0.1197148586273578</v>
       </c>
       <c r="T8">
-        <v>0.7090082927089287</v>
+        <v>0.7148131747517397</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.24413570457927</v>
+        <v>14.78068774678223</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1139755685234428</v>
+        <v>0.1137199054992101</v>
       </c>
       <c r="C9">
-        <v>19.61417007597537</v>
+        <v>19.47965055622405</v>
       </c>
       <c r="D9">
-        <v>18.88337007597537</v>
+        <v>18.95445055622405</v>
       </c>
       <c r="E9">
-        <v>1.3792</v>
+        <v>1.5848</v>
       </c>
       <c r="F9">
-        <v>1.4392</v>
+        <v>1.6448</v>
       </c>
       <c r="G9">
         <v>2.17</v>
@@ -2025,28 +2025,28 @@
         <v>1.07</v>
       </c>
       <c r="M9">
-        <v>0.07239176</v>
+        <v>0.08273343999999999</v>
       </c>
       <c r="N9">
-        <v>0.99760824</v>
+        <v>0.9872665600000001</v>
       </c>
       <c r="O9">
-        <v>0.24940206</v>
+        <v>0.24681664</v>
       </c>
       <c r="P9">
-        <v>0.7482061800000001</v>
+        <v>0.7404499200000001</v>
       </c>
       <c r="Q9">
-        <v>0.98820618</v>
+        <v>0.9804499200000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1197148586273578</v>
+        <v>0.1203281581513153</v>
       </c>
       <c r="T9">
-        <v>0.7148131747517397</v>
+        <v>0.7207442498824378</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.78068774678223</v>
+        <v>12.93310177843446</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1137199054992101</v>
+        <v>0.1135654924749774</v>
       </c>
       <c r="C10">
-        <v>19.47965055622405</v>
+        <v>19.31724088696851</v>
       </c>
       <c r="D10">
-        <v>18.95445055622405</v>
+        <v>18.99764088696851</v>
       </c>
       <c r="E10">
-        <v>1.5848</v>
+        <v>1.7904</v>
       </c>
       <c r="F10">
-        <v>1.6448</v>
+        <v>1.8504</v>
       </c>
       <c r="G10">
         <v>2.17</v>
@@ -2107,45 +2107,45 @@
         <v>1.07</v>
       </c>
       <c r="M10">
-        <v>0.08273343999999999</v>
+        <v>0.09585071999999999</v>
       </c>
       <c r="N10">
-        <v>0.9872665600000001</v>
+        <v>0.9741492800000001</v>
       </c>
       <c r="O10">
-        <v>0.24681664</v>
+        <v>0.24353732</v>
       </c>
       <c r="P10">
-        <v>0.7404499200000001</v>
+        <v>0.7306119600000001</v>
       </c>
       <c r="Q10">
-        <v>0.9804499200000001</v>
+        <v>0.9706119600000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1203281581513153</v>
+        <v>0.1209549367856894</v>
       </c>
       <c r="T10">
-        <v>0.7207442498824378</v>
+        <v>0.7268056783127117</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>12.93310177843446</v>
+        <v>11.16319209704424</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1135654924749774</v>
+        <v>0.1133210794507447</v>
       </c>
       <c r="C11">
-        <v>19.31724088696851</v>
+        <v>19.18040860958552</v>
       </c>
       <c r="D11">
-        <v>18.99764088696851</v>
+        <v>19.06640860958553</v>
       </c>
       <c r="E11">
-        <v>1.7904</v>
+        <v>1.996</v>
       </c>
       <c r="F11">
-        <v>1.8504</v>
+        <v>2.056</v>
       </c>
       <c r="G11">
         <v>2.17</v>
@@ -2189,28 +2189,28 @@
         <v>1.07</v>
       </c>
       <c r="M11">
-        <v>0.09585071999999999</v>
+        <v>0.1065008</v>
       </c>
       <c r="N11">
-        <v>0.9741492800000001</v>
+        <v>0.9634992000000001</v>
       </c>
       <c r="O11">
-        <v>0.24353732</v>
+        <v>0.2408748</v>
       </c>
       <c r="P11">
-        <v>0.7306119600000001</v>
+        <v>0.7226244000000001</v>
       </c>
       <c r="Q11">
-        <v>0.9706119600000001</v>
+        <v>0.9626244</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1209549367856894</v>
+        <v>0.1215956438341608</v>
       </c>
       <c r="T11">
-        <v>0.7268056783127117</v>
+        <v>0.7330018051525472</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.16319209704424</v>
+        <v>10.04687288733982</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1133210794507447</v>
+        <v>0.113216916426512</v>
       </c>
       <c r="C12">
-        <v>19.18040860958552</v>
+        <v>19.00426731056594</v>
       </c>
       <c r="D12">
-        <v>19.06640860958553</v>
+        <v>19.09586731056594</v>
       </c>
       <c r="E12">
-        <v>1.996</v>
+        <v>2.2016</v>
       </c>
       <c r="F12">
-        <v>2.056</v>
+        <v>2.2616</v>
       </c>
       <c r="G12">
         <v>2.17</v>
@@ -2271,45 +2271,45 @@
         <v>1.07</v>
       </c>
       <c r="M12">
-        <v>0.1065008</v>
+        <v>0.1209956</v>
       </c>
       <c r="N12">
-        <v>0.9634992</v>
+        <v>0.9490044000000001</v>
       </c>
       <c r="O12">
-        <v>0.2408748</v>
+        <v>0.2372511</v>
       </c>
       <c r="P12">
-        <v>0.7226243999999999</v>
+        <v>0.7117533</v>
       </c>
       <c r="Q12">
-        <v>0.9626243999999999</v>
+        <v>0.9517533</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1215956438341608</v>
+        <v>0.1222507487938338</v>
       </c>
       <c r="T12">
-        <v>0.7330018051525472</v>
+        <v>0.7393371707977725</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.04687288733981</v>
+        <v>8.843296781039973</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.113216916426512</v>
+        <v>0.1129852534022794</v>
       </c>
       <c r="C13">
-        <v>19.00426731056594</v>
+        <v>18.86451221175317</v>
       </c>
       <c r="D13">
-        <v>19.09586731056594</v>
+        <v>19.16171221175317</v>
       </c>
       <c r="E13">
-        <v>2.2016</v>
+        <v>2.4072</v>
       </c>
       <c r="F13">
-        <v>2.2616</v>
+        <v>2.4672</v>
       </c>
       <c r="G13">
         <v>2.17</v>
@@ -2353,28 +2353,28 @@
         <v>1.07</v>
       </c>
       <c r="M13">
-        <v>0.1209956</v>
+        <v>0.1319952</v>
       </c>
       <c r="N13">
-        <v>0.9490044000000001</v>
+        <v>0.9380048000000001</v>
       </c>
       <c r="O13">
-        <v>0.2372511</v>
+        <v>0.2345012</v>
       </c>
       <c r="P13">
-        <v>0.7117533</v>
+        <v>0.7035036000000001</v>
       </c>
       <c r="Q13">
-        <v>0.9517533</v>
+        <v>0.9435036000000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1222507487938338</v>
+        <v>0.1229207425025902</v>
       </c>
       <c r="T13">
-        <v>0.7393371707977725</v>
+        <v>0.7458165220258436</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.843296781039973</v>
+        <v>8.106355382619975</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1129852534022794</v>
+        <v>0.1128315903780467</v>
       </c>
       <c r="C14">
-        <v>18.86451221175317</v>
+        <v>18.70283846549902</v>
       </c>
       <c r="D14">
-        <v>19.16171221175317</v>
+        <v>19.20563846549902</v>
       </c>
       <c r="E14">
-        <v>2.4072</v>
+        <v>2.6128</v>
       </c>
       <c r="F14">
-        <v>2.4672</v>
+        <v>2.6728</v>
       </c>
       <c r="G14">
         <v>2.17</v>
@@ -2435,45 +2435,45 @@
         <v>1.07</v>
       </c>
       <c r="M14">
-        <v>0.1319952</v>
+        <v>0.14513304</v>
       </c>
       <c r="N14">
-        <v>0.9380048000000001</v>
+        <v>0.92486696</v>
       </c>
       <c r="O14">
-        <v>0.2345012</v>
+        <v>0.23121674</v>
       </c>
       <c r="P14">
-        <v>0.7035036000000001</v>
+        <v>0.69365022</v>
       </c>
       <c r="Q14">
-        <v>0.9435036000000001</v>
+        <v>0.93365022</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1229207425025902</v>
+        <v>0.1236061383655709</v>
       </c>
       <c r="T14">
-        <v>0.7458165220258436</v>
+        <v>0.7524448238568588</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.106355382619975</v>
+        <v>7.372545906845194</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1128315903780467</v>
+        <v>0.112605927353814</v>
       </c>
       <c r="C15">
-        <v>18.70283846549902</v>
+        <v>18.56211298532255</v>
       </c>
       <c r="D15">
-        <v>19.20563846549902</v>
+        <v>19.27051298532255</v>
       </c>
       <c r="E15">
-        <v>2.6128</v>
+        <v>2.8184</v>
       </c>
       <c r="F15">
-        <v>2.6728</v>
+        <v>2.8784</v>
       </c>
       <c r="G15">
         <v>2.17</v>
@@ -2517,28 +2517,28 @@
         <v>1.07</v>
       </c>
       <c r="M15">
-        <v>0.14513304</v>
+        <v>0.15629712</v>
       </c>
       <c r="N15">
-        <v>0.92486696</v>
+        <v>0.91370288</v>
       </c>
       <c r="O15">
-        <v>0.23121674</v>
+        <v>0.22842572</v>
       </c>
       <c r="P15">
-        <v>0.69365022</v>
+        <v>0.6852771600000001</v>
       </c>
       <c r="Q15">
-        <v>0.93365022</v>
+        <v>0.92527716</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1236061383655709</v>
+        <v>0.1243074736672256</v>
       </c>
       <c r="T15">
-        <v>0.7524448238568588</v>
+        <v>0.7592272722420839</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.372545906845194</v>
+        <v>6.845935484927681</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.112605927353814</v>
+        <v>0.1123802643295813</v>
       </c>
       <c r="C16">
-        <v>18.56211298532255</v>
+        <v>18.42182726850498</v>
       </c>
       <c r="D16">
-        <v>19.27051298532255</v>
+        <v>19.33582726850498</v>
       </c>
       <c r="E16">
-        <v>2.8184</v>
+        <v>3.024</v>
       </c>
       <c r="F16">
-        <v>2.8784</v>
+        <v>3.084</v>
       </c>
       <c r="G16">
         <v>2.17</v>
@@ -2599,28 +2599,28 @@
         <v>1.07</v>
       </c>
       <c r="M16">
-        <v>0.15629712</v>
+        <v>0.1674612</v>
       </c>
       <c r="N16">
-        <v>0.91370288</v>
+        <v>0.9025388000000001</v>
       </c>
       <c r="O16">
-        <v>0.22842572</v>
+        <v>0.2256347</v>
       </c>
       <c r="P16">
-        <v>0.6852771600000001</v>
+        <v>0.6769041</v>
       </c>
       <c r="Q16">
-        <v>0.92527716</v>
+        <v>0.9169041</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1243074736672256</v>
+        <v>0.125025310975978</v>
       </c>
       <c r="T16">
-        <v>0.7592272722420839</v>
+        <v>0.7661693076481376</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.845935484927681</v>
+        <v>6.389539785932503</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1123802643295813</v>
+        <v>0.1122746013053487</v>
       </c>
       <c r="C17">
-        <v>18.42182726850498</v>
+        <v>18.24696204457149</v>
       </c>
       <c r="D17">
-        <v>19.33582726850498</v>
+        <v>19.36656204457149</v>
       </c>
       <c r="E17">
-        <v>3.024</v>
+        <v>3.2296</v>
       </c>
       <c r="F17">
-        <v>3.084</v>
+        <v>3.2896</v>
       </c>
       <c r="G17">
         <v>2.17</v>
@@ -2681,45 +2681,45 @@
         <v>1.07</v>
       </c>
       <c r="M17">
-        <v>0.1674612</v>
+        <v>0.18191488</v>
       </c>
       <c r="N17">
-        <v>0.9025388000000001</v>
+        <v>0.8880851200000001</v>
       </c>
       <c r="O17">
-        <v>0.2256347</v>
+        <v>0.22202128</v>
       </c>
       <c r="P17">
-        <v>0.6769041</v>
+        <v>0.6660638400000001</v>
       </c>
       <c r="Q17">
-        <v>0.9169041</v>
+        <v>0.9060638400000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.125025310975978</v>
+        <v>0.1257602396492246</v>
       </c>
       <c r="T17">
-        <v>0.7661693076481376</v>
+        <v>0.7732766296114784</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.389539785932504</v>
+        <v>5.881871785309701</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1122746013053487</v>
+        <v>0.112056438281116</v>
       </c>
       <c r="C18">
-        <v>18.24696204457149</v>
+        <v>18.1051304549214</v>
       </c>
       <c r="D18">
-        <v>19.36656204457149</v>
+        <v>19.4303304549214</v>
       </c>
       <c r="E18">
-        <v>3.2296</v>
+        <v>3.4352</v>
       </c>
       <c r="F18">
-        <v>3.2896</v>
+        <v>3.4952</v>
       </c>
       <c r="G18">
         <v>2.17</v>
@@ -2763,28 +2763,28 @@
         <v>1.07</v>
       </c>
       <c r="M18">
-        <v>0.18191488</v>
+        <v>0.19328456</v>
       </c>
       <c r="N18">
-        <v>0.8880851200000001</v>
+        <v>0.87671544</v>
       </c>
       <c r="O18">
-        <v>0.22202128</v>
+        <v>0.21917886</v>
       </c>
       <c r="P18">
-        <v>0.6660638400000001</v>
+        <v>0.65753658</v>
       </c>
       <c r="Q18">
-        <v>0.9060638400000001</v>
+        <v>0.89753658</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1257602396492246</v>
+        <v>0.1265128774471277</v>
       </c>
       <c r="T18">
-        <v>0.7732766296114784</v>
+        <v>0.7805552123450203</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.881871785309701</v>
+        <v>5.535879327350306</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.112056438281116</v>
+        <v>0.1118382752568833</v>
       </c>
       <c r="C19">
-        <v>18.1051304549214</v>
+        <v>17.96372019393861</v>
       </c>
       <c r="D19">
-        <v>19.4303304549214</v>
+        <v>19.49452019393861</v>
       </c>
       <c r="E19">
-        <v>3.4352</v>
+        <v>3.6408</v>
       </c>
       <c r="F19">
-        <v>3.4952</v>
+        <v>3.7008</v>
       </c>
       <c r="G19">
         <v>2.17</v>
@@ -2845,28 +2845,28 @@
         <v>1.07</v>
       </c>
       <c r="M19">
-        <v>0.19328456</v>
+        <v>0.20465424</v>
       </c>
       <c r="N19">
-        <v>0.87671544</v>
+        <v>0.8653457600000001</v>
       </c>
       <c r="O19">
-        <v>0.21917886</v>
+        <v>0.21633644</v>
       </c>
       <c r="P19">
-        <v>0.65753658</v>
+        <v>0.64900932</v>
       </c>
       <c r="Q19">
-        <v>0.89753658</v>
+        <v>0.88900932</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1265128774471277</v>
+        <v>0.1272838722644918</v>
       </c>
       <c r="T19">
-        <v>0.7805552123450203</v>
+        <v>0.7880113214866972</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.535879327350306</v>
+        <v>5.228330475830846</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1118382752568833</v>
+        <v>0.1116201122326506</v>
       </c>
       <c r="C20">
-        <v>17.96372019393861</v>
+        <v>17.82273545114816</v>
       </c>
       <c r="D20">
-        <v>19.49452019393861</v>
+        <v>19.55913545114816</v>
       </c>
       <c r="E20">
-        <v>3.6408</v>
+        <v>3.8464</v>
       </c>
       <c r="F20">
-        <v>3.7008</v>
+        <v>3.9064</v>
       </c>
       <c r="G20">
         <v>2.17</v>
@@ -2927,28 +2927,28 @@
         <v>1.07</v>
       </c>
       <c r="M20">
-        <v>0.20465424</v>
+        <v>0.21602392</v>
       </c>
       <c r="N20">
-        <v>0.8653457600000001</v>
+        <v>0.85397608</v>
       </c>
       <c r="O20">
-        <v>0.21633644</v>
+        <v>0.21349402</v>
       </c>
       <c r="P20">
-        <v>0.64900932</v>
+        <v>0.6404820600000001</v>
       </c>
       <c r="Q20">
-        <v>0.88900932</v>
+        <v>0.8804820600000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1272838722644918</v>
+        <v>0.1280739039909267</v>
       </c>
       <c r="T20">
-        <v>0.7880113214866972</v>
+        <v>0.7956515320886626</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.228330475830846</v>
+        <v>4.953155187629222</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1116201122326506</v>
+        <v>0.1114019492084179</v>
       </c>
       <c r="C21">
-        <v>17.82273545114816</v>
+        <v>17.68218047180513</v>
       </c>
       <c r="D21">
-        <v>19.55913545114816</v>
+        <v>19.62418047180513</v>
       </c>
       <c r="E21">
-        <v>3.8464</v>
+        <v>4.052</v>
       </c>
       <c r="F21">
-        <v>3.9064</v>
+        <v>4.112</v>
       </c>
       <c r="G21">
         <v>2.17</v>
@@ -3009,28 +3009,28 @@
         <v>1.07</v>
       </c>
       <c r="M21">
-        <v>0.21602392</v>
+        <v>0.2273936</v>
       </c>
       <c r="N21">
-        <v>0.85397608</v>
+        <v>0.8426064000000001</v>
       </c>
       <c r="O21">
-        <v>0.21349402</v>
+        <v>0.2106516</v>
       </c>
       <c r="P21">
-        <v>0.6404820600000001</v>
+        <v>0.6319548</v>
       </c>
       <c r="Q21">
-        <v>0.8804820600000001</v>
+        <v>0.8719548</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1280739039909267</v>
+        <v>0.1288836865105224</v>
       </c>
       <c r="T21">
-        <v>0.7956515320886626</v>
+        <v>0.8034827479556769</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.953155187629222</v>
+        <v>4.705497428247761</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1114019492084179</v>
+        <v>0.1115775361841853</v>
       </c>
       <c r="C22">
-        <v>17.68218047180513</v>
+        <v>17.42419555894814</v>
       </c>
       <c r="D22">
-        <v>19.62418047180513</v>
+        <v>19.57179555894814</v>
       </c>
       <c r="E22">
-        <v>4.052</v>
+        <v>4.257600000000001</v>
       </c>
       <c r="F22">
-        <v>4.112</v>
+        <v>4.317600000000001</v>
       </c>
       <c r="G22">
         <v>2.17</v>
@@ -3091,45 +3091,45 @@
         <v>1.07</v>
       </c>
       <c r="M22">
-        <v>0.2273936</v>
+        <v>0.24955728</v>
       </c>
       <c r="N22">
-        <v>0.8426064000000001</v>
+        <v>0.82044272</v>
       </c>
       <c r="O22">
-        <v>0.2106516</v>
+        <v>0.20511068</v>
       </c>
       <c r="P22">
-        <v>0.6319548</v>
+        <v>0.61533204</v>
       </c>
       <c r="Q22">
-        <v>0.8719548</v>
+        <v>0.85533204</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1288836865105224</v>
+        <v>0.1297139698533991</v>
       </c>
       <c r="T22">
-        <v>0.8034827479556769</v>
+        <v>0.8115122224522359</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.705497428247761</v>
+        <v>4.28759281235955</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1115775361841853</v>
+        <v>0.1113781231599526</v>
       </c>
       <c r="C23">
-        <v>17.42419555894814</v>
+        <v>17.27811039032802</v>
       </c>
       <c r="D23">
-        <v>19.57179555894814</v>
+        <v>19.63131039032802</v>
       </c>
       <c r="E23">
-        <v>4.2576</v>
+        <v>4.463200000000001</v>
       </c>
       <c r="F23">
-        <v>4.3176</v>
+        <v>4.5232</v>
       </c>
       <c r="G23">
         <v>2.17</v>
@@ -3173,28 +3173,28 @@
         <v>1.07</v>
       </c>
       <c r="M23">
-        <v>0.24955728</v>
+        <v>0.26144096</v>
       </c>
       <c r="N23">
-        <v>0.8204427200000001</v>
+        <v>0.80855904</v>
       </c>
       <c r="O23">
-        <v>0.20511068</v>
+        <v>0.20213976</v>
       </c>
       <c r="P23">
-        <v>0.6153320400000001</v>
+        <v>0.60641928</v>
       </c>
       <c r="Q23">
-        <v>0.8553320400000001</v>
+        <v>0.84641928</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1297139698533991</v>
+        <v>0.1305655425127597</v>
       </c>
       <c r="T23">
-        <v>0.8115122224522359</v>
+        <v>0.8197475809102451</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.287592812359552</v>
+        <v>4.092702229979572</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1113781231599526</v>
+        <v>0.1117824601357199</v>
       </c>
       <c r="C24">
-        <v>17.27811039032802</v>
+        <v>16.95221077347154</v>
       </c>
       <c r="D24">
-        <v>19.63131039032802</v>
+        <v>19.51101077347154</v>
       </c>
       <c r="E24">
-        <v>4.463200000000001</v>
+        <v>4.6688</v>
       </c>
       <c r="F24">
-        <v>4.5232</v>
+        <v>4.7288</v>
       </c>
       <c r="G24">
         <v>2.17</v>
@@ -3255,45 +3255,45 @@
         <v>1.07</v>
       </c>
       <c r="M24">
-        <v>0.26144096</v>
+        <v>0.28987544</v>
       </c>
       <c r="N24">
-        <v>0.80855904</v>
+        <v>0.7801245600000001</v>
       </c>
       <c r="O24">
-        <v>0.20213976</v>
+        <v>0.19503114</v>
       </c>
       <c r="P24">
-        <v>0.60641928</v>
+        <v>0.5850934200000001</v>
       </c>
       <c r="Q24">
-        <v>0.84641928</v>
+        <v>0.8250934200000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1305655425127597</v>
+        <v>0.1314392339424934</v>
       </c>
       <c r="T24">
-        <v>0.8197475809102451</v>
+        <v>0.8281968447827482</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.092702229979572</v>
+        <v>3.69124062390384</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1117824601357199</v>
+        <v>0.1116092971114872</v>
       </c>
       <c r="C25">
-        <v>16.95221077347154</v>
+        <v>16.79794980579166</v>
       </c>
       <c r="D25">
-        <v>19.51101077347154</v>
+        <v>19.56234980579166</v>
       </c>
       <c r="E25">
-        <v>4.6688</v>
+        <v>4.874400000000001</v>
       </c>
       <c r="F25">
-        <v>4.7288</v>
+        <v>4.9344</v>
       </c>
       <c r="G25">
         <v>2.17</v>
@@ -3337,28 +3337,28 @@
         <v>1.07</v>
       </c>
       <c r="M25">
-        <v>0.28987544</v>
+        <v>0.30247872</v>
       </c>
       <c r="N25">
-        <v>0.7801245600000001</v>
+        <v>0.76752128</v>
       </c>
       <c r="O25">
-        <v>0.19503114</v>
+        <v>0.19188032</v>
       </c>
       <c r="P25">
-        <v>0.5850934200000001</v>
+        <v>0.57564096</v>
       </c>
       <c r="Q25">
-        <v>0.8250934200000001</v>
+        <v>0.81564096</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1314392339424934</v>
+        <v>0.1323359172519569</v>
       </c>
       <c r="T25">
-        <v>0.8281968447827482</v>
+        <v>0.8368684577045277</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.69124062390384</v>
+        <v>3.537438931241179</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1116092971114872</v>
+        <v>0.1119611340872545</v>
       </c>
       <c r="C26">
-        <v>16.79794980579166</v>
+        <v>16.48831957581563</v>
       </c>
       <c r="D26">
-        <v>19.56234980579166</v>
+        <v>19.45831957581563</v>
       </c>
       <c r="E26">
-        <v>4.8744</v>
+        <v>5.08</v>
       </c>
       <c r="F26">
-        <v>4.934399999999999</v>
+        <v>5.14</v>
       </c>
       <c r="G26">
         <v>2.17</v>
@@ -3419,45 +3419,45 @@
         <v>1.07</v>
       </c>
       <c r="M26">
-        <v>0.30247872</v>
+        <v>0.329474</v>
       </c>
       <c r="N26">
-        <v>0.7675212800000001</v>
+        <v>0.740526</v>
       </c>
       <c r="O26">
-        <v>0.19188032</v>
+        <v>0.1851315</v>
       </c>
       <c r="P26">
-        <v>0.5756409600000001</v>
+        <v>0.5553945</v>
       </c>
       <c r="Q26">
-        <v>0.8156409600000001</v>
+        <v>0.7953945</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1323359172519569</v>
+        <v>0.1332565121163394</v>
       </c>
       <c r="T26">
-        <v>0.8368684577045277</v>
+        <v>0.8457713136375545</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.53743893124118</v>
+        <v>3.247600721149469</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1119611340872545</v>
+        <v>0.1118089710630219</v>
       </c>
       <c r="C27">
-        <v>16.48831957581563</v>
+        <v>16.32757464180832</v>
       </c>
       <c r="D27">
-        <v>19.45831957581563</v>
+        <v>19.50317464180833</v>
       </c>
       <c r="E27">
-        <v>5.08</v>
+        <v>5.285600000000001</v>
       </c>
       <c r="F27">
-        <v>5.14</v>
+        <v>5.3456</v>
       </c>
       <c r="G27">
         <v>2.17</v>
@@ -3501,28 +3501,28 @@
         <v>1.07</v>
       </c>
       <c r="M27">
-        <v>0.329474</v>
+        <v>0.34265296</v>
       </c>
       <c r="N27">
-        <v>0.740526</v>
+        <v>0.7273470400000001</v>
       </c>
       <c r="O27">
-        <v>0.1851315</v>
+        <v>0.18183676</v>
       </c>
       <c r="P27">
-        <v>0.5553945</v>
+        <v>0.54551028</v>
       </c>
       <c r="Q27">
-        <v>0.7953945</v>
+        <v>0.78551028</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1332565121163394</v>
+        <v>0.1342019879230025</v>
       </c>
       <c r="T27">
-        <v>0.8457713136375545</v>
+        <v>0.8549147872985011</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.247600721149469</v>
+        <v>3.122693001105258</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1118089710630219</v>
+        <v>0.1116568080387892</v>
       </c>
       <c r="C28">
-        <v>16.32757464180832</v>
+        <v>16.16703698424508</v>
       </c>
       <c r="D28">
-        <v>19.50317464180833</v>
+        <v>19.54823698424508</v>
       </c>
       <c r="E28">
-        <v>5.285600000000001</v>
+        <v>5.4912</v>
       </c>
       <c r="F28">
-        <v>5.3456</v>
+        <v>5.5512</v>
       </c>
       <c r="G28">
         <v>2.17</v>
@@ -3583,28 +3583,28 @@
         <v>1.07</v>
       </c>
       <c r="M28">
-        <v>0.34265296</v>
+        <v>0.35583192</v>
       </c>
       <c r="N28">
-        <v>0.7273470400000001</v>
+        <v>0.7141680800000001</v>
       </c>
       <c r="O28">
-        <v>0.18183676</v>
+        <v>0.17854202</v>
       </c>
       <c r="P28">
-        <v>0.54551028</v>
+        <v>0.53562606</v>
       </c>
       <c r="Q28">
-        <v>0.78551028</v>
+        <v>0.77562606</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1342019879230025</v>
+        <v>0.1351733671764236</v>
       </c>
       <c r="T28">
-        <v>0.8549147872985011</v>
+        <v>0.8643087670871449</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.122693001105258</v>
+        <v>3.007037704768027</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1116568080387892</v>
+        <v>0.1131426450145565</v>
       </c>
       <c r="C29">
-        <v>16.16703698424508</v>
+        <v>15.53012791825911</v>
       </c>
       <c r="D29">
-        <v>19.54823698424508</v>
+        <v>19.11692791825911</v>
       </c>
       <c r="E29">
-        <v>5.4912</v>
+        <v>5.696800000000001</v>
       </c>
       <c r="F29">
-        <v>5.5512</v>
+        <v>5.7568</v>
       </c>
       <c r="G29">
         <v>2.17</v>
@@ -3665,45 +3665,45 @@
         <v>1.07</v>
       </c>
       <c r="M29">
-        <v>0.35583192</v>
+        <v>0.41391392</v>
       </c>
       <c r="N29">
-        <v>0.7141680800000001</v>
+        <v>0.65608608</v>
       </c>
       <c r="O29">
-        <v>0.17854202</v>
+        <v>0.16402152</v>
       </c>
       <c r="P29">
-        <v>0.53562606</v>
+        <v>0.49206456</v>
       </c>
       <c r="Q29">
-        <v>0.77562606</v>
+        <v>0.73206456</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1351733671764236</v>
+        <v>0.136171729186884</v>
       </c>
       <c r="T29">
-        <v>0.8643087670871449</v>
+        <v>0.8739636907588064</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.007037704768027</v>
+        <v>2.585078559329437</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1131426450145565</v>
+        <v>0.1138972319903238</v>
       </c>
       <c r="C30">
-        <v>15.53012791825911</v>
+        <v>15.11269280540385</v>
       </c>
       <c r="D30">
-        <v>19.11692791825911</v>
+        <v>18.90509280540385</v>
       </c>
       <c r="E30">
-        <v>5.696800000000001</v>
+        <v>5.902400000000001</v>
       </c>
       <c r="F30">
-        <v>5.7568</v>
+        <v>5.962400000000001</v>
       </c>
       <c r="G30">
         <v>2.17</v>
@@ -3747,45 +3747,45 @@
         <v>1.07</v>
       </c>
       <c r="M30">
-        <v>0.41391392</v>
+        <v>0.4519499200000001</v>
       </c>
       <c r="N30">
-        <v>0.65608608</v>
+        <v>0.6180500799999999</v>
       </c>
       <c r="O30">
-        <v>0.16402152</v>
+        <v>0.15451252</v>
       </c>
       <c r="P30">
-        <v>0.49206456</v>
+        <v>0.46353756</v>
       </c>
       <c r="Q30">
-        <v>0.73206456</v>
+        <v>0.70353756</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.136171729186884</v>
+        <v>0.1371982140708786</v>
       </c>
       <c r="T30">
-        <v>0.8739636907588064</v>
+        <v>0.8838905841113598</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.585078559329437</v>
+        <v>2.367518949887191</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1138972319903238</v>
+        <v>0.1138328189660911</v>
       </c>
       <c r="C31">
-        <v>15.11269280540385</v>
+        <v>14.92499202256847</v>
       </c>
       <c r="D31">
-        <v>18.90509280540385</v>
+        <v>18.92299202256847</v>
       </c>
       <c r="E31">
-        <v>5.902399999999999</v>
+        <v>6.108</v>
       </c>
       <c r="F31">
-        <v>5.962399999999999</v>
+        <v>6.167999999999999</v>
       </c>
       <c r="G31">
         <v>2.17</v>
@@ -3829,28 +3829,28 @@
         <v>1.07</v>
       </c>
       <c r="M31">
-        <v>0.4519499199999999</v>
+        <v>0.4675344</v>
       </c>
       <c r="N31">
-        <v>0.6180500800000002</v>
+        <v>0.6024656000000002</v>
       </c>
       <c r="O31">
-        <v>0.15451252</v>
+        <v>0.1506164</v>
       </c>
       <c r="P31">
-        <v>0.4635375600000001</v>
+        <v>0.4518492000000001</v>
       </c>
       <c r="Q31">
-        <v>0.7035375600000001</v>
+        <v>0.6918492000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1371982140708786</v>
+        <v>0.1382540270944159</v>
       </c>
       <c r="T31">
-        <v>0.8838905841113598</v>
+        <v>0.8941011029882719</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.367518949887192</v>
+        <v>2.288601651557618</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1138328189660911</v>
+        <v>0.1137684059418585</v>
       </c>
       <c r="C32">
-        <v>14.92499202256847</v>
+        <v>14.73732516557535</v>
       </c>
       <c r="D32">
-        <v>18.92299202256847</v>
+        <v>18.94092516557534</v>
       </c>
       <c r="E32">
-        <v>6.108</v>
+        <v>6.3136</v>
       </c>
       <c r="F32">
-        <v>6.167999999999999</v>
+        <v>6.3736</v>
       </c>
       <c r="G32">
         <v>2.17</v>
@@ -3911,28 +3911,28 @@
         <v>1.07</v>
       </c>
       <c r="M32">
-        <v>0.4675344</v>
+        <v>0.48311888</v>
       </c>
       <c r="N32">
-        <v>0.6024656000000002</v>
+        <v>0.58688112</v>
       </c>
       <c r="O32">
-        <v>0.1506164</v>
+        <v>0.14672028</v>
       </c>
       <c r="P32">
-        <v>0.4518492000000001</v>
+        <v>0.44016084</v>
       </c>
       <c r="Q32">
-        <v>0.6918492000000001</v>
+        <v>0.68016084</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1382540270944159</v>
+        <v>0.1393404433939978</v>
       </c>
       <c r="T32">
-        <v>0.8941011029882719</v>
+        <v>0.9046075789340801</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.288601651557618</v>
+        <v>2.214775791829953</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1137684059418585</v>
+        <v>0.1137039929176258</v>
       </c>
       <c r="C33">
-        <v>14.73732516557535</v>
+        <v>14.54969233096957</v>
       </c>
       <c r="D33">
-        <v>18.94092516557534</v>
+        <v>18.95889233096957</v>
       </c>
       <c r="E33">
-        <v>6.3136</v>
+        <v>6.519200000000001</v>
       </c>
       <c r="F33">
-        <v>6.3736</v>
+        <v>6.5792</v>
       </c>
       <c r="G33">
         <v>2.17</v>
@@ -3993,28 +3993,28 @@
         <v>1.07</v>
       </c>
       <c r="M33">
-        <v>0.48311888</v>
+        <v>0.49870336</v>
       </c>
       <c r="N33">
-        <v>0.58688112</v>
+        <v>0.57129664</v>
       </c>
       <c r="O33">
-        <v>0.14672028</v>
+        <v>0.14282416</v>
       </c>
       <c r="P33">
-        <v>0.44016084</v>
+        <v>0.42847248</v>
       </c>
       <c r="Q33">
-        <v>0.68016084</v>
+        <v>0.66847248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1393404433939978</v>
+        <v>0.1404588131141556</v>
       </c>
       <c r="T33">
-        <v>0.9046075789340801</v>
+        <v>0.9154230688782944</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.214775791829953</v>
+        <v>2.145564048335267</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1137039929176258</v>
+        <v>0.1136395798933931</v>
       </c>
       <c r="C34">
-        <v>14.54969233096957</v>
+        <v>14.36209361566294</v>
       </c>
       <c r="D34">
-        <v>18.95889233096957</v>
+        <v>18.97689361566294</v>
       </c>
       <c r="E34">
-        <v>6.519200000000001</v>
+        <v>6.7248</v>
       </c>
       <c r="F34">
-        <v>6.5792</v>
+        <v>6.7848</v>
       </c>
       <c r="G34">
         <v>2.17</v>
@@ -4075,28 +4075,28 @@
         <v>1.07</v>
       </c>
       <c r="M34">
-        <v>0.49870336</v>
+        <v>0.5142878400000001</v>
       </c>
       <c r="N34">
-        <v>0.57129664</v>
+        <v>0.55571216</v>
       </c>
       <c r="O34">
-        <v>0.14282416</v>
+        <v>0.13892804</v>
       </c>
       <c r="P34">
-        <v>0.42847248</v>
+        <v>0.41678412</v>
       </c>
       <c r="Q34">
-        <v>0.66847248</v>
+        <v>0.65678412</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1404588131141556</v>
+        <v>0.1416105670050644</v>
       </c>
       <c r="T34">
-        <v>0.9154230688782944</v>
+        <v>0.9265614092686046</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.145564048335267</v>
+        <v>2.080546955961471</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1136395798933931</v>
+        <v>0.1135751668691604</v>
       </c>
       <c r="C35">
-        <v>14.36209361566294</v>
+        <v>14.17452911693564</v>
       </c>
       <c r="D35">
-        <v>18.97689361566294</v>
+        <v>18.99492911693565</v>
       </c>
       <c r="E35">
-        <v>6.7248</v>
+        <v>6.930400000000001</v>
       </c>
       <c r="F35">
-        <v>6.7848</v>
+        <v>6.9904</v>
       </c>
       <c r="G35">
         <v>2.17</v>
@@ -4157,28 +4157,28 @@
         <v>1.07</v>
       </c>
       <c r="M35">
-        <v>0.5142878400000001</v>
+        <v>0.5298723200000001</v>
       </c>
       <c r="N35">
-        <v>0.55571216</v>
+        <v>0.54012768</v>
       </c>
       <c r="O35">
-        <v>0.13892804</v>
+        <v>0.13503192</v>
       </c>
       <c r="P35">
-        <v>0.41678412</v>
+        <v>0.40509576</v>
       </c>
       <c r="Q35">
-        <v>0.65678412</v>
+        <v>0.64509576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1416105670050644</v>
+        <v>0.142797222529031</v>
       </c>
       <c r="T35">
-        <v>0.9265614092686046</v>
+        <v>0.9380372751252879</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.080546955961471</v>
+        <v>2.019354398433192</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1135751668691604</v>
+        <v>0.1172382538449278</v>
       </c>
       <c r="C36">
-        <v>14.17452911693564</v>
+        <v>12.99494006052744</v>
       </c>
       <c r="D36">
-        <v>18.99492911693565</v>
+        <v>18.02094006052745</v>
       </c>
       <c r="E36">
-        <v>6.930400000000001</v>
+        <v>7.136000000000001</v>
       </c>
       <c r="F36">
-        <v>6.9904</v>
+        <v>7.196000000000001</v>
       </c>
       <c r="G36">
         <v>2.17</v>
@@ -4239,45 +4239,45 @@
         <v>1.07</v>
       </c>
       <c r="M36">
-        <v>0.5298723200000001</v>
+        <v>0.64764</v>
       </c>
       <c r="N36">
-        <v>0.54012768</v>
+        <v>0.4223600000000001</v>
       </c>
       <c r="O36">
-        <v>0.13503192</v>
+        <v>0.10559</v>
       </c>
       <c r="P36">
-        <v>0.40509576</v>
+        <v>0.3167700000000001</v>
       </c>
       <c r="Q36">
-        <v>0.64509576</v>
+        <v>0.55677</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.142797222529031</v>
+        <v>0.1440203905306581</v>
       </c>
       <c r="T36">
-        <v>0.9380372751252879</v>
+        <v>0.9498662445467921</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.019354398433192</v>
+        <v>1.652152430362547</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1172382538449278</v>
+        <v>0.1172803408206951</v>
       </c>
       <c r="C37">
-        <v>12.99494006052744</v>
+        <v>12.77872949461627</v>
       </c>
       <c r="D37">
-        <v>18.02094006052745</v>
+        <v>18.01032949461627</v>
       </c>
       <c r="E37">
-        <v>7.136000000000001</v>
+        <v>7.341600000000001</v>
       </c>
       <c r="F37">
-        <v>7.196000000000001</v>
+        <v>7.4016</v>
       </c>
       <c r="G37">
         <v>2.17</v>
@@ -4321,28 +4321,28 @@
         <v>1.07</v>
       </c>
       <c r="M37">
-        <v>0.64764</v>
+        <v>0.666144</v>
       </c>
       <c r="N37">
-        <v>0.4223600000000001</v>
+        <v>0.4038560000000001</v>
       </c>
       <c r="O37">
-        <v>0.10559</v>
+        <v>0.100964</v>
       </c>
       <c r="P37">
-        <v>0.3167700000000001</v>
+        <v>0.3028920000000001</v>
       </c>
       <c r="Q37">
-        <v>0.55677</v>
+        <v>0.542892</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1440203905306581</v>
+        <v>0.1452817825323361</v>
       </c>
       <c r="T37">
-        <v>0.9498662445467921</v>
+        <v>0.9620648692627183</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.652152430362547</v>
+        <v>1.606259307296921</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1172803408206951</v>
+        <v>0.1173224277964624</v>
       </c>
       <c r="C38">
-        <v>12.77872949461627</v>
+        <v>12.56253141616235</v>
       </c>
       <c r="D38">
-        <v>18.01032949461626</v>
+        <v>17.99973141616235</v>
       </c>
       <c r="E38">
-        <v>7.3416</v>
+        <v>7.5472</v>
       </c>
       <c r="F38">
-        <v>7.401599999999999</v>
+        <v>7.6072</v>
       </c>
       <c r="G38">
         <v>2.17</v>
@@ -4403,28 +4403,28 @@
         <v>1.07</v>
       </c>
       <c r="M38">
-        <v>0.666144</v>
+        <v>0.6846479999999999</v>
       </c>
       <c r="N38">
-        <v>0.4038560000000001</v>
+        <v>0.3853520000000001</v>
       </c>
       <c r="O38">
-        <v>0.100964</v>
+        <v>0.09633800000000003</v>
       </c>
       <c r="P38">
-        <v>0.3028920000000001</v>
+        <v>0.2890140000000001</v>
       </c>
       <c r="Q38">
-        <v>0.542892</v>
+        <v>0.5290140000000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1452817825323361</v>
+        <v>0.1465832187245435</v>
       </c>
       <c r="T38">
-        <v>0.9620648692627183</v>
+        <v>0.9746507519061343</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.606259307296921</v>
+        <v>1.562846893586193</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1173224277964624</v>
+        <v>0.1173645147722297</v>
       </c>
       <c r="C39">
-        <v>12.56253141616235</v>
+        <v>12.34634580313415</v>
       </c>
       <c r="D39">
-        <v>17.99973141616235</v>
+        <v>17.98914580313414</v>
       </c>
       <c r="E39">
-        <v>7.5472</v>
+        <v>7.7528</v>
       </c>
       <c r="F39">
-        <v>7.6072</v>
+        <v>7.812799999999999</v>
       </c>
       <c r="G39">
         <v>2.17</v>
@@ -4485,28 +4485,28 @@
         <v>1.07</v>
       </c>
       <c r="M39">
-        <v>0.6846479999999999</v>
+        <v>0.7031519999999999</v>
       </c>
       <c r="N39">
-        <v>0.3853520000000001</v>
+        <v>0.3668480000000002</v>
       </c>
       <c r="O39">
-        <v>0.09633800000000003</v>
+        <v>0.09171200000000004</v>
       </c>
       <c r="P39">
-        <v>0.2890140000000001</v>
+        <v>0.2751360000000002</v>
       </c>
       <c r="Q39">
-        <v>0.5290140000000001</v>
+        <v>0.5151360000000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1465832187245435</v>
+        <v>0.1479266367294028</v>
       </c>
       <c r="T39">
-        <v>0.9746507519061343</v>
+        <v>0.9876426307638541</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.562846893586193</v>
+        <v>1.521719343754978</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1173645147722297</v>
+        <v>0.1359435802782344</v>
       </c>
       <c r="C40">
-        <v>12.34634580313415</v>
+        <v>8.433088338876551</v>
       </c>
       <c r="D40">
-        <v>17.98914580313414</v>
+        <v>14.28148833887655</v>
       </c>
       <c r="E40">
-        <v>7.7528</v>
+        <v>7.9584</v>
       </c>
       <c r="F40">
-        <v>7.812799999999999</v>
+        <v>8.0184</v>
       </c>
       <c r="G40">
         <v>2.17</v>
@@ -4567,45 +4567,45 @@
         <v>1.07</v>
       </c>
       <c r="M40">
-        <v>0.7031519999999999</v>
+        <v>1.17710112</v>
       </c>
       <c r="N40">
-        <v>0.3668480000000002</v>
+        <v>-0.10710112</v>
       </c>
       <c r="O40">
-        <v>0.09171200000000004</v>
+        <v>-0.02677528000000001</v>
       </c>
       <c r="P40">
-        <v>0.2751360000000002</v>
+        <v>-0.08032584000000004</v>
       </c>
       <c r="Q40">
-        <v>0.5151360000000001</v>
+        <v>0.15967416</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1479266367294028</v>
+        <v>0.1503316076513762</v>
       </c>
       <c r="T40">
-        <v>0.9876426307638541</v>
+        <v>1.010900537656274</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.25</v>
+        <v>0.2272532031912432</v>
       </c>
       <c r="W40">
-        <v>0.0675</v>
+        <v>0.1134392297715255</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.521719343754978</v>
+        <v>0.9090128127649729</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1359435802782344</v>
+        <v>0.1369535802782344</v>
       </c>
       <c r="C41">
-        <v>8.433088338876551</v>
+        <v>8.069246576147794</v>
       </c>
       <c r="D41">
-        <v>14.28148833887655</v>
+        <v>14.12324657614779</v>
       </c>
       <c r="E41">
-        <v>7.9584</v>
+        <v>8.164</v>
       </c>
       <c r="F41">
-        <v>8.0184</v>
+        <v>8.224</v>
       </c>
       <c r="G41">
         <v>2.17</v>
@@ -4649,37 +4649,37 @@
         <v>1.07</v>
       </c>
       <c r="M41">
-        <v>1.17710112</v>
+        <v>1.2072832</v>
       </c>
       <c r="N41">
-        <v>-0.10710112</v>
+        <v>-0.1372832000000002</v>
       </c>
       <c r="O41">
-        <v>-0.02677528000000001</v>
+        <v>-0.03432080000000004</v>
       </c>
       <c r="P41">
-        <v>-0.08032584000000004</v>
+        <v>-0.1029624000000001</v>
       </c>
       <c r="Q41">
-        <v>0.15967416</v>
+        <v>0.1370375999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1503316076513762</v>
+        <v>0.1520738011122325</v>
       </c>
       <c r="T41">
-        <v>1.010900537656274</v>
+        <v>1.027748879950545</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2272532031912432</v>
+        <v>0.2215718731114621</v>
       </c>
       <c r="W41">
-        <v>0.1134392297715255</v>
+        <v>0.1142732490272374</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9090128127649729</v>
+        <v>0.8862874924458486</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1369535802782344</v>
+        <v>0.1379635802782344</v>
       </c>
       <c r="C42">
-        <v>8.069246576147794</v>
+        <v>7.708873085373611</v>
       </c>
       <c r="D42">
-        <v>14.12324657614779</v>
+        <v>13.96847308537361</v>
       </c>
       <c r="E42">
-        <v>8.164</v>
+        <v>8.3696</v>
       </c>
       <c r="F42">
-        <v>8.224</v>
+        <v>8.429600000000001</v>
       </c>
       <c r="G42">
         <v>2.17</v>
@@ -4731,37 +4731,37 @@
         <v>1.07</v>
       </c>
       <c r="M42">
-        <v>1.2072832</v>
+        <v>1.23746528</v>
       </c>
       <c r="N42">
-        <v>-0.1372832000000002</v>
+        <v>-0.16746528</v>
       </c>
       <c r="O42">
-        <v>-0.03432080000000004</v>
+        <v>-0.04186632000000001</v>
       </c>
       <c r="P42">
-        <v>-0.1029624000000001</v>
+        <v>-0.12559896</v>
       </c>
       <c r="Q42">
-        <v>0.1370375999999999</v>
+        <v>0.11440104</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1520738011122325</v>
+        <v>0.1538750519785415</v>
       </c>
       <c r="T42">
-        <v>1.027748879950545</v>
+        <v>1.045168352492079</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2215718731114621</v>
+        <v>0.2161676810843533</v>
       </c>
       <c r="W42">
-        <v>0.1142732490272374</v>
+        <v>0.1150665844168169</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8862874924458486</v>
+        <v>0.8646707243374133</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1379635802782344</v>
+        <v>0.1389735802782344</v>
       </c>
       <c r="C43">
-        <v>7.708873085373611</v>
+        <v>7.35185507852985</v>
       </c>
       <c r="D43">
-        <v>13.96847308537361</v>
+        <v>13.81705507852985</v>
       </c>
       <c r="E43">
-        <v>8.3696</v>
+        <v>8.575200000000001</v>
       </c>
       <c r="F43">
-        <v>8.429600000000001</v>
+        <v>8.635200000000001</v>
       </c>
       <c r="G43">
         <v>2.17</v>
@@ -4813,37 +4813,37 @@
         <v>1.07</v>
       </c>
       <c r="M43">
-        <v>1.23746528</v>
+        <v>1.26764736</v>
       </c>
       <c r="N43">
-        <v>-0.16746528</v>
+        <v>-0.1976473600000002</v>
       </c>
       <c r="O43">
-        <v>-0.04186632000000001</v>
+        <v>-0.04941184000000004</v>
       </c>
       <c r="P43">
-        <v>-0.12559896</v>
+        <v>-0.1482355200000001</v>
       </c>
       <c r="Q43">
-        <v>0.11440104</v>
+        <v>0.09176447999999987</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1538750519785415</v>
+        <v>0.1557384149436888</v>
       </c>
       <c r="T43">
-        <v>1.045168352492079</v>
+        <v>1.063188496500564</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2161676810843533</v>
+        <v>0.2110208315347258</v>
       </c>
       <c r="W43">
-        <v>0.1150665844168169</v>
+        <v>0.1158221419307023</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8646707243374133</v>
+        <v>0.8440833261389034</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1389735802782344</v>
+        <v>0.1399835802782344</v>
       </c>
       <c r="C44">
-        <v>7.351855078529852</v>
+        <v>6.998084605629062</v>
       </c>
       <c r="D44">
-        <v>13.81705507852985</v>
+        <v>13.66888460562906</v>
       </c>
       <c r="E44">
-        <v>8.575199999999999</v>
+        <v>8.780799999999999</v>
       </c>
       <c r="F44">
-        <v>8.635199999999999</v>
+        <v>8.8408</v>
       </c>
       <c r="G44">
         <v>2.17</v>
@@ -4895,37 +4895,37 @@
         <v>1.07</v>
       </c>
       <c r="M44">
-        <v>1.26764736</v>
+        <v>1.29782944</v>
       </c>
       <c r="N44">
-        <v>-0.1976473599999999</v>
+        <v>-0.22782944</v>
       </c>
       <c r="O44">
-        <v>-0.04941183999999998</v>
+        <v>-0.05695736000000001</v>
       </c>
       <c r="P44">
-        <v>-0.14823552</v>
+        <v>-0.17087208</v>
       </c>
       <c r="Q44">
-        <v>0.09176448000000004</v>
+        <v>0.06912791999999995</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1557384149436888</v>
+        <v>0.1576671590655079</v>
       </c>
       <c r="T44">
-        <v>1.063188496500564</v>
+        <v>1.081840926263731</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2110208315347259</v>
+        <v>0.2061133703362439</v>
       </c>
       <c r="W44">
-        <v>0.1158221419307022</v>
+        <v>0.1165425572346394</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8440833261389036</v>
+        <v>0.8244534813449755</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1399835802782344</v>
+        <v>0.1409935802782344</v>
       </c>
       <c r="C45">
-        <v>6.998084605629062</v>
+        <v>6.647458298063635</v>
       </c>
       <c r="D45">
-        <v>13.66888460562906</v>
+        <v>13.52385829806363</v>
       </c>
       <c r="E45">
-        <v>8.780799999999999</v>
+        <v>8.9864</v>
       </c>
       <c r="F45">
-        <v>8.8408</v>
+        <v>9.0464</v>
       </c>
       <c r="G45">
         <v>2.17</v>
@@ -4977,37 +4977,37 @@
         <v>1.07</v>
       </c>
       <c r="M45">
-        <v>1.29782944</v>
+        <v>1.32801152</v>
       </c>
       <c r="N45">
-        <v>-0.22782944</v>
+        <v>-0.2580115200000002</v>
       </c>
       <c r="O45">
-        <v>-0.05695736000000001</v>
+        <v>-0.06450288000000004</v>
       </c>
       <c r="P45">
-        <v>-0.17087208</v>
+        <v>-0.1935086400000001</v>
       </c>
       <c r="Q45">
-        <v>0.06912791999999995</v>
+        <v>0.04649135999999987</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1576671590655079</v>
+        <v>0.1596647869059634</v>
       </c>
       <c r="T45">
-        <v>1.081840926263731</v>
+        <v>1.101159514232727</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2061133703362439</v>
+        <v>0.2014289755558747</v>
       </c>
       <c r="W45">
-        <v>0.1165425572346394</v>
+        <v>0.1172302263883976</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8244534813449755</v>
+        <v>0.8057159022234988</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1409935802782344</v>
+        <v>0.1679711607931225</v>
       </c>
       <c r="C46">
-        <v>6.647458298063635</v>
+        <v>3.455548159570728</v>
       </c>
       <c r="D46">
-        <v>13.52385829806363</v>
+        <v>10.53754815957073</v>
       </c>
       <c r="E46">
-        <v>8.9864</v>
+        <v>9.191999999999998</v>
       </c>
       <c r="F46">
-        <v>9.0464</v>
+        <v>9.251999999999999</v>
       </c>
       <c r="G46">
         <v>2.17</v>
@@ -5059,45 +5059,45 @@
         <v>1.07</v>
       </c>
       <c r="M46">
-        <v>1.32801152</v>
+        <v>1.8578016</v>
       </c>
       <c r="N46">
-        <v>-0.2580115200000002</v>
+        <v>-0.7878015999999999</v>
       </c>
       <c r="O46">
-        <v>-0.06450288000000004</v>
+        <v>-0.1969504</v>
       </c>
       <c r="P46">
-        <v>-0.1935086400000001</v>
+        <v>-0.5908511999999999</v>
       </c>
       <c r="Q46">
-        <v>0.04649135999999987</v>
+        <v>-0.3508511999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1596647869059634</v>
+        <v>0.1647670203313228</v>
       </c>
       <c r="T46">
-        <v>1.101159514232727</v>
+        <v>1.150502011003136</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.2014289755558747</v>
+        <v>0.1439873881043057</v>
       </c>
       <c r="W46">
-        <v>0.1172302263883976</v>
+        <v>0.1718873324686554</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8057159022234988</v>
+        <v>0.5759495524172227</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1679711607931225</v>
+        <v>0.1695211607931225</v>
       </c>
       <c r="C47">
-        <v>3.455548159570728</v>
+        <v>3.117931942275082</v>
       </c>
       <c r="D47">
-        <v>10.53754815957073</v>
+        <v>10.40553194227508</v>
       </c>
       <c r="E47">
-        <v>9.191999999999998</v>
+        <v>9.397599999999999</v>
       </c>
       <c r="F47">
-        <v>9.251999999999999</v>
+        <v>9.457599999999999</v>
       </c>
       <c r="G47">
         <v>2.17</v>
@@ -5141,37 +5141,37 @@
         <v>1.07</v>
       </c>
       <c r="M47">
-        <v>1.8578016</v>
+        <v>1.89908608</v>
       </c>
       <c r="N47">
-        <v>-0.7878015999999999</v>
+        <v>-0.8290860799999999</v>
       </c>
       <c r="O47">
-        <v>-0.1969504</v>
+        <v>-0.20727152</v>
       </c>
       <c r="P47">
-        <v>-0.5908511999999999</v>
+        <v>-0.62181456</v>
       </c>
       <c r="Q47">
-        <v>-0.3508511999999999</v>
+        <v>-0.38181456</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1647670203313228</v>
+        <v>0.1669701133004214</v>
       </c>
       <c r="T47">
-        <v>1.150502011003136</v>
+        <v>1.17180760379949</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1439873881043057</v>
+        <v>0.1408572274933425</v>
       </c>
       <c r="W47">
-        <v>0.1718873324686554</v>
+        <v>0.1725158687193368</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5759495524172227</v>
+        <v>0.56342890997337</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1695211607931225</v>
+        <v>0.1710711607931225</v>
       </c>
       <c r="C48">
-        <v>3.117931942275082</v>
+        <v>2.783582640293583</v>
       </c>
       <c r="D48">
-        <v>10.40553194227508</v>
+        <v>10.27678264029358</v>
       </c>
       <c r="E48">
-        <v>9.397599999999999</v>
+        <v>9.603199999999999</v>
       </c>
       <c r="F48">
-        <v>9.457599999999999</v>
+        <v>9.6632</v>
       </c>
       <c r="G48">
         <v>2.17</v>
@@ -5223,37 +5223,37 @@
         <v>1.07</v>
       </c>
       <c r="M48">
-        <v>1.89908608</v>
+        <v>1.94037056</v>
       </c>
       <c r="N48">
-        <v>-0.8290860799999999</v>
+        <v>-0.87037056</v>
       </c>
       <c r="O48">
-        <v>-0.20727152</v>
+        <v>-0.21759264</v>
       </c>
       <c r="P48">
-        <v>-0.62181456</v>
+        <v>-0.65277792</v>
       </c>
       <c r="Q48">
-        <v>-0.38181456</v>
+        <v>-0.41277792</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1669701133004214</v>
+        <v>0.1692563418532596</v>
       </c>
       <c r="T48">
-        <v>1.17180760379949</v>
+        <v>1.19391718122967</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1408572274933425</v>
+        <v>0.1378602652062501</v>
       </c>
       <c r="W48">
-        <v>0.1725158687193368</v>
+        <v>0.173117658746585</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.56342890997337</v>
+        <v>0.5514410608250004</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1710711607931225</v>
+        <v>0.1726211607931226</v>
       </c>
       <c r="C49">
-        <v>2.783582640293583</v>
+        <v>2.452380469545123</v>
       </c>
       <c r="D49">
-        <v>10.27678264029358</v>
+        <v>10.15118046954512</v>
       </c>
       <c r="E49">
-        <v>9.603199999999999</v>
+        <v>9.8088</v>
       </c>
       <c r="F49">
-        <v>9.6632</v>
+        <v>9.8688</v>
       </c>
       <c r="G49">
         <v>2.17</v>
@@ -5305,37 +5305,37 @@
         <v>1.07</v>
       </c>
       <c r="M49">
-        <v>1.94037056</v>
+        <v>1.98165504</v>
       </c>
       <c r="N49">
-        <v>-0.87037056</v>
+        <v>-0.9116550400000001</v>
       </c>
       <c r="O49">
-        <v>-0.21759264</v>
+        <v>-0.22791376</v>
       </c>
       <c r="P49">
-        <v>-0.65277792</v>
+        <v>-0.68374128</v>
       </c>
       <c r="Q49">
-        <v>-0.41277792</v>
+        <v>-0.44374128</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1692563418532596</v>
+        <v>0.1716305022735146</v>
       </c>
       <c r="T49">
-        <v>1.19391718122967</v>
+        <v>1.216877127022548</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1378602652062501</v>
+        <v>0.1349881763477865</v>
       </c>
       <c r="W49">
-        <v>0.173117658746585</v>
+        <v>0.1736943741893645</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5514410608250004</v>
+        <v>0.5399527053911461</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1726211607931225</v>
+        <v>0.1741711607931225</v>
       </c>
       <c r="C50">
-        <v>2.45238046954513</v>
+        <v>2.124211431214537</v>
       </c>
       <c r="D50">
-        <v>10.15118046954513</v>
+        <v>10.02861143121454</v>
       </c>
       <c r="E50">
-        <v>9.808799999999998</v>
+        <v>10.0144</v>
       </c>
       <c r="F50">
-        <v>9.868799999999998</v>
+        <v>10.0744</v>
       </c>
       <c r="G50">
         <v>2.17</v>
@@ -5387,37 +5387,37 @@
         <v>1.07</v>
       </c>
       <c r="M50">
-        <v>1.98165504</v>
+        <v>2.02293952</v>
       </c>
       <c r="N50">
-        <v>-0.9116550399999996</v>
+        <v>-0.9529395199999999</v>
       </c>
       <c r="O50">
-        <v>-0.2279137599999999</v>
+        <v>-0.23823488</v>
       </c>
       <c r="P50">
-        <v>-0.6837412799999998</v>
+        <v>-0.7147046399999999</v>
       </c>
       <c r="Q50">
-        <v>-0.4437412799999998</v>
+        <v>-0.4747046399999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1716305022735146</v>
+        <v>0.1740977670239756</v>
       </c>
       <c r="T50">
-        <v>1.216877127022548</v>
+        <v>1.240737462846519</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1349881763477866</v>
+        <v>0.132233315605995</v>
       </c>
       <c r="W50">
-        <v>0.1736943741893645</v>
+        <v>0.1742475502263162</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5399527053911464</v>
+        <v>0.52893326242398</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1741711607931225</v>
+        <v>0.1757211607931225</v>
       </c>
       <c r="C51">
-        <v>2.124211431214537</v>
+        <v>1.798966966652413</v>
       </c>
       <c r="D51">
-        <v>10.02861143121454</v>
+        <v>9.908966966652413</v>
       </c>
       <c r="E51">
-        <v>10.0144</v>
+        <v>10.22</v>
       </c>
       <c r="F51">
-        <v>10.0744</v>
+        <v>10.28</v>
       </c>
       <c r="G51">
         <v>2.17</v>
@@ -5469,37 +5469,37 @@
         <v>1.07</v>
       </c>
       <c r="M51">
-        <v>2.02293952</v>
+        <v>2.064224</v>
       </c>
       <c r="N51">
-        <v>-0.9529395199999999</v>
+        <v>-0.9942239999999998</v>
       </c>
       <c r="O51">
-        <v>-0.23823488</v>
+        <v>-0.2485559999999999</v>
       </c>
       <c r="P51">
-        <v>-0.7147046399999999</v>
+        <v>-0.7456679999999998</v>
       </c>
       <c r="Q51">
-        <v>-0.4747046399999999</v>
+        <v>-0.5056679999999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1740977670239756</v>
+        <v>0.1766637223644551</v>
       </c>
       <c r="T51">
-        <v>1.240737462846519</v>
+        <v>1.265552212103449</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.132233315605995</v>
+        <v>0.1295886492938751</v>
       </c>
       <c r="W51">
-        <v>0.1742475502263162</v>
+        <v>0.1747785992217899</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.52893326242398</v>
+        <v>0.5183545971755004</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1757211607931225</v>
+        <v>0.1772711607931225</v>
       </c>
       <c r="C52">
-        <v>1.798966966652413</v>
+        <v>1.47654363668669</v>
       </c>
       <c r="D52">
-        <v>9.908966966652413</v>
+        <v>9.79214363668669</v>
       </c>
       <c r="E52">
-        <v>10.22</v>
+        <v>10.4256</v>
       </c>
       <c r="F52">
-        <v>10.28</v>
+        <v>10.4856</v>
       </c>
       <c r="G52">
         <v>2.17</v>
@@ -5551,37 +5551,37 @@
         <v>1.07</v>
       </c>
       <c r="M52">
-        <v>2.064224</v>
+        <v>2.10550848</v>
       </c>
       <c r="N52">
-        <v>-0.9942239999999998</v>
+        <v>-1.03550848</v>
       </c>
       <c r="O52">
-        <v>-0.2485559999999999</v>
+        <v>-0.25887712</v>
       </c>
       <c r="P52">
-        <v>-0.7456679999999998</v>
+        <v>-0.7766313600000001</v>
       </c>
       <c r="Q52">
-        <v>-0.5056679999999998</v>
+        <v>-0.5366313600000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1766637223644551</v>
+        <v>0.1793344105759747</v>
       </c>
       <c r="T52">
-        <v>1.265552212103449</v>
+        <v>1.291379808268826</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1295886492938751</v>
+        <v>0.127047695386152</v>
       </c>
       <c r="W52">
-        <v>0.1747785992217899</v>
+        <v>0.1752888227664607</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5183545971755004</v>
+        <v>0.5081907815446082</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1772711607931225</v>
+        <v>0.1976940496730188</v>
       </c>
       <c r="C53">
-        <v>1.47654363668669</v>
+        <v>-0.04565738763611371</v>
       </c>
       <c r="D53">
-        <v>9.79214363668669</v>
+        <v>8.475542612363887</v>
       </c>
       <c r="E53">
-        <v>10.4256</v>
+        <v>10.6312</v>
       </c>
       <c r="F53">
-        <v>10.4856</v>
+        <v>10.6912</v>
       </c>
       <c r="G53">
         <v>2.17</v>
@@ -5633,45 +5633,45 @@
         <v>1.07</v>
       </c>
       <c r="M53">
-        <v>2.10550848</v>
+        <v>2.52098496</v>
       </c>
       <c r="N53">
-        <v>-1.03550848</v>
+        <v>-1.45098496</v>
       </c>
       <c r="O53">
-        <v>-0.25887712</v>
+        <v>-0.3627462400000001</v>
       </c>
       <c r="P53">
-        <v>-0.7766313600000001</v>
+        <v>-1.08823872</v>
       </c>
       <c r="Q53">
-        <v>-0.5366313600000001</v>
+        <v>-0.8482387200000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1793344105759747</v>
+        <v>0.1835182292960913</v>
       </c>
       <c r="T53">
-        <v>1.291379808268826</v>
+        <v>1.331840532911347</v>
       </c>
       <c r="U53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.127047695386152</v>
+        <v>0.1061093200651225</v>
       </c>
       <c r="W53">
-        <v>0.1752888227664607</v>
+        <v>0.2107794223286441</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.5081907815446082</v>
+        <v>0.4244372802604899</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1976940496730188</v>
+        <v>0.1995940496730188</v>
       </c>
       <c r="C54">
-        <v>-0.04565738763611371</v>
+        <v>-0.3559658012433307</v>
       </c>
       <c r="D54">
-        <v>8.475542612363887</v>
+        <v>8.37083419875667</v>
       </c>
       <c r="E54">
-        <v>10.6312</v>
+        <v>10.8368</v>
       </c>
       <c r="F54">
-        <v>10.6912</v>
+        <v>10.8968</v>
       </c>
       <c r="G54">
         <v>2.17</v>
@@ -5715,37 +5715,37 @@
         <v>1.07</v>
       </c>
       <c r="M54">
-        <v>2.52098496</v>
+        <v>2.56946544</v>
       </c>
       <c r="N54">
-        <v>-1.45098496</v>
+        <v>-1.49946544</v>
       </c>
       <c r="O54">
-        <v>-0.3627462400000001</v>
+        <v>-0.37486636</v>
       </c>
       <c r="P54">
-        <v>-1.08823872</v>
+        <v>-1.12459908</v>
       </c>
       <c r="Q54">
-        <v>-0.8482387200000001</v>
+        <v>-0.8845990800000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1835182292960913</v>
+        <v>0.1864484043874975</v>
       </c>
       <c r="T54">
-        <v>1.331840532911347</v>
+        <v>1.360177565526482</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1061093200651225</v>
+        <v>0.1041072574223843</v>
       </c>
       <c r="W54">
-        <v>0.2107794223286441</v>
+        <v>0.2112515086998018</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4244372802604899</v>
+        <v>0.4164290296895373</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1995940496730188</v>
+        <v>0.2014940496730188</v>
       </c>
       <c r="C55">
-        <v>-0.3559658012433307</v>
+        <v>-0.6637186131911204</v>
       </c>
       <c r="D55">
-        <v>8.37083419875667</v>
+        <v>8.268681386808879</v>
       </c>
       <c r="E55">
-        <v>10.8368</v>
+        <v>11.0424</v>
       </c>
       <c r="F55">
-        <v>10.8968</v>
+        <v>11.1024</v>
       </c>
       <c r="G55">
         <v>2.17</v>
@@ -5797,37 +5797,37 @@
         <v>1.07</v>
       </c>
       <c r="M55">
-        <v>2.56946544</v>
+        <v>2.61794592</v>
       </c>
       <c r="N55">
-        <v>-1.49946544</v>
+        <v>-1.54794592</v>
       </c>
       <c r="O55">
-        <v>-0.37486636</v>
+        <v>-0.38698648</v>
       </c>
       <c r="P55">
-        <v>-1.12459908</v>
+        <v>-1.16095944</v>
       </c>
       <c r="Q55">
-        <v>-0.8845990800000001</v>
+        <v>-0.9209594399999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1864484043874975</v>
+        <v>0.1895059783959214</v>
       </c>
       <c r="T55">
-        <v>1.360177565526482</v>
+        <v>1.389746643037927</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1041072574223843</v>
+        <v>0.1021793452478957</v>
       </c>
       <c r="W55">
-        <v>0.2112515086998018</v>
+        <v>0.2117061103905462</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4164290296895373</v>
+        <v>0.4087173809915829</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2014940496730188</v>
+        <v>0.2033940496730188</v>
       </c>
       <c r="C56">
-        <v>-0.6637186131911204</v>
+        <v>-0.9690082567248304</v>
       </c>
       <c r="D56">
-        <v>8.268681386808879</v>
+        <v>8.16899174327517</v>
       </c>
       <c r="E56">
-        <v>11.0424</v>
+        <v>11.248</v>
       </c>
       <c r="F56">
-        <v>11.1024</v>
+        <v>11.308</v>
       </c>
       <c r="G56">
         <v>2.17</v>
@@ -5879,37 +5879,37 @@
         <v>1.07</v>
       </c>
       <c r="M56">
-        <v>2.61794592</v>
+        <v>2.6664264</v>
       </c>
       <c r="N56">
-        <v>-1.54794592</v>
+        <v>-1.5964264</v>
       </c>
       <c r="O56">
-        <v>-0.38698648</v>
+        <v>-0.3991066</v>
       </c>
       <c r="P56">
-        <v>-1.16095944</v>
+        <v>-1.1973198</v>
       </c>
       <c r="Q56">
-        <v>-0.9209594399999999</v>
+        <v>-0.9573198000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1895059783959214</v>
+        <v>0.1926994445824975</v>
       </c>
       <c r="T56">
-        <v>1.389746643037927</v>
+        <v>1.420629901772104</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1021793452478957</v>
+        <v>0.1003215389706613</v>
       </c>
       <c r="W56">
-        <v>0.2117061103905462</v>
+        <v>0.2121441811107181</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4087173809915829</v>
+        <v>0.401286155882645</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2033940496730188</v>
+        <v>0.2052940496730188</v>
       </c>
       <c r="C57">
-        <v>-0.9690082567248304</v>
+        <v>-1.271922760582767</v>
       </c>
       <c r="D57">
-        <v>8.16899174327517</v>
+        <v>8.071677239417234</v>
       </c>
       <c r="E57">
-        <v>11.248</v>
+        <v>11.4536</v>
       </c>
       <c r="F57">
-        <v>11.308</v>
+        <v>11.5136</v>
       </c>
       <c r="G57">
         <v>2.17</v>
@@ -5961,37 +5961,37 @@
         <v>1.07</v>
       </c>
       <c r="M57">
-        <v>2.6664264</v>
+        <v>2.71490688</v>
       </c>
       <c r="N57">
-        <v>-1.5964264</v>
+        <v>-1.64490688</v>
       </c>
       <c r="O57">
-        <v>-0.3991066</v>
+        <v>-0.41122672</v>
       </c>
       <c r="P57">
-        <v>-1.1973198</v>
+        <v>-1.23368016</v>
       </c>
       <c r="Q57">
-        <v>-0.9573198000000001</v>
+        <v>-0.99368016</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1926994445824975</v>
+        <v>0.1960380683230087</v>
       </c>
       <c r="T57">
-        <v>1.420629901772104</v>
+        <v>1.452916944994196</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1003215389706613</v>
+        <v>0.09853008291761374</v>
       </c>
       <c r="W57">
-        <v>0.2121441811107181</v>
+        <v>0.2125666064480267</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.401286155882645</v>
+        <v>0.3941203316704549</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2052940496730188</v>
+        <v>0.2071940496730188</v>
       </c>
       <c r="C58">
-        <v>-1.271922760582767</v>
+        <v>-1.572546008254932</v>
       </c>
       <c r="D58">
-        <v>8.071677239417234</v>
+        <v>7.97665399174507</v>
       </c>
       <c r="E58">
-        <v>11.4536</v>
+        <v>11.6592</v>
       </c>
       <c r="F58">
-        <v>11.5136</v>
+        <v>11.7192</v>
       </c>
       <c r="G58">
         <v>2.17</v>
@@ -6043,37 +6043,37 @@
         <v>1.07</v>
       </c>
       <c r="M58">
-        <v>2.71490688</v>
+        <v>2.76338736</v>
       </c>
       <c r="N58">
-        <v>-1.64490688</v>
+        <v>-1.69338736</v>
       </c>
       <c r="O58">
-        <v>-0.41122672</v>
+        <v>-0.4233468400000001</v>
       </c>
       <c r="P58">
-        <v>-1.23368016</v>
+        <v>-1.27004052</v>
       </c>
       <c r="Q58">
-        <v>-0.99368016</v>
+        <v>-1.03004052</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1960380683230087</v>
+        <v>0.1995319768886601</v>
       </c>
       <c r="T58">
-        <v>1.452916944994196</v>
+        <v>1.486705711156852</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09853008291761374</v>
+        <v>0.09680148497169068</v>
       </c>
       <c r="W58">
-        <v>0.2125666064480267</v>
+        <v>0.2129742098436753</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3941203316704549</v>
+        <v>0.3872059398867628</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2071940496730188</v>
+        <v>0.2090940496730188</v>
       </c>
       <c r="C59">
-        <v>-1.572546008254932</v>
+        <v>-1.870957979142196</v>
       </c>
       <c r="D59">
-        <v>7.97665399174507</v>
+        <v>7.883842020857806</v>
       </c>
       <c r="E59">
-        <v>11.6592</v>
+        <v>11.8648</v>
       </c>
       <c r="F59">
-        <v>11.7192</v>
+        <v>11.9248</v>
       </c>
       <c r="G59">
         <v>2.17</v>
@@ -6125,37 +6125,37 @@
         <v>1.07</v>
       </c>
       <c r="M59">
-        <v>2.76338736</v>
+        <v>2.811867840000001</v>
       </c>
       <c r="N59">
-        <v>-1.69338736</v>
+        <v>-1.741867840000001</v>
       </c>
       <c r="O59">
-        <v>-0.4233468400000001</v>
+        <v>-0.4354669600000001</v>
       </c>
       <c r="P59">
-        <v>-1.27004052</v>
+        <v>-1.30640088</v>
       </c>
       <c r="Q59">
-        <v>-1.03004052</v>
+        <v>-1.06640088</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1995319768886601</v>
+        <v>0.2031922620526758</v>
       </c>
       <c r="T59">
-        <v>1.486705711156852</v>
+        <v>1.522103466184397</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09680148497169068</v>
+        <v>0.09513249385148911</v>
       </c>
       <c r="W59">
-        <v>0.2129742098436753</v>
+        <v>0.2133677579498189</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3872059398867628</v>
+        <v>0.3805299754059565</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2090940496730188</v>
+        <v>0.2109940496730188</v>
       </c>
       <c r="C60">
-        <v>-1.87095797914219</v>
+        <v>-2.167234973073143</v>
       </c>
       <c r="D60">
-        <v>7.883842020857808</v>
+        <v>7.793165026926856</v>
       </c>
       <c r="E60">
-        <v>11.8648</v>
+        <v>12.0704</v>
       </c>
       <c r="F60">
-        <v>11.9248</v>
+        <v>12.1304</v>
       </c>
       <c r="G60">
         <v>2.17</v>
@@ -6207,37 +6207,37 @@
         <v>1.07</v>
       </c>
       <c r="M60">
-        <v>2.81186784</v>
+        <v>2.86034832</v>
       </c>
       <c r="N60">
-        <v>-1.74186784</v>
+        <v>-1.790348319999999</v>
       </c>
       <c r="O60">
-        <v>-0.4354669599999999</v>
+        <v>-0.4475870799999999</v>
       </c>
       <c r="P60">
-        <v>-1.30640088</v>
+        <v>-1.34276124</v>
       </c>
       <c r="Q60">
-        <v>-1.06640088</v>
+        <v>-1.10276124</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2031922620526758</v>
+        <v>0.2070310977124971</v>
       </c>
       <c r="T60">
-        <v>1.522103466184396</v>
+        <v>1.559227940969381</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09513249385148914</v>
+        <v>0.09352007870146391</v>
       </c>
       <c r="W60">
-        <v>0.2133677579498189</v>
+        <v>0.2137479654421948</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3805299754059566</v>
+        <v>0.3740803148058556</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2109940496730188</v>
+        <v>0.2128940496730188</v>
       </c>
       <c r="C61">
-        <v>-2.167234973073143</v>
+        <v>-2.461449819503262</v>
       </c>
       <c r="D61">
-        <v>7.793165026926856</v>
+        <v>7.704550180496737</v>
       </c>
       <c r="E61">
-        <v>12.0704</v>
+        <v>12.276</v>
       </c>
       <c r="F61">
-        <v>12.1304</v>
+        <v>12.336</v>
       </c>
       <c r="G61">
         <v>2.17</v>
@@ -6289,37 +6289,37 @@
         <v>1.07</v>
       </c>
       <c r="M61">
-        <v>2.86034832</v>
+        <v>2.9088288</v>
       </c>
       <c r="N61">
-        <v>-1.790348319999999</v>
+        <v>-1.8388288</v>
       </c>
       <c r="O61">
-        <v>-0.4475870799999999</v>
+        <v>-0.4597071999999999</v>
       </c>
       <c r="P61">
-        <v>-1.34276124</v>
+        <v>-1.3791216</v>
       </c>
       <c r="Q61">
-        <v>-1.10276124</v>
+        <v>-1.1391216</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2070310977124971</v>
+        <v>0.2110618751553096</v>
       </c>
       <c r="T61">
-        <v>1.559227940969381</v>
+        <v>1.598208639493616</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09352007870146391</v>
+        <v>0.09196141072310617</v>
       </c>
       <c r="W61">
-        <v>0.2137479654421948</v>
+        <v>0.2141154993514916</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3740803148058556</v>
+        <v>0.3678456428924246</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2128940496730188</v>
+        <v>0.2147940496730188</v>
       </c>
       <c r="C62">
-        <v>-2.461449819503262</v>
+        <v>-2.753672072601923</v>
       </c>
       <c r="D62">
-        <v>7.704550180496737</v>
+        <v>7.617927927398076</v>
       </c>
       <c r="E62">
-        <v>12.276</v>
+        <v>12.4816</v>
       </c>
       <c r="F62">
-        <v>12.336</v>
+        <v>12.5416</v>
       </c>
       <c r="G62">
         <v>2.17</v>
@@ -6371,37 +6371,37 @@
         <v>1.07</v>
       </c>
       <c r="M62">
-        <v>2.9088288</v>
+        <v>2.95730928</v>
       </c>
       <c r="N62">
-        <v>-1.8388288</v>
+        <v>-1.88730928</v>
       </c>
       <c r="O62">
-        <v>-0.4597071999999999</v>
+        <v>-0.47182732</v>
       </c>
       <c r="P62">
-        <v>-1.3791216</v>
+        <v>-1.41548196</v>
       </c>
       <c r="Q62">
-        <v>-1.1391216</v>
+        <v>-1.17548196</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2110618751553096</v>
+        <v>0.2152993591336509</v>
       </c>
       <c r="T62">
-        <v>1.598208639493616</v>
+        <v>1.639188348198581</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09196141072310617</v>
+        <v>0.0904538466128913</v>
       </c>
       <c r="W62">
-        <v>0.2141154993514916</v>
+        <v>0.2144709829686803</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3678456428924246</v>
+        <v>0.3618153864515652</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2147940496730188</v>
+        <v>0.2166940496730188</v>
       </c>
       <c r="C63">
-        <v>-2.753672072601923</v>
+        <v>-3.043968193325558</v>
       </c>
       <c r="D63">
-        <v>7.617927927398076</v>
+        <v>7.533231806674443</v>
       </c>
       <c r="E63">
-        <v>12.4816</v>
+        <v>12.6872</v>
       </c>
       <c r="F63">
-        <v>12.5416</v>
+        <v>12.7472</v>
       </c>
       <c r="G63">
         <v>2.17</v>
@@ -6453,37 +6453,37 @@
         <v>1.07</v>
       </c>
       <c r="M63">
-        <v>2.95730928</v>
+        <v>3.00578976</v>
       </c>
       <c r="N63">
-        <v>-1.88730928</v>
+        <v>-1.93578976</v>
       </c>
       <c r="O63">
-        <v>-0.47182732</v>
+        <v>-0.48394744</v>
       </c>
       <c r="P63">
-        <v>-1.41548196</v>
+        <v>-1.45184232</v>
       </c>
       <c r="Q63">
-        <v>-1.17548196</v>
+        <v>-1.21184232</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2152993591336509</v>
+        <v>0.2197598685845364</v>
       </c>
       <c r="T63">
-        <v>1.639188348198581</v>
+        <v>1.682324883677491</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0904538466128913</v>
+        <v>0.08899491360300596</v>
       </c>
       <c r="W63">
-        <v>0.2144709829686803</v>
+        <v>0.2148149993724112</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3618153864515652</v>
+        <v>0.3559796544120238</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2166940496730188</v>
+        <v>0.2185940496730188</v>
       </c>
       <c r="C64">
-        <v>-3.043968193325558</v>
+        <v>-3.332401719478606</v>
       </c>
       <c r="D64">
-        <v>7.533231806674443</v>
+        <v>7.450398280521394</v>
       </c>
       <c r="E64">
-        <v>12.6872</v>
+        <v>12.8928</v>
       </c>
       <c r="F64">
-        <v>12.7472</v>
+        <v>12.9528</v>
       </c>
       <c r="G64">
         <v>2.17</v>
@@ -6535,37 +6535,37 @@
         <v>1.07</v>
       </c>
       <c r="M64">
-        <v>3.00578976</v>
+        <v>3.05427024</v>
       </c>
       <c r="N64">
-        <v>-1.93578976</v>
+        <v>-1.98427024</v>
       </c>
       <c r="O64">
-        <v>-0.48394744</v>
+        <v>-0.49606756</v>
       </c>
       <c r="P64">
-        <v>-1.45184232</v>
+        <v>-1.48820268</v>
       </c>
       <c r="Q64">
-        <v>-1.21184232</v>
+        <v>-1.24820268</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2197598685845364</v>
+        <v>0.2244614866543888</v>
       </c>
       <c r="T64">
-        <v>1.682324883677491</v>
+        <v>1.727793123776882</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08899491360300596</v>
+        <v>0.08758229592676776</v>
       </c>
       <c r="W64">
-        <v>0.2148149993724112</v>
+        <v>0.2151480946204682</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3559796544120238</v>
+        <v>0.3503291837070711</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2185940496730188</v>
+        <v>0.2204940496730188</v>
       </c>
       <c r="C65">
-        <v>-3.332401719478606</v>
+        <v>-3.619033424676845</v>
       </c>
       <c r="D65">
-        <v>7.450398280521394</v>
+        <v>7.369366575323156</v>
       </c>
       <c r="E65">
-        <v>12.8928</v>
+        <v>13.0984</v>
       </c>
       <c r="F65">
-        <v>12.9528</v>
+        <v>13.1584</v>
       </c>
       <c r="G65">
         <v>2.17</v>
@@ -6617,37 +6617,37 @@
         <v>1.07</v>
       </c>
       <c r="M65">
-        <v>3.05427024</v>
+        <v>3.10275072</v>
       </c>
       <c r="N65">
-        <v>-1.98427024</v>
+        <v>-2.03275072</v>
       </c>
       <c r="O65">
-        <v>-0.49606756</v>
+        <v>-0.50818768</v>
       </c>
       <c r="P65">
-        <v>-1.48820268</v>
+        <v>-1.52456304</v>
       </c>
       <c r="Q65">
-        <v>-1.24820268</v>
+        <v>-1.28456304</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2244614866543888</v>
+        <v>0.2294243057281218</v>
       </c>
       <c r="T65">
-        <v>1.727793123776882</v>
+        <v>1.775787377215129</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08758229592676776</v>
+        <v>0.08621382255291202</v>
       </c>
       <c r="W65">
-        <v>0.2151480946204682</v>
+        <v>0.2154707806420234</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3503291837070711</v>
+        <v>0.3448552902116481</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2204940496730188</v>
+        <v>0.2223940496730188</v>
       </c>
       <c r="C66">
-        <v>-3.619033424676845</v>
+        <v>-3.903921467048827</v>
       </c>
       <c r="D66">
-        <v>7.369366575323156</v>
+        <v>7.290078532951173</v>
       </c>
       <c r="E66">
-        <v>13.0984</v>
+        <v>13.304</v>
       </c>
       <c r="F66">
-        <v>13.1584</v>
+        <v>13.364</v>
       </c>
       <c r="G66">
         <v>2.17</v>
@@ -6699,37 +6699,37 @@
         <v>1.07</v>
       </c>
       <c r="M66">
-        <v>3.10275072</v>
+        <v>3.1512312</v>
       </c>
       <c r="N66">
-        <v>-2.03275072</v>
+        <v>-2.0812312</v>
       </c>
       <c r="O66">
-        <v>-0.50818768</v>
+        <v>-0.5203077999999999</v>
       </c>
       <c r="P66">
-        <v>-1.52456304</v>
+        <v>-1.5609234</v>
       </c>
       <c r="Q66">
-        <v>-1.28456304</v>
+        <v>-1.3209234</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2294243057281218</v>
+        <v>0.234670714463211</v>
       </c>
       <c r="T66">
-        <v>1.775787377215129</v>
+        <v>1.826524159421276</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08621382255291202</v>
+        <v>0.08488745605209799</v>
       </c>
       <c r="W66">
-        <v>0.2154707806420234</v>
+        <v>0.2157835378629153</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3448552902116481</v>
+        <v>0.3395498242083921</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2223940496730188</v>
+        <v>0.2242940496730188</v>
       </c>
       <c r="C67">
-        <v>-3.903921467048827</v>
+        <v>-4.187121528440121</v>
       </c>
       <c r="D67">
-        <v>7.290078532951173</v>
+        <v>7.212478471559878</v>
       </c>
       <c r="E67">
-        <v>13.304</v>
+        <v>13.5096</v>
       </c>
       <c r="F67">
-        <v>13.364</v>
+        <v>13.5696</v>
       </c>
       <c r="G67">
         <v>2.17</v>
@@ -6781,37 +6781,37 @@
         <v>1.07</v>
       </c>
       <c r="M67">
-        <v>3.1512312</v>
+        <v>3.19971168</v>
       </c>
       <c r="N67">
-        <v>-2.0812312</v>
+        <v>-2.12971168</v>
       </c>
       <c r="O67">
-        <v>-0.5203077999999999</v>
+        <v>-0.5324279199999999</v>
       </c>
       <c r="P67">
-        <v>-1.5609234</v>
+        <v>-1.59728376</v>
       </c>
       <c r="Q67">
-        <v>-1.3209234</v>
+        <v>-1.35728376</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.234670714463211</v>
+        <v>0.2402257354768348</v>
       </c>
       <c r="T67">
-        <v>1.826524159421276</v>
+        <v>1.880245458227784</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08488745605209799</v>
+        <v>0.08360128247555106</v>
       </c>
       <c r="W67">
-        <v>0.2157835378629153</v>
+        <v>0.2160868175922651</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3395498242083921</v>
+        <v>0.3344051299022043</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2242940496730188</v>
+        <v>0.2261940496730188</v>
       </c>
       <c r="C68">
-        <v>-4.187121528440121</v>
+        <v>-4.468686944820556</v>
       </c>
       <c r="D68">
-        <v>7.212478471559878</v>
+        <v>7.136513055179444</v>
       </c>
       <c r="E68">
-        <v>13.5096</v>
+        <v>13.7152</v>
       </c>
       <c r="F68">
-        <v>13.5696</v>
+        <v>13.7752</v>
       </c>
       <c r="G68">
         <v>2.17</v>
@@ -6863,37 +6863,37 @@
         <v>1.07</v>
       </c>
       <c r="M68">
-        <v>3.19971168</v>
+        <v>3.24819216</v>
       </c>
       <c r="N68">
-        <v>-2.12971168</v>
+        <v>-2.17819216</v>
       </c>
       <c r="O68">
-        <v>-0.5324279199999999</v>
+        <v>-0.54454804</v>
       </c>
       <c r="P68">
-        <v>-1.59728376</v>
+        <v>-1.63364412</v>
       </c>
       <c r="Q68">
-        <v>-1.35728376</v>
+        <v>-1.39364412</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2402257354768348</v>
+        <v>0.2461174244306783</v>
       </c>
       <c r="T68">
-        <v>1.880245458227784</v>
+        <v>1.937222593325596</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08360128247555106</v>
+        <v>0.08235350214009507</v>
       </c>
       <c r="W68">
-        <v>0.2160868175922651</v>
+        <v>0.2163810441953656</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3344051299022043</v>
+        <v>0.3294140085603802</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2261940496730188</v>
+        <v>0.2280940496730188</v>
       </c>
       <c r="C69">
-        <v>-4.468686944820556</v>
+        <v>-4.748668828536248</v>
       </c>
       <c r="D69">
-        <v>7.136513055179444</v>
+        <v>7.062131171463752</v>
       </c>
       <c r="E69">
-        <v>13.7152</v>
+        <v>13.9208</v>
       </c>
       <c r="F69">
-        <v>13.7752</v>
+        <v>13.9808</v>
       </c>
       <c r="G69">
         <v>2.17</v>
@@ -6945,37 +6945,37 @@
         <v>1.07</v>
       </c>
       <c r="M69">
-        <v>3.24819216</v>
+        <v>3.29667264</v>
       </c>
       <c r="N69">
-        <v>-2.17819216</v>
+        <v>-2.22667264</v>
       </c>
       <c r="O69">
-        <v>-0.54454804</v>
+        <v>-0.5566681600000001</v>
       </c>
       <c r="P69">
-        <v>-1.63364412</v>
+        <v>-1.67000448</v>
       </c>
       <c r="Q69">
-        <v>-1.39364412</v>
+        <v>-1.43000448</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2461174244306783</v>
+        <v>0.252377343944137</v>
       </c>
       <c r="T69">
-        <v>1.937222593325596</v>
+        <v>1.99776079936702</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08235350214009507</v>
+        <v>0.08114242122627013</v>
       </c>
       <c r="W69">
-        <v>0.2163810441953656</v>
+        <v>0.2166666170748455</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3294140085603802</v>
+        <v>0.3245696849050804</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2280940496730188</v>
+        <v>0.2299940496730188</v>
       </c>
       <c r="C70">
-        <v>-4.748668828536248</v>
+        <v>-5.027116182995316</v>
       </c>
       <c r="D70">
-        <v>7.062131171463752</v>
+        <v>6.989283817004685</v>
       </c>
       <c r="E70">
-        <v>13.9208</v>
+        <v>14.1264</v>
       </c>
       <c r="F70">
-        <v>13.9808</v>
+        <v>14.1864</v>
       </c>
       <c r="G70">
         <v>2.17</v>
@@ -7027,37 +7027,37 @@
         <v>1.07</v>
       </c>
       <c r="M70">
-        <v>3.29667264</v>
+        <v>3.34515312</v>
       </c>
       <c r="N70">
-        <v>-2.22667264</v>
+        <v>-2.275153120000001</v>
       </c>
       <c r="O70">
-        <v>-0.5566681600000001</v>
+        <v>-0.5687882800000001</v>
       </c>
       <c r="P70">
-        <v>-1.67000448</v>
+        <v>-1.70636484</v>
       </c>
       <c r="Q70">
-        <v>-1.43000448</v>
+        <v>-1.46636484</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.252377343944137</v>
+        <v>0.2590411292326576</v>
       </c>
       <c r="T70">
-        <v>1.99776079936702</v>
+        <v>2.062204696120796</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08114242122627013</v>
+        <v>0.07996644410704883</v>
       </c>
       <c r="W70">
-        <v>0.2166666170748455</v>
+        <v>0.2169439124795579</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3245696849050804</v>
+        <v>0.3198657764281952</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2299940496730188</v>
+        <v>0.2318940496730188</v>
       </c>
       <c r="C71">
-        <v>-5.027116182995316</v>
+        <v>-5.304076010328012</v>
       </c>
       <c r="D71">
-        <v>6.989283817004685</v>
+        <v>6.917923989671989</v>
       </c>
       <c r="E71">
-        <v>14.1264</v>
+        <v>14.332</v>
       </c>
       <c r="F71">
-        <v>14.1864</v>
+        <v>14.392</v>
       </c>
       <c r="G71">
         <v>2.17</v>
@@ -7109,37 +7109,37 @@
         <v>1.07</v>
       </c>
       <c r="M71">
-        <v>3.34515312</v>
+        <v>3.3936336</v>
       </c>
       <c r="N71">
-        <v>-2.275153120000001</v>
+        <v>-2.3236336</v>
       </c>
       <c r="O71">
-        <v>-0.5687882800000001</v>
+        <v>-0.5809084</v>
       </c>
       <c r="P71">
-        <v>-1.70636484</v>
+        <v>-1.7427252</v>
       </c>
       <c r="Q71">
-        <v>-1.46636484</v>
+        <v>-1.5027252</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2590411292326576</v>
+        <v>0.2661491668737461</v>
       </c>
       <c r="T71">
-        <v>2.062204696120796</v>
+        <v>2.130944852658155</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07996644410704883</v>
+        <v>0.07882406633409099</v>
       </c>
       <c r="W71">
-        <v>0.2169439124795579</v>
+        <v>0.2172132851584213</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3198657764281952</v>
+        <v>0.315296265336364</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2318940496730188</v>
+        <v>0.2337940496730188</v>
       </c>
       <c r="C72">
-        <v>-5.304076010328012</v>
+        <v>-5.579593412518335</v>
       </c>
       <c r="D72">
-        <v>6.917923989671989</v>
+        <v>6.848006587481664</v>
       </c>
       <c r="E72">
-        <v>14.332</v>
+        <v>14.5376</v>
       </c>
       <c r="F72">
-        <v>14.392</v>
+        <v>14.5976</v>
       </c>
       <c r="G72">
         <v>2.17</v>
@@ -7191,37 +7191,37 @@
         <v>1.07</v>
       </c>
       <c r="M72">
-        <v>3.3936336</v>
+        <v>3.44211408</v>
       </c>
       <c r="N72">
-        <v>-2.3236336</v>
+        <v>-2.37211408</v>
       </c>
       <c r="O72">
-        <v>-0.5809084</v>
+        <v>-0.5930285200000001</v>
       </c>
       <c r="P72">
-        <v>-1.7427252</v>
+        <v>-1.77908556</v>
       </c>
       <c r="Q72">
-        <v>-1.5027252</v>
+        <v>-1.53908556</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2661491668737461</v>
+        <v>0.2737474140073236</v>
       </c>
       <c r="T72">
-        <v>2.130944852658155</v>
+        <v>2.204425709646368</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07882406633409099</v>
+        <v>0.07771386821670943</v>
       </c>
       <c r="W72">
-        <v>0.2172132851584213</v>
+        <v>0.2174750698744999</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.315296265336364</v>
+        <v>0.3108554728668377</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2337940496730188</v>
+        <v>0.2356940496730188</v>
       </c>
       <c r="C73">
-        <v>-5.579593412518333</v>
+        <v>-5.853711686464356</v>
       </c>
       <c r="D73">
-        <v>6.848006587481664</v>
+        <v>6.779488313535642</v>
       </c>
       <c r="E73">
-        <v>14.5376</v>
+        <v>14.7432</v>
       </c>
       <c r="F73">
-        <v>14.5976</v>
+        <v>14.8032</v>
       </c>
       <c r="G73">
         <v>2.17</v>
@@ -7273,37 +7273,37 @@
         <v>1.07</v>
       </c>
       <c r="M73">
-        <v>3.44211408</v>
+        <v>3.49059456</v>
       </c>
       <c r="N73">
-        <v>-2.372114079999999</v>
+        <v>-2.42059456</v>
       </c>
       <c r="O73">
-        <v>-0.5930285199999998</v>
+        <v>-0.6051486399999999</v>
       </c>
       <c r="P73">
-        <v>-1.77908556</v>
+        <v>-1.81544592</v>
       </c>
       <c r="Q73">
-        <v>-1.53908556</v>
+        <v>-1.57544592</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2737474140073235</v>
+        <v>0.2818883930790136</v>
       </c>
       <c r="T73">
-        <v>2.204425709646367</v>
+        <v>2.283155199276594</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07771386821670943</v>
+        <v>0.0766345089359218</v>
       </c>
       <c r="W73">
-        <v>0.2174750698744999</v>
+        <v>0.2177295827929096</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3108554728668378</v>
+        <v>0.3065380357436872</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2356940496730188</v>
+        <v>0.2375940496730187</v>
       </c>
       <c r="C74">
-        <v>-5.853711686464356</v>
+        <v>-6.126472413388251</v>
       </c>
       <c r="D74">
-        <v>6.779488313535642</v>
+        <v>6.712327586611748</v>
       </c>
       <c r="E74">
-        <v>14.7432</v>
+        <v>14.9488</v>
       </c>
       <c r="F74">
-        <v>14.8032</v>
+        <v>15.0088</v>
       </c>
       <c r="G74">
         <v>2.17</v>
@@ -7355,37 +7355,37 @@
         <v>1.07</v>
       </c>
       <c r="M74">
-        <v>3.49059456</v>
+        <v>3.53907504</v>
       </c>
       <c r="N74">
-        <v>-2.42059456</v>
+        <v>-2.46907504</v>
       </c>
       <c r="O74">
-        <v>-0.6051486399999999</v>
+        <v>-0.61726876</v>
       </c>
       <c r="P74">
-        <v>-1.81544592</v>
+        <v>-1.85180628</v>
       </c>
       <c r="Q74">
-        <v>-1.57544592</v>
+        <v>-1.61180628</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2818883930790136</v>
+        <v>0.2906324076374956</v>
       </c>
       <c r="T74">
-        <v>2.283155199276594</v>
+        <v>2.367716502953505</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0766345089359218</v>
+        <v>0.07558472114227904</v>
       </c>
       <c r="W74">
-        <v>0.2177295827929096</v>
+        <v>0.2179771227546506</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3065380357436872</v>
+        <v>0.3023388845691161</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2375940496730187</v>
+        <v>0.2394940496730188</v>
       </c>
       <c r="C75">
-        <v>-6.126472413388251</v>
+        <v>-6.397915542984087</v>
       </c>
       <c r="D75">
-        <v>6.712327586611748</v>
+        <v>6.646484457015912</v>
       </c>
       <c r="E75">
-        <v>14.9488</v>
+        <v>15.1544</v>
       </c>
       <c r="F75">
-        <v>15.0088</v>
+        <v>15.2144</v>
       </c>
       <c r="G75">
         <v>2.17</v>
@@ -7437,37 +7437,37 @@
         <v>1.07</v>
       </c>
       <c r="M75">
-        <v>3.53907504</v>
+        <v>3.58755552</v>
       </c>
       <c r="N75">
-        <v>-2.46907504</v>
+        <v>-2.51755552</v>
       </c>
       <c r="O75">
-        <v>-0.61726876</v>
+        <v>-0.62938888</v>
       </c>
       <c r="P75">
-        <v>-1.85180628</v>
+        <v>-1.88816664</v>
       </c>
       <c r="Q75">
-        <v>-1.61180628</v>
+        <v>-1.64816664</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2906324076374956</v>
+        <v>0.3000490387004763</v>
       </c>
       <c r="T75">
-        <v>2.367716502953505</v>
+        <v>2.458782522297871</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07558472114227904</v>
+        <v>0.0745633059917077</v>
       </c>
       <c r="W75">
-        <v>0.2179771227546506</v>
+        <v>0.2182179724471554</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3023388845691161</v>
+        <v>0.2982532239668307</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2394940496730188</v>
+        <v>0.2413940496730188</v>
       </c>
       <c r="C76">
-        <v>-6.397915542984087</v>
+        <v>-6.668079472661095</v>
       </c>
       <c r="D76">
-        <v>6.646484457015912</v>
+        <v>6.581920527338904</v>
       </c>
       <c r="E76">
-        <v>15.1544</v>
+        <v>15.36</v>
       </c>
       <c r="F76">
-        <v>15.2144</v>
+        <v>15.42</v>
       </c>
       <c r="G76">
         <v>2.17</v>
@@ -7519,37 +7519,37 @@
         <v>1.07</v>
       </c>
       <c r="M76">
-        <v>3.58755552</v>
+        <v>3.636036</v>
       </c>
       <c r="N76">
-        <v>-2.51755552</v>
+        <v>-2.566036</v>
       </c>
       <c r="O76">
-        <v>-0.62938888</v>
+        <v>-0.6415089999999999</v>
       </c>
       <c r="P76">
-        <v>-1.88816664</v>
+        <v>-1.924527</v>
       </c>
       <c r="Q76">
-        <v>-1.64816664</v>
+        <v>-1.684527</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3000490387004763</v>
+        <v>0.3102190002484953</v>
       </c>
       <c r="T76">
-        <v>2.458782522297871</v>
+        <v>2.557133823189786</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0745633059917077</v>
+        <v>0.07356912857848492</v>
       </c>
       <c r="W76">
-        <v>0.2182179724471554</v>
+        <v>0.2184523994811932</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2982532239668307</v>
+        <v>0.2942765143139398</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2413940496730188</v>
+        <v>0.2432940496730188</v>
       </c>
       <c r="C77">
-        <v>-6.668079472661095</v>
+        <v>-6.937001122212813</v>
       </c>
       <c r="D77">
-        <v>6.581920527338904</v>
+        <v>6.518598877787187</v>
       </c>
       <c r="E77">
-        <v>15.36</v>
+        <v>15.5656</v>
       </c>
       <c r="F77">
-        <v>15.42</v>
+        <v>15.6256</v>
       </c>
       <c r="G77">
         <v>2.17</v>
@@ -7601,37 +7601,37 @@
         <v>1.07</v>
       </c>
       <c r="M77">
-        <v>3.636036</v>
+        <v>3.68451648</v>
       </c>
       <c r="N77">
-        <v>-2.566036</v>
+        <v>-2.61451648</v>
       </c>
       <c r="O77">
-        <v>-0.6415089999999999</v>
+        <v>-0.65362912</v>
       </c>
       <c r="P77">
-        <v>-1.924527</v>
+        <v>-1.96088736</v>
       </c>
       <c r="Q77">
-        <v>-1.684527</v>
+        <v>-1.72088736</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3102190002484953</v>
+        <v>0.3212364585921827</v>
       </c>
       <c r="T77">
-        <v>2.557133823189786</v>
+        <v>2.663681065822694</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07356912857848492</v>
+        <v>0.07260111372876803</v>
       </c>
       <c r="W77">
-        <v>0.2184523994811932</v>
+        <v>0.2186806573827565</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2942765143139398</v>
+        <v>0.2904044549150721</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2432940496730188</v>
+        <v>0.2451940496730188</v>
       </c>
       <c r="C78">
-        <v>-6.937001122212813</v>
+        <v>-7.204716004217094</v>
       </c>
       <c r="D78">
-        <v>6.518598877787187</v>
+        <v>6.456483995782906</v>
       </c>
       <c r="E78">
-        <v>15.5656</v>
+        <v>15.7712</v>
       </c>
       <c r="F78">
-        <v>15.6256</v>
+        <v>15.8312</v>
       </c>
       <c r="G78">
         <v>2.17</v>
@@ -7683,37 +7683,37 @@
         <v>1.07</v>
       </c>
       <c r="M78">
-        <v>3.68451648</v>
+        <v>3.73299696</v>
       </c>
       <c r="N78">
-        <v>-2.61451648</v>
+        <v>-2.66299696</v>
       </c>
       <c r="O78">
-        <v>-0.65362912</v>
+        <v>-0.66574924</v>
       </c>
       <c r="P78">
-        <v>-1.96088736</v>
+        <v>-1.99724772</v>
       </c>
       <c r="Q78">
-        <v>-1.72088736</v>
+        <v>-1.75724772</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3212364585921827</v>
+        <v>0.3332119567918428</v>
       </c>
       <c r="T78">
-        <v>2.663681065822694</v>
+        <v>2.779493286075854</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07260111372876803</v>
+        <v>0.0716582421219009</v>
       </c>
       <c r="W78">
-        <v>0.2186806573827565</v>
+        <v>0.2189029865076558</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2904044549150721</v>
+        <v>0.2866329684876036</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2451940496730188</v>
+        <v>0.2470940496730188</v>
       </c>
       <c r="C79">
-        <v>-7.204716004217094</v>
+        <v>-7.471258290449175</v>
       </c>
       <c r="D79">
-        <v>6.456483995782906</v>
+        <v>6.395541709550826</v>
       </c>
       <c r="E79">
-        <v>15.7712</v>
+        <v>15.9768</v>
       </c>
       <c r="F79">
-        <v>15.8312</v>
+        <v>16.0368</v>
       </c>
       <c r="G79">
         <v>2.17</v>
@@ -7765,37 +7765,37 @@
         <v>1.07</v>
       </c>
       <c r="M79">
-        <v>3.73299696</v>
+        <v>3.78147744</v>
       </c>
       <c r="N79">
-        <v>-2.66299696</v>
+        <v>-2.71147744</v>
       </c>
       <c r="O79">
-        <v>-0.66574924</v>
+        <v>-0.6778693600000001</v>
       </c>
       <c r="P79">
-        <v>-1.99724772</v>
+        <v>-2.03360808</v>
       </c>
       <c r="Q79">
-        <v>-1.75724772</v>
+        <v>-1.79360808</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3332119567918428</v>
+        <v>0.3462761366460174</v>
       </c>
       <c r="T79">
-        <v>2.779493286075854</v>
+        <v>2.905833889988393</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0716582421219009</v>
+        <v>0.07073954671008166</v>
       </c>
       <c r="W79">
-        <v>0.2189029865076558</v>
+        <v>0.2191196148857628</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2866329684876036</v>
+        <v>0.2829581868403266</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2470940496730188</v>
+        <v>0.2489940496730188</v>
       </c>
       <c r="C80">
-        <v>-7.471258290449175</v>
+        <v>-7.736660874568644</v>
       </c>
       <c r="D80">
-        <v>6.395541709550826</v>
+        <v>6.335739125431356</v>
       </c>
       <c r="E80">
-        <v>15.9768</v>
+        <v>16.1824</v>
       </c>
       <c r="F80">
-        <v>16.0368</v>
+        <v>16.2424</v>
       </c>
       <c r="G80">
         <v>2.17</v>
@@ -7847,37 +7847,37 @@
         <v>1.07</v>
       </c>
       <c r="M80">
-        <v>3.78147744</v>
+        <v>3.82995792</v>
       </c>
       <c r="N80">
-        <v>-2.71147744</v>
+        <v>-2.75995792</v>
       </c>
       <c r="O80">
-        <v>-0.6778693600000001</v>
+        <v>-0.6899894799999999</v>
       </c>
       <c r="P80">
-        <v>-2.03360808</v>
+        <v>-2.06996844</v>
       </c>
       <c r="Q80">
-        <v>-1.79360808</v>
+        <v>-1.82996844</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3462761366460174</v>
+        <v>0.3605845241053517</v>
       </c>
       <c r="T80">
-        <v>2.905833889988393</v>
+        <v>3.044206932368793</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07073954671008166</v>
+        <v>0.06984410940995404</v>
       </c>
       <c r="W80">
-        <v>0.2191196148857628</v>
+        <v>0.2193307590011329</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2829581868403266</v>
+        <v>0.2793764376398162</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2489940496730188</v>
+        <v>0.2508940496730188</v>
       </c>
       <c r="C81">
-        <v>-7.736660874568644</v>
+        <v>-8.000955431322055</v>
       </c>
       <c r="D81">
-        <v>6.335739125431356</v>
+        <v>6.277044568677947</v>
       </c>
       <c r="E81">
-        <v>16.1824</v>
+        <v>16.388</v>
       </c>
       <c r="F81">
-        <v>16.2424</v>
+        <v>16.448</v>
       </c>
       <c r="G81">
         <v>2.17</v>
@@ -7929,37 +7929,37 @@
         <v>1.07</v>
       </c>
       <c r="M81">
-        <v>3.82995792</v>
+        <v>3.8784384</v>
       </c>
       <c r="N81">
-        <v>-2.75995792</v>
+        <v>-2.8084384</v>
       </c>
       <c r="O81">
-        <v>-0.6899894799999999</v>
+        <v>-0.7021096</v>
       </c>
       <c r="P81">
-        <v>-2.06996844</v>
+        <v>-2.1063288</v>
       </c>
       <c r="Q81">
-        <v>-1.82996844</v>
+        <v>-1.8663288</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3605845241053517</v>
+        <v>0.3763237503106192</v>
       </c>
       <c r="T81">
-        <v>3.044206932368793</v>
+        <v>3.196417278987233</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06984410940995404</v>
+        <v>0.06897105804232961</v>
       </c>
       <c r="W81">
-        <v>0.2193307590011329</v>
+        <v>0.2195366245136187</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2793764376398162</v>
+        <v>0.2758842321693185</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2508940496730188</v>
+        <v>0.2527940496730188</v>
       </c>
       <c r="C82">
-        <v>-8.000955431322055</v>
+        <v>-8.264172472484965</v>
       </c>
       <c r="D82">
-        <v>6.277044568677947</v>
+        <v>6.219427527515036</v>
       </c>
       <c r="E82">
-        <v>16.388</v>
+        <v>16.5936</v>
       </c>
       <c r="F82">
-        <v>16.448</v>
+        <v>16.6536</v>
       </c>
       <c r="G82">
         <v>2.17</v>
@@ -8011,37 +8011,37 @@
         <v>1.07</v>
       </c>
       <c r="M82">
-        <v>3.8784384</v>
+        <v>3.926918880000001</v>
       </c>
       <c r="N82">
-        <v>-2.8084384</v>
+        <v>-2.85691888</v>
       </c>
       <c r="O82">
-        <v>-0.7021096</v>
+        <v>-0.7142297200000001</v>
       </c>
       <c r="P82">
-        <v>-2.1063288</v>
+        <v>-2.14268916</v>
       </c>
       <c r="Q82">
-        <v>-1.8663288</v>
+        <v>-1.90268916</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3763237503106192</v>
+        <v>0.3937197371690729</v>
       </c>
       <c r="T82">
-        <v>3.196417278987233</v>
+        <v>3.364649767354982</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06897105804232961</v>
+        <v>0.06811956349859714</v>
       </c>
       <c r="W82">
-        <v>0.2195366245136187</v>
+        <v>0.2197374069270308</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2758842321693185</v>
+        <v>0.2724782539943886</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2527940496730188</v>
+        <v>0.2546940496730188</v>
       </c>
       <c r="C83">
-        <v>-8.264172472484965</v>
+        <v>-8.526341399751088</v>
       </c>
       <c r="D83">
-        <v>6.219427527515036</v>
+        <v>6.162858600248914</v>
       </c>
       <c r="E83">
-        <v>16.5936</v>
+        <v>16.7992</v>
       </c>
       <c r="F83">
-        <v>16.6536</v>
+        <v>16.8592</v>
       </c>
       <c r="G83">
         <v>2.17</v>
@@ -8093,37 +8093,37 @@
         <v>1.07</v>
       </c>
       <c r="M83">
-        <v>3.926918880000001</v>
+        <v>3.97539936</v>
       </c>
       <c r="N83">
-        <v>-2.85691888</v>
+        <v>-2.905399360000001</v>
       </c>
       <c r="O83">
-        <v>-0.7142297200000001</v>
+        <v>-0.7263498400000001</v>
       </c>
       <c r="P83">
-        <v>-2.14268916</v>
+        <v>-2.17904952</v>
       </c>
       <c r="Q83">
-        <v>-1.90268916</v>
+        <v>-1.93904952</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3937197371690729</v>
+        <v>0.4130486114562437</v>
       </c>
       <c r="T83">
-        <v>3.364649767354982</v>
+        <v>3.551574754430259</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06811956349859714</v>
+        <v>0.06728883711446791</v>
       </c>
       <c r="W83">
-        <v>0.2197374069270308</v>
+        <v>0.2199332922084085</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2724782539943886</v>
+        <v>0.2691553484578716</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2546940496730188</v>
+        <v>0.2565940496730188</v>
       </c>
       <c r="C84">
-        <v>-8.526341399751088</v>
+        <v>-8.787490554761092</v>
       </c>
       <c r="D84">
-        <v>6.162858600248914</v>
+        <v>6.107309445238909</v>
       </c>
       <c r="E84">
-        <v>16.7992</v>
+        <v>17.0048</v>
       </c>
       <c r="F84">
-        <v>16.8592</v>
+        <v>17.0648</v>
       </c>
       <c r="G84">
         <v>2.17</v>
@@ -8175,37 +8175,37 @@
         <v>1.07</v>
       </c>
       <c r="M84">
-        <v>3.97539936</v>
+        <v>4.02387984</v>
       </c>
       <c r="N84">
-        <v>-2.905399360000001</v>
+        <v>-2.95387984</v>
       </c>
       <c r="O84">
-        <v>-0.7263498400000001</v>
+        <v>-0.73846996</v>
       </c>
       <c r="P84">
-        <v>-2.17904952</v>
+        <v>-2.21540988</v>
       </c>
       <c r="Q84">
-        <v>-1.93904952</v>
+        <v>-1.97540988</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4130486114562437</v>
+        <v>0.4346514709536697</v>
       </c>
       <c r="T84">
-        <v>3.551574754430259</v>
+        <v>3.760490916455569</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06728883711446791</v>
+        <v>0.06647812823357072</v>
       </c>
       <c r="W84">
-        <v>0.2199332922084085</v>
+        <v>0.220124457362524</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2691553484578716</v>
+        <v>0.2659125129342829</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2565940496730188</v>
+        <v>0.2584940496730188</v>
       </c>
       <c r="C85">
-        <v>-8.787490554761092</v>
+        <v>-9.047647266449987</v>
       </c>
       <c r="D85">
-        <v>6.107309445238909</v>
+        <v>6.052752733550015</v>
       </c>
       <c r="E85">
-        <v>17.0048</v>
+        <v>17.2104</v>
       </c>
       <c r="F85">
-        <v>17.0648</v>
+        <v>17.2704</v>
       </c>
       <c r="G85">
         <v>2.17</v>
@@ -8257,37 +8257,37 @@
         <v>1.07</v>
       </c>
       <c r="M85">
-        <v>4.02387984</v>
+        <v>4.07236032</v>
       </c>
       <c r="N85">
-        <v>-2.95387984</v>
+        <v>-3.00236032</v>
       </c>
       <c r="O85">
-        <v>-0.73846996</v>
+        <v>-0.75059008</v>
       </c>
       <c r="P85">
-        <v>-2.21540988</v>
+        <v>-2.25177024</v>
       </c>
       <c r="Q85">
-        <v>-1.97540988</v>
+        <v>-2.01177024</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4346514709536697</v>
+        <v>0.4589546878882742</v>
       </c>
       <c r="T85">
-        <v>3.760490916455569</v>
+        <v>3.995521598734042</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06647812823357072</v>
+        <v>0.06568672194507581</v>
       </c>
       <c r="W85">
-        <v>0.220124457362524</v>
+        <v>0.2203110709653511</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2659125129342829</v>
+        <v>0.2627468877803033</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2584940496730188</v>
+        <v>0.2603940496730188</v>
       </c>
       <c r="C86">
-        <v>-9.047647266449982</v>
+        <v>-9.306837895879216</v>
       </c>
       <c r="D86">
-        <v>6.052752733550017</v>
+        <v>5.999162104120784</v>
       </c>
       <c r="E86">
-        <v>17.2104</v>
+        <v>17.416</v>
       </c>
       <c r="F86">
-        <v>17.2704</v>
+        <v>17.476</v>
       </c>
       <c r="G86">
         <v>2.17</v>
@@ -8339,37 +8339,37 @@
         <v>1.07</v>
       </c>
       <c r="M86">
-        <v>4.07236032</v>
+        <v>4.1208408</v>
       </c>
       <c r="N86">
-        <v>-3.002360319999999</v>
+        <v>-3.0508408</v>
       </c>
       <c r="O86">
-        <v>-0.7505900799999998</v>
+        <v>-0.7627101999999999</v>
       </c>
       <c r="P86">
-        <v>-2.251770239999999</v>
+        <v>-2.2881306</v>
       </c>
       <c r="Q86">
-        <v>-2.01177024</v>
+        <v>-2.048130599999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4589546878882739</v>
+        <v>0.4864983337474922</v>
       </c>
       <c r="T86">
-        <v>3.995521598734039</v>
+        <v>4.261889705316309</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06568672194507583</v>
+        <v>0.06491393698101611</v>
       </c>
       <c r="W86">
-        <v>0.2203110709653511</v>
+        <v>0.2204932936598764</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2627468877803034</v>
+        <v>0.2596557479240645</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2603940496730188</v>
+        <v>0.2622940496730188</v>
       </c>
       <c r="C87">
-        <v>-9.306837895879216</v>
+        <v>-9.565087878708052</v>
       </c>
       <c r="D87">
-        <v>5.999162104120784</v>
+        <v>5.946512121291948</v>
       </c>
       <c r="E87">
-        <v>17.416</v>
+        <v>17.6216</v>
       </c>
       <c r="F87">
-        <v>17.476</v>
+        <v>17.6816</v>
       </c>
       <c r="G87">
         <v>2.17</v>
@@ -8421,37 +8421,37 @@
         <v>1.07</v>
       </c>
       <c r="M87">
-        <v>4.1208408</v>
+        <v>4.16932128</v>
       </c>
       <c r="N87">
-        <v>-3.0508408</v>
+        <v>-3.09932128</v>
       </c>
       <c r="O87">
-        <v>-0.7627101999999999</v>
+        <v>-0.77483032</v>
       </c>
       <c r="P87">
-        <v>-2.2881306</v>
+        <v>-2.32449096</v>
       </c>
       <c r="Q87">
-        <v>-2.048130599999999</v>
+        <v>-2.08449096</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4864983337474922</v>
+        <v>0.5179767861580273</v>
       </c>
       <c r="T87">
-        <v>4.261889705316309</v>
+        <v>4.566310398553188</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06491393698101611</v>
+        <v>0.06415912376030662</v>
       </c>
       <c r="W87">
-        <v>0.2204932936598764</v>
+        <v>0.2206712786173197</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2596557479240645</v>
+        <v>0.2566364950412265</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2622940496730188</v>
+        <v>0.2641940496730188</v>
       </c>
       <c r="C88">
-        <v>-9.565087878708052</v>
+        <v>-9.822421765447963</v>
       </c>
       <c r="D88">
-        <v>5.946512121291948</v>
+        <v>5.894778234552037</v>
       </c>
       <c r="E88">
-        <v>17.6216</v>
+        <v>17.8272</v>
       </c>
       <c r="F88">
-        <v>17.6816</v>
+        <v>17.8872</v>
       </c>
       <c r="G88">
         <v>2.17</v>
@@ -8503,37 +8503,37 @@
         <v>1.07</v>
       </c>
       <c r="M88">
-        <v>4.16932128</v>
+        <v>4.21780176</v>
       </c>
       <c r="N88">
-        <v>-3.09932128</v>
+        <v>-3.14780176</v>
       </c>
       <c r="O88">
-        <v>-0.77483032</v>
+        <v>-0.78695044</v>
       </c>
       <c r="P88">
-        <v>-2.32449096</v>
+        <v>-2.36085132</v>
       </c>
       <c r="Q88">
-        <v>-2.08449096</v>
+        <v>-2.12085132</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5179767861580273</v>
+        <v>0.5542980774009525</v>
       </c>
       <c r="T88">
-        <v>4.566310398553188</v>
+        <v>4.917565044595742</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06415912376030662</v>
+        <v>0.06342166256765941</v>
       </c>
       <c r="W88">
-        <v>0.2206712786173197</v>
+        <v>0.2208451719665459</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2566364950412265</v>
+        <v>0.2536866502706377</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2641940496730188</v>
+        <v>0.2660940496730188</v>
       </c>
       <c r="C89">
-        <v>-9.822421765447963</v>
+        <v>-10.07886325963391</v>
       </c>
       <c r="D89">
-        <v>5.894778234552037</v>
+        <v>5.843936740366093</v>
       </c>
       <c r="E89">
-        <v>17.8272</v>
+        <v>18.0328</v>
       </c>
       <c r="F89">
-        <v>17.8872</v>
+        <v>18.0928</v>
       </c>
       <c r="G89">
         <v>2.17</v>
@@ -8585,37 +8585,37 @@
         <v>1.07</v>
       </c>
       <c r="M89">
-        <v>4.21780176</v>
+        <v>4.266282240000001</v>
       </c>
       <c r="N89">
-        <v>-3.14780176</v>
+        <v>-3.19628224</v>
       </c>
       <c r="O89">
-        <v>-0.78695044</v>
+        <v>-0.7990705600000001</v>
       </c>
       <c r="P89">
-        <v>-2.36085132</v>
+        <v>-2.39721168</v>
       </c>
       <c r="Q89">
-        <v>-2.12085132</v>
+        <v>-2.157211680000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5542980774009525</v>
+        <v>0.5966729171843652</v>
       </c>
       <c r="T89">
-        <v>4.917565044595742</v>
+        <v>5.327362131645387</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06342166256765941</v>
+        <v>0.06270096185666328</v>
       </c>
       <c r="W89">
-        <v>0.2208451719665459</v>
+        <v>0.2210151131941988</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2536866502706377</v>
+        <v>0.2508038474266532</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2660940496730188</v>
+        <v>0.2679940496730188</v>
       </c>
       <c r="C90">
-        <v>-10.07886325963391</v>
+        <v>-10.33443525403716</v>
       </c>
       <c r="D90">
-        <v>5.843936740366093</v>
+        <v>5.793964745962843</v>
       </c>
       <c r="E90">
-        <v>18.0328</v>
+        <v>18.2384</v>
       </c>
       <c r="F90">
-        <v>18.0928</v>
+        <v>18.2984</v>
       </c>
       <c r="G90">
         <v>2.17</v>
@@ -8667,37 +8667,37 @@
         <v>1.07</v>
       </c>
       <c r="M90">
-        <v>4.266282240000001</v>
+        <v>4.31476272</v>
       </c>
       <c r="N90">
-        <v>-3.19628224</v>
+        <v>-3.24476272</v>
       </c>
       <c r="O90">
-        <v>-0.7990705600000001</v>
+        <v>-0.8111906799999999</v>
       </c>
       <c r="P90">
-        <v>-2.39721168</v>
+        <v>-2.43357204</v>
       </c>
       <c r="Q90">
-        <v>-2.157211680000001</v>
+        <v>-2.193572039999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5966729171843652</v>
+        <v>0.6467522732920348</v>
       </c>
       <c r="T90">
-        <v>5.327362131645387</v>
+        <v>5.811667779976785</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06270096185666328</v>
+        <v>0.06199645666726258</v>
       </c>
       <c r="W90">
-        <v>0.2210151131941988</v>
+        <v>0.2211812355178595</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2508038474266532</v>
+        <v>0.2479858266690503</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2679940496730188</v>
+        <v>0.2698940496730188</v>
       </c>
       <c r="C91">
-        <v>-10.33443525403716</v>
+        <v>-10.58915986503594</v>
       </c>
       <c r="D91">
-        <v>5.793964745962843</v>
+        <v>5.744840134964058</v>
       </c>
       <c r="E91">
-        <v>18.2384</v>
+        <v>18.444</v>
       </c>
       <c r="F91">
-        <v>18.2984</v>
+        <v>18.504</v>
       </c>
       <c r="G91">
         <v>2.17</v>
@@ -8749,37 +8749,37 @@
         <v>1.07</v>
       </c>
       <c r="M91">
-        <v>4.31476272</v>
+        <v>4.363243199999999</v>
       </c>
       <c r="N91">
-        <v>-3.24476272</v>
+        <v>-3.293243199999999</v>
       </c>
       <c r="O91">
-        <v>-0.8111906799999999</v>
+        <v>-0.8233107999999998</v>
       </c>
       <c r="P91">
-        <v>-2.43357204</v>
+        <v>-2.469932399999999</v>
       </c>
       <c r="Q91">
-        <v>-2.193572039999999</v>
+        <v>-2.229932399999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6467522732920348</v>
+        <v>0.7068475006212385</v>
       </c>
       <c r="T91">
-        <v>5.811667779976785</v>
+        <v>6.392834557974466</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06199645666726258</v>
+        <v>0.06130760714873745</v>
       </c>
       <c r="W91">
-        <v>0.2211812355178595</v>
+        <v>0.2213436662343277</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2479858266690503</v>
+        <v>0.2452304285949498</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2698940496730188</v>
+        <v>0.2717940496730188</v>
       </c>
       <c r="C92">
-        <v>-10.58915986503594</v>
+        <v>-10.84305846525229</v>
       </c>
       <c r="D92">
-        <v>5.744840134964058</v>
+        <v>5.696541534747706</v>
       </c>
       <c r="E92">
-        <v>18.444</v>
+        <v>18.6496</v>
       </c>
       <c r="F92">
-        <v>18.504</v>
+        <v>18.7096</v>
       </c>
       <c r="G92">
         <v>2.17</v>
@@ -8831,37 +8831,37 @@
         <v>1.07</v>
       </c>
       <c r="M92">
-        <v>4.363243199999999</v>
+        <v>4.41172368</v>
       </c>
       <c r="N92">
-        <v>-3.293243199999999</v>
+        <v>-3.341723679999999</v>
       </c>
       <c r="O92">
-        <v>-0.8233107999999998</v>
+        <v>-0.8354309199999999</v>
       </c>
       <c r="P92">
-        <v>-2.469932399999999</v>
+        <v>-2.50629276</v>
       </c>
       <c r="Q92">
-        <v>-2.229932399999999</v>
+        <v>-2.26629276</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7068475006212385</v>
+        <v>0.7802972229124873</v>
       </c>
       <c r="T92">
-        <v>6.392834557974466</v>
+        <v>7.103149508860518</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06130760714873745</v>
+        <v>0.06063389718007</v>
       </c>
       <c r="W92">
-        <v>0.2213436662343277</v>
+        <v>0.2215025270449395</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2452304285949498</v>
+        <v>0.24253558872028</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2717940496730188</v>
+        <v>0.2736940496730188</v>
       </c>
       <c r="C93">
-        <v>-10.84305846525229</v>
+        <v>-11.0961517145563</v>
       </c>
       <c r="D93">
-        <v>5.696541534747706</v>
+        <v>5.649048285443697</v>
       </c>
       <c r="E93">
-        <v>18.6496</v>
+        <v>18.8552</v>
       </c>
       <c r="F93">
-        <v>18.7096</v>
+        <v>18.9152</v>
       </c>
       <c r="G93">
         <v>2.17</v>
@@ -8913,37 +8913,37 @@
         <v>1.07</v>
       </c>
       <c r="M93">
-        <v>4.41172368</v>
+        <v>4.46020416</v>
       </c>
       <c r="N93">
-        <v>-3.341723679999999</v>
+        <v>-3.39020416</v>
       </c>
       <c r="O93">
-        <v>-0.8354309199999999</v>
+        <v>-0.8475510399999999</v>
       </c>
       <c r="P93">
-        <v>-2.50629276</v>
+        <v>-2.54265312</v>
       </c>
       <c r="Q93">
-        <v>-2.26629276</v>
+        <v>-2.30265312</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7802972229124873</v>
+        <v>0.8721093757765483</v>
       </c>
       <c r="T93">
-        <v>7.103149508860518</v>
+        <v>7.991043197468085</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06063389718007</v>
+        <v>0.05997483308028662</v>
       </c>
       <c r="W93">
-        <v>0.2215025270449395</v>
+        <v>0.2216579343596684</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.24253558872028</v>
+        <v>0.2398993323211466</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2736940496730188</v>
+        <v>0.2755940496730188</v>
       </c>
       <c r="C94">
-        <v>-11.0961517145563</v>
+        <v>-11.34845958953225</v>
       </c>
       <c r="D94">
-        <v>5.649048285443697</v>
+        <v>5.602340410467754</v>
       </c>
       <c r="E94">
-        <v>18.8552</v>
+        <v>19.0608</v>
       </c>
       <c r="F94">
-        <v>18.9152</v>
+        <v>19.1208</v>
       </c>
       <c r="G94">
         <v>2.17</v>
@@ -8995,37 +8995,37 @@
         <v>1.07</v>
       </c>
       <c r="M94">
-        <v>4.46020416</v>
+        <v>4.50868464</v>
       </c>
       <c r="N94">
-        <v>-3.39020416</v>
+        <v>-3.43868464</v>
       </c>
       <c r="O94">
-        <v>-0.8475510399999999</v>
+        <v>-0.85967116</v>
       </c>
       <c r="P94">
-        <v>-2.54265312</v>
+        <v>-2.57901348</v>
       </c>
       <c r="Q94">
-        <v>-2.30265312</v>
+        <v>-2.33901348</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8721093757765483</v>
+        <v>0.9901535723160554</v>
       </c>
       <c r="T94">
-        <v>7.991043197468085</v>
+        <v>9.132620797106384</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05997483308028662</v>
+        <v>0.05932994240200397</v>
       </c>
       <c r="W94">
-        <v>0.2216579343596684</v>
+        <v>0.2218099995816075</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2398993323211466</v>
+        <v>0.2373197696080159</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2755940496730188</v>
+        <v>0.2774940496730188</v>
       </c>
       <c r="C95">
-        <v>-11.34845958953225</v>
+        <v>-11.60000141149492</v>
       </c>
       <c r="D95">
-        <v>5.602340410467754</v>
+        <v>5.556398588505079</v>
       </c>
       <c r="E95">
-        <v>19.0608</v>
+        <v>19.2664</v>
       </c>
       <c r="F95">
-        <v>19.1208</v>
+        <v>19.3264</v>
       </c>
       <c r="G95">
         <v>2.17</v>
@@ -9077,37 +9077,37 @@
         <v>1.07</v>
       </c>
       <c r="M95">
-        <v>4.50868464</v>
+        <v>4.557165120000001</v>
       </c>
       <c r="N95">
-        <v>-3.43868464</v>
+        <v>-3.48716512</v>
       </c>
       <c r="O95">
-        <v>-0.85967116</v>
+        <v>-0.8717912800000001</v>
       </c>
       <c r="P95">
-        <v>-2.57901348</v>
+        <v>-2.61537384</v>
       </c>
       <c r="Q95">
-        <v>-2.33901348</v>
+        <v>-2.37537384</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9901535723160554</v>
+        <v>1.147545834368732</v>
       </c>
       <c r="T95">
-        <v>9.132620797106384</v>
+        <v>10.65472426329078</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05932994240200397</v>
+        <v>0.05869877280198265</v>
       </c>
       <c r="W95">
-        <v>0.2218099995816075</v>
+        <v>0.2219588293732925</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2373197696080159</v>
+        <v>0.2347950912079306</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2774940496730188</v>
+        <v>0.2793940496730188</v>
       </c>
       <c r="C96">
-        <v>-11.60000141149492</v>
+        <v>-11.85079587313869</v>
       </c>
       <c r="D96">
-        <v>5.556398588505079</v>
+        <v>5.51120412686131</v>
       </c>
       <c r="E96">
-        <v>19.2664</v>
+        <v>19.472</v>
       </c>
       <c r="F96">
-        <v>19.3264</v>
+        <v>19.532</v>
       </c>
       <c r="G96">
         <v>2.17</v>
@@ -9159,37 +9159,37 @@
         <v>1.07</v>
       </c>
       <c r="M96">
-        <v>4.557165120000001</v>
+        <v>4.6056456</v>
       </c>
       <c r="N96">
-        <v>-3.48716512</v>
+        <v>-3.5356456</v>
       </c>
       <c r="O96">
-        <v>-0.8717912800000001</v>
+        <v>-0.8839113999999999</v>
       </c>
       <c r="P96">
-        <v>-2.61537384</v>
+        <v>-2.6517342</v>
       </c>
       <c r="Q96">
-        <v>-2.37537384</v>
+        <v>-2.4117342</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.147545834368732</v>
+        <v>1.367895001242479</v>
       </c>
       <c r="T96">
-        <v>10.65472426329078</v>
+        <v>12.78566911594895</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05869877280198265</v>
+        <v>0.05808089098301442</v>
       </c>
       <c r="W96">
-        <v>0.2219588293732925</v>
+        <v>0.2221045259062052</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2347950912079306</v>
+        <v>0.2323235639320577</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2793940496730188</v>
+        <v>0.2812940496730187</v>
       </c>
       <c r="C97">
-        <v>-11.85079587313869</v>
+        <v>-12.10086106389648</v>
       </c>
       <c r="D97">
-        <v>5.51120412686131</v>
+        <v>5.466738936103518</v>
       </c>
       <c r="E97">
-        <v>19.472</v>
+        <v>19.6776</v>
       </c>
       <c r="F97">
-        <v>19.532</v>
+        <v>19.7376</v>
       </c>
       <c r="G97">
         <v>2.17</v>
@@ -9241,37 +9241,37 @@
         <v>1.07</v>
       </c>
       <c r="M97">
-        <v>4.6056456</v>
+        <v>4.65412608</v>
       </c>
       <c r="N97">
-        <v>-3.5356456</v>
+        <v>-3.58412608</v>
       </c>
       <c r="O97">
-        <v>-0.8839113999999999</v>
+        <v>-0.89603152</v>
       </c>
       <c r="P97">
-        <v>-2.6517342</v>
+        <v>-2.68809456</v>
       </c>
       <c r="Q97">
-        <v>-2.4117342</v>
+        <v>-2.448094559999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.367895001242479</v>
+        <v>1.698418751553099</v>
       </c>
       <c r="T97">
-        <v>12.78566911594895</v>
+        <v>15.98208639493619</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05808089098301442</v>
+        <v>0.05747588170194134</v>
       </c>
       <c r="W97">
-        <v>0.2221045259062052</v>
+        <v>0.2222471870946822</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2323235639320577</v>
+        <v>0.2299035268077654</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2812940496730187</v>
+        <v>0.2831940496730188</v>
       </c>
       <c r="C98">
-        <v>-12.10086106389648</v>
+        <v>-12.35021449408103</v>
       </c>
       <c r="D98">
-        <v>5.466738936103518</v>
+        <v>5.422985505918964</v>
       </c>
       <c r="E98">
-        <v>19.6776</v>
+        <v>19.8832</v>
       </c>
       <c r="F98">
-        <v>19.7376</v>
+        <v>19.9432</v>
       </c>
       <c r="G98">
         <v>2.17</v>
@@ -9323,37 +9323,37 @@
         <v>1.07</v>
       </c>
       <c r="M98">
-        <v>4.654126079999999</v>
+        <v>4.70260656</v>
       </c>
       <c r="N98">
-        <v>-3.584126079999999</v>
+        <v>-3.632606559999999</v>
       </c>
       <c r="O98">
-        <v>-0.8960315199999997</v>
+        <v>-0.9081516399999998</v>
       </c>
       <c r="P98">
-        <v>-2.688094559999999</v>
+        <v>-2.724454919999999</v>
       </c>
       <c r="Q98">
-        <v>-2.448094559999999</v>
+        <v>-2.484454919999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.698418751553094</v>
+        <v>2.249291668737459</v>
       </c>
       <c r="T98">
-        <v>15.98208639493614</v>
+        <v>21.30944852658153</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05747588170194136</v>
+        <v>0.05688334683903474</v>
       </c>
       <c r="W98">
-        <v>0.2222471870946822</v>
+        <v>0.2223869068153556</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2299035268077655</v>
+        <v>0.227533387356139</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2831940496730188</v>
+        <v>0.2850940496730188</v>
       </c>
       <c r="C99">
-        <v>-12.35021449408103</v>
+        <v>-12.59887311787601</v>
       </c>
       <c r="D99">
-        <v>5.422985505918964</v>
+        <v>5.379926882123993</v>
       </c>
       <c r="E99">
-        <v>19.8832</v>
+        <v>20.0888</v>
       </c>
       <c r="F99">
-        <v>19.9432</v>
+        <v>20.1488</v>
       </c>
       <c r="G99">
         <v>2.17</v>
@@ -9405,37 +9405,37 @@
         <v>1.07</v>
       </c>
       <c r="M99">
-        <v>4.70260656</v>
+        <v>4.75108704</v>
       </c>
       <c r="N99">
-        <v>-3.632606559999999</v>
+        <v>-3.68108704</v>
       </c>
       <c r="O99">
-        <v>-0.9081516399999998</v>
+        <v>-0.9202717599999999</v>
       </c>
       <c r="P99">
-        <v>-2.724454919999999</v>
+        <v>-2.76081528</v>
       </c>
       <c r="Q99">
-        <v>-2.484454919999999</v>
+        <v>-2.52081528</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.249291668737459</v>
+        <v>3.351037503106189</v>
       </c>
       <c r="T99">
-        <v>21.30944852658153</v>
+        <v>31.9641727898723</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05688334683903474</v>
+        <v>0.05630290452435071</v>
       </c>
       <c r="W99">
-        <v>0.2223869068153556</v>
+        <v>0.2225237751131581</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.227533387356139</v>
+        <v>0.2252116180974029</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2850940496730188</v>
+        <v>0.2869940496730188</v>
       </c>
       <c r="C100">
-        <v>-12.59887311787601</v>
+        <v>-12.84685335524046</v>
       </c>
       <c r="D100">
-        <v>5.379926882123993</v>
+        <v>5.337546644759542</v>
       </c>
       <c r="E100">
-        <v>20.0888</v>
+        <v>20.2944</v>
       </c>
       <c r="F100">
-        <v>20.1488</v>
+        <v>20.3544</v>
       </c>
       <c r="G100">
         <v>2.17</v>
@@ -9487,37 +9487,37 @@
         <v>1.07</v>
       </c>
       <c r="M100">
-        <v>4.75108704</v>
+        <v>4.79956752</v>
       </c>
       <c r="N100">
-        <v>-3.68108704</v>
+        <v>-3.72956752</v>
       </c>
       <c r="O100">
-        <v>-0.9202717599999999</v>
+        <v>-0.93239188</v>
       </c>
       <c r="P100">
-        <v>-2.76081528</v>
+        <v>-2.79717564</v>
       </c>
       <c r="Q100">
-        <v>-2.52081528</v>
+        <v>-2.55717564</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.351037503106189</v>
+        <v>6.656275006212378</v>
       </c>
       <c r="T100">
-        <v>31.9641727898723</v>
+        <v>63.92834557974459</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05630290452435071</v>
+        <v>0.05573418831703403</v>
       </c>
       <c r="W100">
-        <v>0.2225237751131581</v>
+        <v>0.2226578783948434</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2252116180974029</v>
+        <v>0.2229367532681362</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2869940496730188</v>
-      </c>
-      <c r="C101">
-        <v>-12.84685335524046</v>
-      </c>
-      <c r="D101">
-        <v>5.337546644759542</v>
-      </c>
-      <c r="E101">
-        <v>20.2944</v>
-      </c>
-      <c r="F101">
-        <v>20.3544</v>
-      </c>
-      <c r="G101">
-        <v>2.17</v>
-      </c>
-      <c r="H101">
-        <v>20.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.31</v>
-      </c>
-      <c r="K101">
-        <v>0.24</v>
-      </c>
-      <c r="L101">
-        <v>1.07</v>
-      </c>
-      <c r="M101">
-        <v>4.79956752</v>
-      </c>
-      <c r="N101">
-        <v>-3.72956752</v>
-      </c>
-      <c r="O101">
-        <v>-0.93239188</v>
-      </c>
-      <c r="P101">
-        <v>-2.79717564</v>
-      </c>
-      <c r="Q101">
-        <v>-2.55717564</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.656275006212378</v>
-      </c>
-      <c r="T101">
-        <v>63.92834557974459</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05573418831703403</v>
-      </c>
-      <c r="W101">
-        <v>0.2226578783948434</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2229367532681362</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
